--- a/other/input/regulatory_limits/master_reg_limits.xlsx
+++ b/other/input/regulatory_limits/master_reg_limits.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26924"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC488831-3D61-4A37-9F88-5E657247C0DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7F48495-511C-4CF4-BE25-42C84A08908E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2805" yWindow="825" windowWidth="25035" windowHeight="14520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="26700" windowHeight="14400" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="regulatory_values" sheetId="2" r:id="rId2"/>
+    <sheet name="static_regulatory_values" sheetId="2" r:id="rId2"/>
     <sheet name="pick_list" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
@@ -521,7 +521,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -549,6 +549,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor indexed="41"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -580,7 +586,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -604,9 +610,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -627,6 +630,25 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -915,27 +937,28 @@
     <col min="3" max="3" width="33.28515625" customWidth="1"/>
     <col min="5" max="5" width="39" customWidth="1"/>
     <col min="6" max="6" width="24.7109375" customWidth="1"/>
-    <col min="7" max="7" width="22.42578125" customWidth="1"/>
+    <col min="7" max="7" width="31.5703125" customWidth="1"/>
+    <col min="8" max="8" width="12.5703125" customWidth="1"/>
     <col min="9" max="9" width="19.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="76.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:10" s="19" customFormat="1" ht="76.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="18" t="s">
         <v>35</v>
       </c>
       <c r="C1" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="19" t="s">
         <v>61</v>
       </c>
       <c r="E1" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="8" t="s">
         <v>60</v>
       </c>
       <c r="G1" s="8" t="s">
@@ -947,7 +970,7 @@
       <c r="I1" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="J1" s="8" t="s">
         <v>65</v>
       </c>
     </row>
@@ -986,7 +1009,7 @@
       <c r="D5" s="4"/>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
-      <c r="G5" s="10" t="s">
+      <c r="G5" s="9" t="s">
         <v>49</v>
       </c>
       <c r="H5" s="4"/>
@@ -1198,7 +1221,7 @@
       <c r="H15" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="I15" s="11">
+      <c r="I15" s="10">
         <v>0.86</v>
       </c>
       <c r="J15" s="4" t="s">
@@ -1241,33 +1264,33 @@
       <c r="I17" s="2"/>
       <c r="J17" s="2"/>
     </row>
-    <row r="18" spans="1:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="1" t="s">
+    <row r="18" spans="1:10" s="23" customFormat="1" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="B18" s="2"/>
-      <c r="C18" s="4" t="s">
+      <c r="B18" s="21"/>
+      <c r="C18" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D18" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="E18" s="11">
+      <c r="E18" s="22">
         <v>0.96</v>
       </c>
-      <c r="F18" s="4" t="s">
+      <c r="F18" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="G18" s="4" t="s">
+      <c r="G18" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="H18" s="4" t="s">
+      <c r="H18" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="I18" s="11">
+      <c r="I18" s="22">
         <v>0.96</v>
       </c>
-      <c r="J18" s="4" t="s">
+      <c r="J18" s="21" t="s">
         <v>47</v>
       </c>
     </row>
@@ -1432,7 +1455,7 @@
       <c r="D27" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E27" s="11">
+      <c r="E27" s="10">
         <v>0.998</v>
       </c>
       <c r="F27" s="4" t="s">
@@ -1444,7 +1467,7 @@
       <c r="H27" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="I27" s="11">
+      <c r="I27" s="10">
         <v>0.997</v>
       </c>
       <c r="J27" s="4" t="s">
@@ -1512,7 +1535,7 @@
       <c r="D31" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E31" s="11">
+      <c r="E31" s="10">
         <v>0.92200000000000004</v>
       </c>
       <c r="F31" s="4" t="s">
@@ -1524,7 +1547,7 @@
       <c r="H31" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="I31" s="11">
+      <c r="I31" s="10">
         <v>0.92200000000000004</v>
       </c>
       <c r="J31" s="4" t="s">
@@ -1542,7 +1565,7 @@
       <c r="D32" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E32" s="11">
+      <c r="E32" s="10">
         <v>0.85</v>
       </c>
       <c r="F32" s="4" t="s">
@@ -1550,7 +1573,7 @@
       </c>
       <c r="G32" s="2"/>
       <c r="H32" s="2"/>
-      <c r="I32" s="12"/>
+      <c r="I32" s="11"/>
       <c r="J32" s="2"/>
     </row>
     <row r="33" spans="1:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -1594,7 +1617,7 @@
       <c r="D35" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E35" s="11">
+      <c r="E35" s="10">
         <v>0.97799999999999998</v>
       </c>
       <c r="F35" s="4" t="s">
@@ -1606,7 +1629,7 @@
       <c r="H35" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="I35" s="11">
+      <c r="I35" s="10">
         <v>0.98599999999999999</v>
       </c>
       <c r="J35" s="4" t="s">
@@ -1625,1021 +1648,1021 @@
   <dimension ref="A1:J49"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="16"/>
-    <col min="2" max="2" width="26.140625" style="16" customWidth="1"/>
-    <col min="3" max="3" width="26.42578125" style="16" customWidth="1"/>
-    <col min="4" max="4" width="23.85546875" style="16" customWidth="1"/>
-    <col min="5" max="5" width="16.7109375" style="16" customWidth="1"/>
-    <col min="6" max="6" width="12.28515625" style="16" customWidth="1"/>
-    <col min="7" max="7" width="9.140625" style="16"/>
-    <col min="8" max="9" width="26.5703125" style="16" customWidth="1"/>
-    <col min="10" max="16384" width="9.140625" style="16"/>
+    <col min="1" max="1" width="9.140625" style="15"/>
+    <col min="2" max="2" width="26.140625" style="15" customWidth="1"/>
+    <col min="3" max="3" width="26.42578125" style="15" customWidth="1"/>
+    <col min="4" max="4" width="23.85546875" style="15" customWidth="1"/>
+    <col min="5" max="5" width="16.7109375" style="15" customWidth="1"/>
+    <col min="6" max="6" width="15.5703125" style="15" customWidth="1"/>
+    <col min="7" max="7" width="9.140625" style="15"/>
+    <col min="8" max="9" width="26.5703125" style="15" customWidth="1"/>
+    <col min="10" max="16384" width="9.140625" style="15"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="15" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="15" t="s">
+    <row r="1" spans="1:10" s="14" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="C1" s="15" t="s">
+      <c r="C1" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="D1" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="E1" s="15" t="s">
+      <c r="E1" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="F1" s="15" t="s">
+      <c r="F1" s="14" t="s">
         <v>121</v>
       </c>
-      <c r="G1" s="15" t="s">
+      <c r="G1" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="H1" s="15" t="s">
+      <c r="H1" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="I1" s="15" t="s">
+      <c r="I1" s="14" t="s">
         <v>114</v>
       </c>
-      <c r="J1" s="15" t="s">
+      <c r="J1" s="14" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A2" s="16" t="s">
-        <v>73</v>
-      </c>
-      <c r="B2" s="16" t="s">
+      <c r="A2" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="B2" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="C2" s="17" t="s">
+      <c r="C2" s="16" t="s">
         <v>78</v>
       </c>
-      <c r="D2" s="16" t="s">
+      <c r="D2" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="F2" s="16">
+      <c r="F2" s="15">
         <v>750</v>
       </c>
-      <c r="G2" s="16" t="s">
-        <v>124</v>
-      </c>
-      <c r="H2" s="16" t="s">
-        <v>80</v>
-      </c>
-      <c r="J2" s="16" t="s">
+      <c r="G2" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="H2" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="J2" s="15" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A3" s="16" t="s">
-        <v>73</v>
-      </c>
-      <c r="B3" s="16" t="s">
+      <c r="A3" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="B3" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="C3" s="17" t="s">
+      <c r="C3" s="16" t="s">
         <v>78</v>
       </c>
-      <c r="D3" s="16" t="s">
+      <c r="D3" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="F3" s="16">
+      <c r="F3" s="15">
         <v>87</v>
       </c>
-      <c r="G3" s="16" t="s">
-        <v>124</v>
-      </c>
-      <c r="H3" s="16" t="s">
-        <v>80</v>
-      </c>
-      <c r="I3" s="16" t="s">
+      <c r="G3" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="H3" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="I3" s="15" t="s">
         <v>113</v>
       </c>
-      <c r="J3" s="16" t="s">
+      <c r="J3" s="15" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A4" s="16" t="s">
-        <v>73</v>
-      </c>
-      <c r="B4" s="14" t="s">
+      <c r="A4" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="B4" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="17" t="s">
+      <c r="C4" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="D4" s="16" t="s">
+      <c r="D4" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="F4" s="16">
+      <c r="F4" s="15">
         <v>6</v>
       </c>
-      <c r="G4" s="16" t="s">
-        <v>124</v>
-      </c>
-      <c r="H4" s="16" t="s">
-        <v>80</v>
-      </c>
-      <c r="J4" s="16" t="s">
+      <c r="G4" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="H4" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="J4" s="15" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A5" s="16" t="s">
-        <v>73</v>
-      </c>
-      <c r="B5" s="14" t="s">
+      <c r="A5" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="B5" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="17" t="s">
+      <c r="C5" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="D5" s="16" t="s">
+      <c r="D5" s="15" t="s">
         <v>116</v>
       </c>
-      <c r="F5" s="16">
+      <c r="F5" s="15">
         <v>14</v>
       </c>
-      <c r="G5" s="16" t="s">
-        <v>124</v>
-      </c>
-      <c r="H5" s="16" t="s">
-        <v>80</v>
-      </c>
-      <c r="J5" s="16" t="s">
+      <c r="G5" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="H5" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="J5" s="15" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A6" s="16" t="s">
-        <v>73</v>
-      </c>
-      <c r="B6" s="14" t="s">
+      <c r="A6" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="B6" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="17" t="s">
+      <c r="C6" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="D6" s="16" t="s">
+      <c r="D6" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="F6" s="16">
+      <c r="F6" s="15">
         <v>4300</v>
       </c>
-      <c r="G6" s="16" t="s">
-        <v>124</v>
-      </c>
-      <c r="H6" s="16" t="s">
-        <v>80</v>
-      </c>
-      <c r="J6" s="16" t="s">
+      <c r="G6" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="H6" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="J6" s="15" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A7" s="16" t="s">
-        <v>73</v>
-      </c>
-      <c r="B7" s="14" t="s">
+      <c r="A7" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="B7" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="17" t="s">
+      <c r="C7" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="D7" s="16" t="s">
+      <c r="D7" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="F7" s="16">
+      <c r="F7" s="15">
         <v>10</v>
       </c>
-      <c r="G7" s="16" t="s">
-        <v>124</v>
-      </c>
-      <c r="H7" s="16" t="s">
-        <v>80</v>
-      </c>
-      <c r="J7" s="16" t="s">
+      <c r="G7" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="H7" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="J7" s="15" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A8" s="16" t="s">
-        <v>73</v>
-      </c>
-      <c r="B8" s="14" t="s">
+      <c r="A8" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="B8" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="C8" s="17" t="s">
+      <c r="C8" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="D8" s="16" t="s">
+      <c r="D8" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="F8" s="16">
+      <c r="F8" s="15">
         <v>50</v>
       </c>
-      <c r="G8" s="16" t="s">
-        <v>124</v>
-      </c>
-      <c r="H8" s="16" t="s">
-        <v>80</v>
-      </c>
-      <c r="J8" s="16" t="s">
+      <c r="G8" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="H8" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="J8" s="15" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A9" s="16" t="s">
-        <v>73</v>
-      </c>
-      <c r="B9" s="14" t="s">
+      <c r="A9" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="B9" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="C9" s="17" t="s">
+      <c r="C9" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="D9" s="16" t="s">
+      <c r="D9" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="F9" s="16">
+      <c r="F9" s="15">
         <v>100</v>
       </c>
-      <c r="G9" s="16" t="s">
-        <v>124</v>
-      </c>
-      <c r="H9" s="16" t="s">
-        <v>80</v>
-      </c>
-      <c r="J9" s="16" t="s">
+      <c r="G9" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="H9" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="J9" s="15" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A10" s="16" t="s">
-        <v>73</v>
-      </c>
-      <c r="B10" s="14" t="s">
+      <c r="A10" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="B10" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="C10" s="17" t="s">
+      <c r="C10" s="16" t="s">
         <v>83</v>
       </c>
-      <c r="D10" s="16" t="s">
+      <c r="D10" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="F10" s="16">
+      <c r="F10" s="15">
         <v>2000</v>
       </c>
-      <c r="G10" s="16" t="s">
-        <v>124</v>
-      </c>
-      <c r="H10" s="16" t="s">
-        <v>80</v>
-      </c>
-      <c r="J10" s="16" t="s">
+      <c r="G10" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="H10" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="J10" s="15" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="C11" s="17" t="s">
+      <c r="C11" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="J11" s="16" t="s">
+      <c r="J11" s="15" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A12" s="16" t="s">
-        <v>73</v>
-      </c>
-      <c r="B12" s="14" t="s">
+      <c r="A12" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="B12" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="C12" s="17" t="s">
+      <c r="C12" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="D12" s="16" t="s">
+      <c r="D12" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="F12" s="16">
+      <c r="F12" s="15">
         <v>4</v>
       </c>
-      <c r="G12" s="16" t="s">
-        <v>124</v>
-      </c>
-      <c r="H12" s="16" t="s">
-        <v>80</v>
-      </c>
-      <c r="J12" s="16" t="s">
+      <c r="G12" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="H12" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="J12" s="15" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A13" s="16" t="s">
-        <v>73</v>
-      </c>
-      <c r="B13" s="14" t="s">
+      <c r="A13" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="B13" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="C13" s="17" t="s">
+      <c r="C13" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="D13" s="16" t="s">
+      <c r="D13" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="F13" s="16">
+      <c r="F13" s="15">
         <v>100</v>
       </c>
-      <c r="G13" s="16" t="s">
-        <v>124</v>
-      </c>
-      <c r="H13" s="16" t="s">
-        <v>80</v>
-      </c>
-      <c r="J13" s="16" t="s">
+      <c r="G13" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="H13" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="J13" s="15" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A14" s="16" t="s">
-        <v>73</v>
-      </c>
-      <c r="B14" s="14" t="s">
+      <c r="A14" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="B14" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="C14" s="17" t="s">
+      <c r="C14" s="16" t="s">
         <v>122</v>
       </c>
-      <c r="D14" s="16" t="s">
+      <c r="D14" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="F14" s="16">
+      <c r="F14" s="15">
         <v>750</v>
       </c>
-      <c r="G14" s="16" t="s">
-        <v>124</v>
-      </c>
-      <c r="H14" s="16" t="s">
-        <v>80</v>
-      </c>
-      <c r="J14" s="16" t="s">
+      <c r="G14" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="H14" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="J14" s="15" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A15" s="16" t="s">
-        <v>73</v>
-      </c>
-      <c r="B15" s="16" t="s">
+      <c r="A15" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="B15" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="C15" s="17" t="s">
+      <c r="C15" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="D15" s="16" t="s">
+      <c r="D15" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="F15" s="16">
+      <c r="F15" s="15">
         <v>5</v>
       </c>
-      <c r="G15" s="16" t="s">
-        <v>124</v>
-      </c>
-      <c r="H15" s="16" t="s">
-        <v>80</v>
-      </c>
-      <c r="J15" s="16" t="s">
+      <c r="G15" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="H15" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="J15" s="15" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A16" s="16" t="s">
-        <v>73</v>
-      </c>
-      <c r="B16" s="16" t="s">
+      <c r="A16" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="B16" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="C16" s="17" t="s">
+      <c r="C16" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="D16" s="16" t="s">
+      <c r="D16" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="F16" s="16">
+      <c r="F16" s="15">
         <v>10</v>
       </c>
-      <c r="G16" s="16" t="s">
-        <v>124</v>
-      </c>
-      <c r="H16" s="16" t="s">
-        <v>80</v>
-      </c>
-      <c r="J16" s="16" t="s">
+      <c r="G16" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="H16" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="J16" s="15" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A17" s="16" t="s">
-        <v>73</v>
-      </c>
-      <c r="B17" s="16" t="s">
+      <c r="A17" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="B17" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="C17" s="17" t="s">
+      <c r="C17" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="D17" s="16" t="s">
+      <c r="D17" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="F17" s="16">
+      <c r="F17" s="15">
         <v>10</v>
       </c>
-      <c r="G17" s="16" t="s">
-        <v>124</v>
-      </c>
-      <c r="H17" s="16" t="s">
-        <v>80</v>
-      </c>
-      <c r="J17" s="16" t="s">
+      <c r="G17" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="H17" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="J17" s="15" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A18" s="16" t="s">
-        <v>73</v>
-      </c>
-      <c r="B18" s="14" t="s">
+      <c r="A18" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="B18" s="13" t="s">
         <v>125</v>
       </c>
-      <c r="C18" s="16" t="s">
+      <c r="C18" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="D18" s="16" t="s">
+      <c r="D18" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="F18" s="16">
+      <c r="F18" s="15">
         <v>100</v>
       </c>
-      <c r="G18" s="16" t="s">
-        <v>124</v>
-      </c>
-      <c r="H18" s="16" t="s">
-        <v>80</v>
-      </c>
-      <c r="I18" s="16" t="s">
+      <c r="G18" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="H18" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="I18" s="15" t="s">
         <v>126</v>
       </c>
-      <c r="J18" s="16" t="s">
+      <c r="J18" s="15" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A19" s="16" t="s">
-        <v>73</v>
-      </c>
-      <c r="B19" s="14" t="s">
+      <c r="A19" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="B19" s="13" t="s">
         <v>125</v>
       </c>
-      <c r="C19" s="16" t="s">
+      <c r="C19" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="D19" s="16" t="s">
+      <c r="D19" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="F19" s="16">
+      <c r="F19" s="15">
         <v>100</v>
       </c>
-      <c r="G19" s="16" t="s">
-        <v>124</v>
-      </c>
-      <c r="H19" s="16" t="s">
-        <v>80</v>
-      </c>
-      <c r="J19" s="16" t="s">
+      <c r="G19" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="H19" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="J19" s="15" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A20" s="16" t="s">
-        <v>73</v>
-      </c>
-      <c r="B20" s="16" t="s">
+      <c r="A20" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="B20" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="C20" s="17" t="s">
+      <c r="C20" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="D20" s="16" t="s">
+      <c r="D20" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="F20" s="16">
+      <c r="F20" s="15">
         <v>50</v>
       </c>
-      <c r="G20" s="16" t="s">
-        <v>124</v>
-      </c>
-      <c r="H20" s="16" t="s">
-        <v>80</v>
-      </c>
-      <c r="J20" s="16" t="s">
+      <c r="G20" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="H20" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="J20" s="15" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A21" s="16" t="s">
-        <v>73</v>
-      </c>
-      <c r="B21" s="16" t="s">
+      <c r="A21" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="B21" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="C21" s="17" t="s">
+      <c r="C21" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="D21" s="16" t="s">
+      <c r="D21" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="F21" s="16">
+      <c r="F21" s="15">
         <v>200</v>
       </c>
-      <c r="G21" s="16" t="s">
-        <v>124</v>
-      </c>
-      <c r="H21" s="16" t="s">
-        <v>80</v>
-      </c>
-      <c r="J21" s="16" t="s">
+      <c r="G21" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="H21" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="J21" s="15" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="C22" s="17" t="s">
+      <c r="C22" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="J22" s="16" t="s">
+      <c r="J22" s="15" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="C23" s="17" t="s">
+      <c r="C23" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="J23" s="16" t="s">
+      <c r="J23" s="15" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A24" s="16" t="s">
-        <v>73</v>
-      </c>
-      <c r="B24" s="16" t="s">
+      <c r="A24" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="B24" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="C24" s="16" t="s">
+      <c r="C24" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="D24" s="16" t="s">
+      <c r="D24" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="F24" s="16">
+      <c r="F24" s="15">
         <v>5000</v>
       </c>
-      <c r="G24" s="16" t="s">
-        <v>124</v>
-      </c>
-      <c r="H24" s="16" t="s">
-        <v>80</v>
-      </c>
-      <c r="J24" s="16" t="s">
+      <c r="G24" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="H24" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="J24" s="15" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A25" s="16" t="s">
-        <v>73</v>
-      </c>
-      <c r="B25" s="16" t="s">
+      <c r="A25" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="B25" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="C25" s="17" t="s">
+      <c r="C25" s="16" t="s">
         <v>92</v>
       </c>
-      <c r="D25" s="16" t="s">
+      <c r="D25" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="F25" s="16">
+      <c r="F25" s="15">
         <v>50</v>
       </c>
-      <c r="G25" s="16" t="s">
-        <v>124</v>
-      </c>
-      <c r="H25" s="16" t="s">
-        <v>80</v>
-      </c>
-      <c r="J25" s="16" t="s">
+      <c r="G25" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="H25" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="J25" s="15" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A26" s="16" t="s">
-        <v>73</v>
-      </c>
-      <c r="B26" s="16" t="s">
+      <c r="A26" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="B26" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="C26" s="17" t="s">
+      <c r="C26" s="16" t="s">
         <v>92</v>
       </c>
-      <c r="D26" s="16" t="s">
+      <c r="D26" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="E26" s="16" t="s">
+      <c r="E26" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="F26" s="16">
+      <c r="F26" s="15">
         <v>5000</v>
       </c>
-      <c r="G26" s="16" t="s">
-        <v>124</v>
-      </c>
-      <c r="H26" s="16" t="s">
-        <v>80</v>
-      </c>
-      <c r="J26" s="16" t="s">
+      <c r="G26" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="H26" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="J26" s="15" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="27" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A27" s="16" t="s">
-        <v>73</v>
-      </c>
-      <c r="B27" s="16" t="s">
+      <c r="A27" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="B27" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="C27" s="17" t="s">
+      <c r="C27" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="D27" s="16" t="s">
+      <c r="D27" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="F27" s="16">
+      <c r="F27" s="15">
         <v>10</v>
       </c>
-      <c r="G27" s="16" t="s">
-        <v>124</v>
-      </c>
-      <c r="H27" s="16" t="s">
-        <v>80</v>
-      </c>
-      <c r="J27" s="16" t="s">
+      <c r="G27" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="H27" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="J27" s="15" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="28" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A28" s="16" t="s">
-        <v>73</v>
-      </c>
-      <c r="B28" s="16" t="s">
+      <c r="A28" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="B28" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="C28" s="17" t="s">
+      <c r="C28" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="D28" s="16" t="s">
+      <c r="D28" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="F28" s="16">
+      <c r="F28" s="15">
         <v>100</v>
       </c>
-      <c r="G28" s="16" t="s">
-        <v>124</v>
-      </c>
-      <c r="H28" s="16" t="s">
-        <v>80</v>
-      </c>
-      <c r="J28" s="16" t="s">
+      <c r="G28" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="H28" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="J28" s="15" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A29" s="16" t="s">
-        <v>73</v>
-      </c>
-      <c r="B29" s="16" t="s">
+      <c r="A29" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="B29" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="C29" s="17" t="s">
+      <c r="C29" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="D29" s="16" t="s">
+      <c r="D29" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="F29" s="16">
+      <c r="F29" s="15">
         <v>200</v>
       </c>
-      <c r="G29" s="16" t="s">
-        <v>124</v>
-      </c>
-      <c r="H29" s="16" t="s">
-        <v>80</v>
-      </c>
-      <c r="J29" s="16" t="s">
+      <c r="G29" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="H29" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="J29" s="15" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="30" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A30" s="16" t="s">
-        <v>73</v>
-      </c>
-      <c r="B30" s="16" t="s">
+      <c r="A30" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="B30" s="15" t="s">
         <v>127</v>
       </c>
-      <c r="C30" s="17" t="s">
+      <c r="C30" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="J30" s="16" t="s">
+      <c r="J30" s="15" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A31" s="16" t="s">
-        <v>73</v>
-      </c>
-      <c r="B31" s="17" t="s">
+      <c r="A31" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="B31" s="16" t="s">
         <v>96</v>
       </c>
-      <c r="C31" s="17" t="s">
+      <c r="C31" s="16" t="s">
         <v>96</v>
       </c>
-      <c r="J31" s="16" t="s">
+      <c r="J31" s="15" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A32" s="16" t="s">
-        <v>73</v>
-      </c>
-      <c r="B32" s="16" t="s">
+      <c r="A32" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="B32" s="15" t="s">
         <v>128</v>
       </c>
-      <c r="C32" s="17" t="s">
+      <c r="C32" s="16" t="s">
         <v>97</v>
       </c>
-      <c r="J32" s="16" t="s">
+      <c r="J32" s="15" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="33" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A33" s="16" t="s">
-        <v>73</v>
-      </c>
-      <c r="B33" s="14" t="s">
+      <c r="A33" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="B33" s="13" t="s">
         <v>129</v>
       </c>
-      <c r="C33" s="17" t="s">
+      <c r="C33" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="J33" s="16" t="s">
+      <c r="J33" s="15" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="34" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A34" s="16" t="s">
-        <v>73</v>
-      </c>
-      <c r="B34" s="16" t="s">
+      <c r="A34" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="B34" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="C34" s="17" t="s">
+      <c r="C34" s="16" t="s">
         <v>99</v>
       </c>
-      <c r="D34" s="16" t="s">
+      <c r="D34" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="F34" s="16">
+      <c r="F34" s="15">
         <v>50</v>
       </c>
-      <c r="G34" s="16" t="s">
-        <v>124</v>
-      </c>
-      <c r="H34" s="16" t="s">
-        <v>80</v>
-      </c>
-      <c r="J34" s="16" t="s">
+      <c r="G34" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="H34" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="J34" s="15" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="35" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A35" s="16" t="s">
-        <v>73</v>
-      </c>
-      <c r="B35" s="16" t="s">
+      <c r="A35" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="B35" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="C35" s="17" t="s">
+      <c r="C35" s="16" t="s">
         <v>99</v>
       </c>
-      <c r="D35" s="16" t="s">
+      <c r="D35" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="F35" s="16">
+      <c r="F35" s="15">
         <v>10</v>
       </c>
-      <c r="G35" s="16" t="s">
-        <v>124</v>
-      </c>
-      <c r="H35" s="16" t="s">
-        <v>80</v>
-      </c>
-      <c r="J35" s="16" t="s">
+      <c r="G35" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="H35" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="J35" s="15" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="36" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A36" s="16" t="s">
-        <v>73</v>
-      </c>
-      <c r="B36" s="16" t="s">
+      <c r="A36" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="B36" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="C36" s="17" t="s">
+      <c r="C36" s="16" t="s">
         <v>99</v>
       </c>
-      <c r="D36" s="16" t="s">
+      <c r="D36" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="F36" s="16">
+      <c r="F36" s="15">
         <v>20</v>
       </c>
-      <c r="G36" s="16" t="s">
-        <v>124</v>
-      </c>
-      <c r="H36" s="16" t="s">
-        <v>80</v>
-      </c>
-      <c r="J36" s="16" t="s">
+      <c r="G36" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="H36" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="J36" s="15" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="37" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="C37" s="17" t="s">
+      <c r="C37" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="J37" s="16" t="s">
+      <c r="J37" s="15" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="38" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="C38" s="17" t="s">
+      <c r="C38" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="J38" s="16" t="s">
+      <c r="J38" s="15" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="39" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="C39" s="17" t="s">
+      <c r="C39" s="16" t="s">
         <v>102</v>
       </c>
-      <c r="J39" s="16" t="s">
+      <c r="J39" s="15" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="40" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A40" s="16" t="s">
-        <v>73</v>
-      </c>
-      <c r="B40" s="16" t="s">
+      <c r="A40" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="B40" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="C40" s="17" t="s">
+      <c r="C40" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="D40" s="16" t="s">
+      <c r="D40" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="F40" s="16">
+      <c r="F40" s="15">
         <v>2</v>
       </c>
-      <c r="G40" s="16" t="s">
-        <v>124</v>
-      </c>
-      <c r="H40" s="16" t="s">
-        <v>80</v>
-      </c>
-      <c r="J40" s="16" t="s">
+      <c r="G40" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="H40" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="J40" s="15" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="41" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="C41" s="17" t="s">
+      <c r="C41" s="16" t="s">
         <v>104</v>
       </c>
-      <c r="J41" s="16" t="s">
+      <c r="J41" s="15" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="42" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="C42" s="17" t="s">
+      <c r="C42" s="16" t="s">
         <v>105</v>
       </c>
-      <c r="J42" s="16" t="s">
+      <c r="J42" s="15" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="43" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="C43" s="17" t="s">
+      <c r="C43" s="16" t="s">
         <v>106</v>
       </c>
-      <c r="J43" s="16" t="s">
+      <c r="J43" s="15" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="44" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="C44" s="17" t="s">
+      <c r="C44" s="16" t="s">
         <v>107</v>
       </c>
-      <c r="J44" s="16" t="s">
+      <c r="J44" s="15" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="45" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="C45" s="17" t="s">
+      <c r="C45" s="16" t="s">
         <v>108</v>
       </c>
-      <c r="J45" s="16" t="s">
+      <c r="J45" s="15" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="46" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="C46" s="17" t="s">
+      <c r="C46" s="16" t="s">
         <v>109</v>
       </c>
-      <c r="J46" s="16" t="s">
+      <c r="J46" s="15" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="47" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A47" s="16" t="s">
-        <v>73</v>
-      </c>
-      <c r="B47" s="16" t="s">
+      <c r="A47" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="B47" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="C47" s="17" t="s">
+      <c r="C47" s="16" t="s">
         <v>110</v>
       </c>
-      <c r="D47" s="16" t="s">
+      <c r="D47" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="F47" s="16">
+      <c r="F47" s="15">
         <v>100</v>
       </c>
-      <c r="G47" s="16" t="s">
-        <v>124</v>
-      </c>
-      <c r="H47" s="16" t="s">
-        <v>80</v>
-      </c>
-      <c r="J47" s="16" t="s">
+      <c r="G47" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="H47" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="J47" s="15" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="48" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="C48" s="17" t="s">
+      <c r="C48" s="16" t="s">
         <v>111</v>
       </c>
-      <c r="J48" s="16" t="s">
+      <c r="J48" s="15" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="49" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A49" s="16" t="s">
-        <v>73</v>
-      </c>
-      <c r="B49" s="16" t="s">
+      <c r="A49" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="B49" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="C49" s="17" t="s">
+      <c r="C49" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="D49" s="16" t="s">
+      <c r="D49" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="F49" s="16">
+      <c r="F49" s="15">
         <v>2000</v>
       </c>
-      <c r="G49" s="16" t="s">
-        <v>124</v>
-      </c>
-      <c r="H49" s="16" t="s">
-        <v>80</v>
-      </c>
-      <c r="J49" s="16" t="s">
+      <c r="G49" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="H49" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="J49" s="15" t="s">
         <v>120</v>
       </c>
     </row>
@@ -2667,7 +2690,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>67</v>
       </c>
     </row>

--- a/other/input/regulatory_limits/master_reg_limits.xlsx
+++ b/other/input/regulatory_limits/master_reg_limits.xlsx
@@ -3,14 +3,17 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26924"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7F48495-511C-4CF4-BE25-42C84A08908E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{167C7E27-C7B2-463C-942C-01196AEFEF36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="26700" windowHeight="14400" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="29385" yWindow="-7080" windowWidth="26790" windowHeight="12690" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="static_regulatory_values" sheetId="2" r:id="rId2"/>
-    <sheet name="pick_list" sheetId="3" r:id="rId3"/>
+    <sheet name="static_regulatory_values" sheetId="2" r:id="rId1"/>
+    <sheet name="ReadMe" sheetId="8" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId3"/>
+    <sheet name="calculated_regulatory_values" sheetId="4" r:id="rId4"/>
+    <sheet name="pick_list" sheetId="3" r:id="rId5"/>
+    <sheet name="questions" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -27,7 +30,7 @@
     <author>Author</author>
   </authors>
   <commentList>
-    <comment ref="G16" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="I16" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
@@ -56,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="490" uniqueCount="143">
   <si>
     <t>alkalinity (as CaCO3)</t>
   </si>
@@ -433,9 +436,6 @@
     <t>ug/l</t>
   </si>
   <si>
-    <t>chromium</t>
-  </si>
-  <si>
     <t>chromium (total), as distinct from other chemical forms</t>
   </si>
   <si>
@@ -446,6 +446,48 @@
   </si>
   <si>
     <t>potassium</t>
+  </si>
+  <si>
+    <t>static or dynamic</t>
+  </si>
+  <si>
+    <t>static</t>
+  </si>
+  <si>
+    <t>formula</t>
+  </si>
+  <si>
+    <t>distinguish between TR and D</t>
+  </si>
+  <si>
+    <t>calculated</t>
+  </si>
+  <si>
+    <t>In the original toxicbooks.xls, for the three columns of static values (drinking water, stockwater, I rrigation water); does this value represent total?</t>
+  </si>
+  <si>
+    <t>sample_fraction</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>Dissolved</t>
+  </si>
+  <si>
+    <t>All ADEC Values acquired from https://dec.alaska.gov/water/water-quality/standards/</t>
+  </si>
+  <si>
+    <t>conversion_factor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(e^1.0166(ln hardness)-3.924) </t>
+  </si>
+  <si>
+    <t>?</t>
+  </si>
+  <si>
+    <t>--&gt; see pg 29 of adec criteria manual at https://dec.alaska.gov/water/water-quality/standards/</t>
   </si>
 </sst>
 </file>
@@ -586,7 +628,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -649,6 +691,18 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -928,724 +982,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J36"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="27.28515625" customWidth="1"/>
-    <col min="2" max="2" width="28.5703125" customWidth="1"/>
-    <col min="3" max="3" width="33.28515625" customWidth="1"/>
-    <col min="5" max="5" width="39" customWidth="1"/>
-    <col min="6" max="6" width="24.7109375" customWidth="1"/>
-    <col min="7" max="7" width="31.5703125" customWidth="1"/>
-    <col min="8" max="8" width="12.5703125" customWidth="1"/>
-    <col min="9" max="9" width="19.42578125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:10" s="19" customFormat="1" ht="76.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="B1" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="D1" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="J1" s="8" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="1"/>
-      <c r="B2" s="6"/>
-    </row>
-    <row r="3" spans="1:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="1"/>
-      <c r="B3" s="6"/>
-    </row>
-    <row r="4" spans="1:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
-    </row>
-    <row r="5" spans="1:10" ht="19.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="5">
-        <v>750</v>
-      </c>
-      <c r="D5" s="4"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="H5" s="4"/>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2"/>
-    </row>
-    <row r="6" spans="1:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B6" s="4">
-        <v>6</v>
-      </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
-    </row>
-    <row r="7" spans="1:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" s="4">
-        <v>10</v>
-      </c>
-      <c r="C7" s="4">
-        <v>340</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="E7" s="4">
-        <v>1</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="G7" s="4">
-        <v>150</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="I7" s="4">
-        <v>1</v>
-      </c>
-      <c r="J7" s="4" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B8" s="5">
-        <v>2000</v>
-      </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
-    </row>
-    <row r="9" spans="1:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B9" s="4">
-        <v>4</v>
-      </c>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
-    </row>
-    <row r="10" spans="1:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
-    </row>
-    <row r="11" spans="1:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B11" s="4">
-        <v>5</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="H11" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="I11" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="J11" s="4" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B12" s="2"/>
-      <c r="C12" s="5">
-        <v>860000</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="5">
-        <v>230000</v>
-      </c>
-      <c r="H12" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
-    </row>
-    <row r="13" spans="1:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B13" s="2"/>
-      <c r="C13" s="4">
-        <v>19</v>
-      </c>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="4">
-        <v>11</v>
-      </c>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2"/>
-    </row>
-    <row r="14" spans="1:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B14" s="4">
-        <v>100</v>
-      </c>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
-    </row>
-    <row r="15" spans="1:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B15" s="2"/>
-      <c r="C15" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="E15" s="4">
-        <v>0.316</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="G15" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="H15" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="I15" s="10">
-        <v>0.86</v>
-      </c>
-      <c r="J15" s="4" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B16" s="2"/>
-      <c r="C16" s="4">
-        <v>16</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="4">
-        <v>11</v>
-      </c>
-      <c r="H16" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="I16" s="2"/>
-      <c r="J16" s="2"/>
-    </row>
-    <row r="17" spans="1:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
-      <c r="J17" s="2"/>
-    </row>
-    <row r="18" spans="1:10" s="23" customFormat="1" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="B18" s="21"/>
-      <c r="C18" s="21" t="s">
-        <v>38</v>
-      </c>
-      <c r="D18" s="21" t="s">
-        <v>46</v>
-      </c>
-      <c r="E18" s="22">
-        <v>0.96</v>
-      </c>
-      <c r="F18" s="21" t="s">
-        <v>47</v>
-      </c>
-      <c r="G18" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="H18" s="21" t="s">
-        <v>46</v>
-      </c>
-      <c r="I18" s="22">
-        <v>0.96</v>
-      </c>
-      <c r="J18" s="21" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
-      <c r="J19" s="2"/>
-    </row>
-    <row r="20" spans="1:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B20" s="5">
-        <v>4000</v>
-      </c>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
-      <c r="I20" s="2"/>
-      <c r="J20" s="2"/>
-    </row>
-    <row r="21" spans="1:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
-      <c r="G21" s="5">
-        <v>1000</v>
-      </c>
-      <c r="H21" s="2"/>
-      <c r="I21" s="2"/>
-      <c r="J21" s="2"/>
-    </row>
-    <row r="22" spans="1:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B22" s="2"/>
-      <c r="C22" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="E22" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="F22" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="G22" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="H22" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="I22" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="J22" s="4" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
-      <c r="H23" s="2"/>
-      <c r="I23" s="2"/>
-      <c r="J23" s="2"/>
-    </row>
-    <row r="24" spans="1:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
-      <c r="G24" s="2"/>
-      <c r="H24" s="2"/>
-      <c r="I24" s="2"/>
-      <c r="J24" s="2"/>
-    </row>
-    <row r="25" spans="1:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B25" s="4">
-        <v>2</v>
-      </c>
-      <c r="C25" s="4">
-        <v>1.4</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="E25" s="2"/>
-      <c r="F25" s="2"/>
-      <c r="G25" s="4">
-        <v>0.77</v>
-      </c>
-      <c r="H25" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="I25" s="2"/>
-      <c r="J25" s="2"/>
-    </row>
-    <row r="26" spans="1:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
-      <c r="E26" s="2"/>
-      <c r="F26" s="2"/>
-      <c r="G26" s="2"/>
-      <c r="H26" s="2"/>
-      <c r="I26" s="2"/>
-      <c r="J26" s="2"/>
-    </row>
-    <row r="27" spans="1:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B27" s="4">
-        <v>100</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="E27" s="10">
-        <v>0.998</v>
-      </c>
-      <c r="F27" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="G27" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="H27" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="I27" s="10">
-        <v>0.997</v>
-      </c>
-      <c r="J27" s="4" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B28" s="5">
-        <v>10000</v>
-      </c>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
-      <c r="E28" s="2"/>
-      <c r="F28" s="2"/>
-      <c r="G28" s="2"/>
-      <c r="H28" s="2"/>
-      <c r="I28" s="2"/>
-      <c r="J28" s="2"/>
-    </row>
-    <row r="29" spans="1:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B29" s="5">
-        <v>10000</v>
-      </c>
-      <c r="C29" s="2"/>
-      <c r="D29" s="2"/>
-      <c r="E29" s="2"/>
-      <c r="F29" s="2"/>
-      <c r="G29" s="2"/>
-      <c r="H29" s="2"/>
-      <c r="I29" s="2"/>
-      <c r="J29" s="2"/>
-    </row>
-    <row r="30" spans="1:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B30" s="5">
-        <v>1000</v>
-      </c>
-      <c r="C30" s="2"/>
-      <c r="D30" s="2"/>
-      <c r="E30" s="2"/>
-      <c r="F30" s="2"/>
-      <c r="G30" s="2"/>
-      <c r="H30" s="2"/>
-      <c r="I30" s="2"/>
-      <c r="J30" s="2"/>
-    </row>
-    <row r="31" spans="1:10" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B31" s="4">
-        <v>50</v>
-      </c>
-      <c r="C31" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="D31" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="E31" s="10">
-        <v>0.92200000000000004</v>
-      </c>
-      <c r="F31" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="G31" s="4">
-        <v>5</v>
-      </c>
-      <c r="H31" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="I31" s="10">
-        <v>0.92200000000000004</v>
-      </c>
-      <c r="J31" s="4" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B32" s="2"/>
-      <c r="C32" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D32" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="E32" s="10">
-        <v>0.85</v>
-      </c>
-      <c r="F32" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="G32" s="2"/>
-      <c r="H32" s="2"/>
-      <c r="I32" s="11"/>
-      <c r="J32" s="2"/>
-    </row>
-    <row r="33" spans="1:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B33" s="4">
-        <v>2</v>
-      </c>
-      <c r="C33" s="2"/>
-      <c r="D33" s="2"/>
-      <c r="E33" s="2"/>
-      <c r="F33" s="2"/>
-      <c r="G33" s="2"/>
-      <c r="H33" s="2"/>
-      <c r="I33" s="2"/>
-      <c r="J33" s="2"/>
-    </row>
-    <row r="34" spans="1:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B34" s="2"/>
-      <c r="C34" s="2"/>
-      <c r="D34" s="2"/>
-      <c r="E34" s="2"/>
-      <c r="F34" s="2"/>
-      <c r="G34" s="2"/>
-      <c r="H34" s="2"/>
-      <c r="I34" s="2"/>
-      <c r="J34" s="2"/>
-    </row>
-    <row r="35" spans="1:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B35" s="2"/>
-      <c r="C35" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="D35" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="E35" s="10">
-        <v>0.97799999999999998</v>
-      </c>
-      <c r="F35" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="G35" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="H35" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="I35" s="10">
-        <v>0.98599999999999999</v>
-      </c>
-      <c r="J35" s="4" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:J49"/>
+  <dimension ref="A1:O49"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="15"/>
@@ -1659,7 +997,7 @@
     <col min="10" max="16384" width="9.140625" style="15"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="14" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" s="14" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="14" t="s">
         <v>66</v>
       </c>
@@ -1691,7 +1029,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:15" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A2" s="15" t="s">
         <v>73</v>
       </c>
@@ -1717,7 +1055,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:15" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A3" s="15" t="s">
         <v>73</v>
       </c>
@@ -1746,7 +1084,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:15" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A4" s="15" t="s">
         <v>73</v>
       </c>
@@ -1772,7 +1110,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A5" s="15" t="s">
         <v>73</v>
       </c>
@@ -1798,7 +1136,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A6" s="15" t="s">
         <v>73</v>
       </c>
@@ -1824,7 +1162,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A7" s="15" t="s">
         <v>73</v>
       </c>
@@ -1850,7 +1188,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A8" s="15" t="s">
         <v>73</v>
       </c>
@@ -1876,7 +1214,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:15" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A9" s="15" t="s">
         <v>73</v>
       </c>
@@ -1902,7 +1240,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:15" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A10" s="15" t="s">
         <v>73</v>
       </c>
@@ -1928,7 +1266,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:15" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C11" s="16" t="s">
         <v>84</v>
       </c>
@@ -1936,7 +1274,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:15" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A12" s="15" t="s">
         <v>73</v>
       </c>
@@ -1961,8 +1299,11 @@
       <c r="J12" s="15" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="13" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="O12" s="15" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A13" s="15" t="s">
         <v>73</v>
       </c>
@@ -1988,7 +1329,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:15" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A14" s="15" t="s">
         <v>73</v>
       </c>
@@ -2014,7 +1355,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:15" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A15" s="15" t="s">
         <v>73</v>
       </c>
@@ -2040,7 +1381,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:15" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A16" s="15" t="s">
         <v>73</v>
       </c>
@@ -2097,7 +1438,7 @@
         <v>73</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>125</v>
+        <v>10</v>
       </c>
       <c r="C18" s="15" t="s">
         <v>70</v>
@@ -2115,7 +1456,7 @@
         <v>80</v>
       </c>
       <c r="I18" s="15" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="J18" s="15" t="s">
         <v>120</v>
@@ -2126,7 +1467,7 @@
         <v>73</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>125</v>
+        <v>10</v>
       </c>
       <c r="C19" s="15" t="s">
         <v>70</v>
@@ -2379,7 +1720,7 @@
         <v>73</v>
       </c>
       <c r="B30" s="15" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C30" s="16" t="s">
         <v>95</v>
@@ -2407,7 +1748,7 @@
         <v>73</v>
       </c>
       <c r="B32" s="15" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C32" s="16" t="s">
         <v>97</v>
@@ -2421,7 +1762,7 @@
         <v>73</v>
       </c>
       <c r="B33" s="13" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C33" s="16" t="s">
         <v>98</v>
@@ -2684,7 +2025,1194 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C524EC06-ADD2-401E-AE7E-9D4059DEE3B4}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>138</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:L36"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="27.28515625" customWidth="1"/>
+    <col min="3" max="3" width="28.5703125" customWidth="1"/>
+    <col min="4" max="4" width="33.28515625" customWidth="1"/>
+    <col min="6" max="6" width="50" customWidth="1"/>
+    <col min="7" max="7" width="24.7109375" customWidth="1"/>
+    <col min="8" max="8" width="7.7109375" customWidth="1"/>
+    <col min="9" max="9" width="31.5703125" customWidth="1"/>
+    <col min="10" max="10" width="12.5703125" customWidth="1"/>
+    <col min="11" max="11" width="19.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" s="19" customFormat="1" ht="76.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="19" t="s">
+        <v>129</v>
+      </c>
+      <c r="B1" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="E1" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="H1" s="8"/>
+      <c r="I1" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="J1" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="K1" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="L1" s="8" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="1"/>
+      <c r="C2" s="6"/>
+    </row>
+    <row r="3" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="1"/>
+      <c r="C3" s="6"/>
+    </row>
+    <row r="4" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>130</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+    </row>
+    <row r="5" spans="1:12" ht="19.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>130</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" s="2"/>
+      <c r="D5" s="5">
+        <v>750</v>
+      </c>
+      <c r="E5" s="4"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="J5" s="4"/>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
+    </row>
+    <row r="6" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>130</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C6" s="4">
+        <v>6</v>
+      </c>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
+      <c r="L6" s="2"/>
+    </row>
+    <row r="7" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>130</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7" s="4">
+        <v>10</v>
+      </c>
+      <c r="D7" s="4">
+        <v>340</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="F7" s="4">
+        <v>1</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4">
+        <v>150</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="K7" s="4">
+        <v>1</v>
+      </c>
+      <c r="L7" s="4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>130</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C8" s="5">
+        <v>2000</v>
+      </c>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
+      <c r="L8" s="2"/>
+    </row>
+    <row r="9" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>130</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="4">
+        <v>4</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
+      <c r="L9" s="2"/>
+    </row>
+    <row r="10" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>130</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="2"/>
+      <c r="L10" s="2"/>
+    </row>
+    <row r="11" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>133</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="4">
+        <v>5</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="K11" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="L11" s="4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>130</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="2"/>
+      <c r="D12" s="5">
+        <v>860000</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="5">
+        <v>230000</v>
+      </c>
+      <c r="J12" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="K12" s="2"/>
+      <c r="L12" s="2"/>
+    </row>
+    <row r="13" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>130</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="2"/>
+      <c r="D13" s="4">
+        <v>19</v>
+      </c>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="4">
+        <v>11</v>
+      </c>
+      <c r="J13" s="2"/>
+      <c r="K13" s="2"/>
+      <c r="L13" s="2"/>
+    </row>
+    <row r="14" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>130</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" s="4">
+        <v>100</v>
+      </c>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+      <c r="K14" s="2"/>
+      <c r="L14" s="2"/>
+    </row>
+    <row r="15" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>133</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" s="2"/>
+      <c r="D15" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="F15" s="4">
+        <v>0.316</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="H15" s="4"/>
+      <c r="I15" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="J15" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="K15" s="10">
+        <v>0.86</v>
+      </c>
+      <c r="L15" s="4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>130</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C16" s="2"/>
+      <c r="D16" s="4">
+        <v>16</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="4">
+        <v>11</v>
+      </c>
+      <c r="J16" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="K16" s="2"/>
+      <c r="L16" s="2"/>
+    </row>
+    <row r="17" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>130</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
+      <c r="K17" s="2"/>
+      <c r="L17" s="2"/>
+    </row>
+    <row r="18" spans="1:12" s="23" customFormat="1" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>133</v>
+      </c>
+      <c r="B18" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="C18" s="21"/>
+      <c r="D18" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="E18" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="F18" s="22">
+        <v>0.96</v>
+      </c>
+      <c r="G18" s="21" t="s">
+        <v>47</v>
+      </c>
+      <c r="H18" s="21"/>
+      <c r="I18" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="J18" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="K18" s="22">
+        <v>0.96</v>
+      </c>
+      <c r="L18" s="21" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>130</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="J19" s="2"/>
+      <c r="K19" s="2"/>
+      <c r="L19" s="2"/>
+    </row>
+    <row r="20" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>130</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C20" s="5">
+        <v>4000</v>
+      </c>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="2"/>
+      <c r="K20" s="2"/>
+      <c r="L20" s="2"/>
+    </row>
+    <row r="21" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>130</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="5">
+        <v>1000</v>
+      </c>
+      <c r="J21" s="2"/>
+      <c r="K21" s="2"/>
+      <c r="L21" s="2"/>
+    </row>
+    <row r="22" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>133</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C22" s="2"/>
+      <c r="D22" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="H22" s="4"/>
+      <c r="I22" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="J22" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="K22" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="L22" s="4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>130</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="2"/>
+      <c r="K23" s="2"/>
+      <c r="L23" s="2"/>
+    </row>
+    <row r="24" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>130</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="2"/>
+      <c r="K24" s="2"/>
+      <c r="L24" s="2"/>
+    </row>
+    <row r="25" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>130</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C25" s="4">
+        <v>2</v>
+      </c>
+      <c r="D25" s="4">
+        <v>1.4</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="4">
+        <v>0.77</v>
+      </c>
+      <c r="J25" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="K25" s="2"/>
+      <c r="L25" s="2"/>
+    </row>
+    <row r="26" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>130</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="2"/>
+      <c r="K26" s="2"/>
+      <c r="L26" s="2"/>
+    </row>
+    <row r="27" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>133</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27" s="4">
+        <v>100</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="F27" s="10">
+        <v>0.998</v>
+      </c>
+      <c r="G27" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="H27" s="4"/>
+      <c r="I27" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="J27" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="K27" s="10">
+        <v>0.997</v>
+      </c>
+      <c r="L27" s="4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>130</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C28" s="5">
+        <v>10000</v>
+      </c>
+      <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="2"/>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
+      <c r="I28" s="2"/>
+      <c r="J28" s="2"/>
+      <c r="K28" s="2"/>
+      <c r="L28" s="2"/>
+    </row>
+    <row r="29" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>130</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C29" s="5">
+        <v>10000</v>
+      </c>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
+      <c r="F29" s="2"/>
+      <c r="G29" s="2"/>
+      <c r="H29" s="2"/>
+      <c r="I29" s="2"/>
+      <c r="J29" s="2"/>
+      <c r="K29" s="2"/>
+      <c r="L29" s="2"/>
+    </row>
+    <row r="30" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>130</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C30" s="5">
+        <v>1000</v>
+      </c>
+      <c r="D30" s="2"/>
+      <c r="E30" s="2"/>
+      <c r="F30" s="2"/>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2"/>
+      <c r="I30" s="2"/>
+      <c r="J30" s="2"/>
+      <c r="K30" s="2"/>
+      <c r="L30" s="2"/>
+    </row>
+    <row r="31" spans="1:12" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>133</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C31" s="4">
+        <v>50</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="F31" s="10">
+        <v>0.92200000000000004</v>
+      </c>
+      <c r="G31" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="H31" s="4"/>
+      <c r="I31" s="4">
+        <v>5</v>
+      </c>
+      <c r="J31" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="K31" s="10">
+        <v>0.92200000000000004</v>
+      </c>
+      <c r="L31" s="4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>133</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C32" s="2"/>
+      <c r="D32" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="F32" s="10">
+        <v>0.85</v>
+      </c>
+      <c r="G32" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="H32" s="4"/>
+      <c r="I32" s="2"/>
+      <c r="J32" s="2"/>
+      <c r="K32" s="11"/>
+      <c r="L32" s="2"/>
+    </row>
+    <row r="33" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>130</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C33" s="4">
+        <v>2</v>
+      </c>
+      <c r="D33" s="2"/>
+      <c r="E33" s="2"/>
+      <c r="F33" s="2"/>
+      <c r="G33" s="2"/>
+      <c r="H33" s="2"/>
+      <c r="I33" s="2"/>
+      <c r="J33" s="2"/>
+      <c r="K33" s="2"/>
+      <c r="L33" s="2"/>
+    </row>
+    <row r="34" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>130</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
+      <c r="E34" s="2"/>
+      <c r="F34" s="2"/>
+      <c r="G34" s="2"/>
+      <c r="H34" s="2"/>
+      <c r="I34" s="2"/>
+      <c r="J34" s="2"/>
+      <c r="K34" s="2"/>
+      <c r="L34" s="2"/>
+    </row>
+    <row r="35" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>133</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C35" s="2"/>
+      <c r="D35" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="F35" s="10">
+        <v>0.97799999999999998</v>
+      </c>
+      <c r="G35" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="H35" s="4"/>
+      <c r="I35" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="J35" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="K35" s="10">
+        <v>0.98599999999999999</v>
+      </c>
+      <c r="L35" s="4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31B77331-D835-4B41-9157-C8D156985AE1}">
+  <dimension ref="A1:G36"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="9.140625" style="15"/>
+    <col min="2" max="2" width="26.140625" style="15" customWidth="1"/>
+    <col min="3" max="3" width="26.42578125" style="15" customWidth="1"/>
+    <col min="4" max="4" width="23.85546875" style="15" customWidth="1"/>
+    <col min="5" max="5" width="23.85546875" style="25" customWidth="1"/>
+    <col min="6" max="6" width="62.85546875" style="28" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="D1" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="E1" s="24" t="s">
+        <v>135</v>
+      </c>
+      <c r="F1" s="26" t="s">
+        <v>131</v>
+      </c>
+      <c r="G1" s="26" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="B2" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="D2" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="E2" s="25" t="s">
+        <v>136</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="D3" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="E3" s="25" t="s">
+        <v>137</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="G3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="D4" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="E4" s="25" t="s">
+        <v>136</v>
+      </c>
+      <c r="F4" s="27" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="D5" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="E5" s="25" t="s">
+        <v>137</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="G5" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>141</v>
+      </c>
+      <c r="D6" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="E6" s="25" t="s">
+        <v>136</v>
+      </c>
+      <c r="F6" s="28" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>141</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="E7" s="25" t="s">
+        <v>137</v>
+      </c>
+      <c r="F7" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="G7">
+        <v>0.316</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>141</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="E8" s="25" t="s">
+        <v>136</v>
+      </c>
+      <c r="F8" s="28" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>141</v>
+      </c>
+      <c r="D9" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="E9" s="25" t="s">
+        <v>137</v>
+      </c>
+      <c r="F9" s="28" t="s">
+        <v>53</v>
+      </c>
+      <c r="G9">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B10" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="16"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B11" s="15" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B12" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" s="16"/>
+      <c r="E12" s="25" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B13" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C13" s="16"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B14" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="C14" s="16"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B15" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="C15" s="16"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C16" s="16"/>
+    </row>
+    <row r="17" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C17" s="16"/>
+      <c r="D17" s="29" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B18" s="16"/>
+      <c r="C18" s="16"/>
+    </row>
+    <row r="19" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C19" s="16"/>
+    </row>
+    <row r="20" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B20" s="13"/>
+      <c r="C20" s="16"/>
+    </row>
+    <row r="21" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C21" s="16"/>
+    </row>
+    <row r="22" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C22" s="16"/>
+    </row>
+    <row r="23" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C23" s="16"/>
+    </row>
+    <row r="24" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C24" s="16"/>
+    </row>
+    <row r="25" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C25" s="16"/>
+    </row>
+    <row r="26" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C26" s="16"/>
+    </row>
+    <row r="27" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C27" s="16"/>
+    </row>
+    <row r="28" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C28" s="16"/>
+    </row>
+    <row r="29" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C29" s="16"/>
+    </row>
+    <row r="30" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C30" s="16"/>
+    </row>
+    <row r="31" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C31" s="16"/>
+    </row>
+    <row r="32" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C32" s="16"/>
+    </row>
+    <row r="33" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C33" s="16"/>
+    </row>
+    <row r="34" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C34" s="16"/>
+    </row>
+    <row r="35" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C35" s="16"/>
+    </row>
+    <row r="36" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C36" s="16"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:A9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2737,4 +3265,24 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80039399-BA6C-4D9A-804C-21A5BB782000}">
+  <dimension ref="A6:G8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G6" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>134</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/other/input/regulatory_limits/master_reg_limits.xlsx
+++ b/other/input/regulatory_limits/master_reg_limits.xlsx
@@ -3,17 +3,18 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26924"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{167C7E27-C7B2-463C-942C-01196AEFEF36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C3A15DA-CD30-480C-BC36-5F04729807E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29385" yWindow="-7080" windowWidth="26790" windowHeight="12690" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="120" yWindow="585" windowWidth="21600" windowHeight="14670" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="static_regulatory_values" sheetId="2" r:id="rId1"/>
-    <sheet name="ReadMe" sheetId="8" r:id="rId2"/>
-    <sheet name="Sheet1" sheetId="1" r:id="rId3"/>
-    <sheet name="calculated_regulatory_values" sheetId="4" r:id="rId4"/>
+    <sheet name="ReadMe" sheetId="8" r:id="rId1"/>
+    <sheet name="static_regulatory_values" sheetId="2" r:id="rId2"/>
+    <sheet name="calculated_regulatory_values" sheetId="4" r:id="rId3"/>
+    <sheet name="Sheet2" sheetId="9" r:id="rId4"/>
     <sheet name="pick_list" sheetId="3" r:id="rId5"/>
     <sheet name="questions" sheetId="6" r:id="rId6"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId7"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -59,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="490" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="147">
   <si>
     <t>alkalinity (as CaCO3)</t>
   </si>
@@ -488,6 +489,18 @@
   </si>
   <si>
     <t>--&gt; see pg 29 of adec criteria manual at https://dec.alaska.gov/water/water-quality/standards/</t>
+  </si>
+  <si>
+    <t>set up in dplyr read in way</t>
+  </si>
+  <si>
+    <t>Chromium III</t>
+  </si>
+  <si>
+    <t>Chr</t>
+  </si>
+  <si>
+    <t>all units in micrograms per liter (ug/L)</t>
   </si>
 </sst>
 </file>
@@ -497,7 +510,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -561,6 +574,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color indexed="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="7">
@@ -691,18 +710,21 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -982,6 +1004,26 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C524EC06-ADD2-401E-AE7E-9D4059DEE3B4}">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" ht="18" x14ac:dyDescent="0.25">
+      <c r="A3" s="29" t="s">
+        <v>146</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:O49"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
@@ -2025,22 +2067,824 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C524EC06-ADD2-401E-AE7E-9D4059DEE3B4}">
-  <dimension ref="A1"/>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31B77331-D835-4B41-9157-C8D156985AE1}">
+  <dimension ref="A1:H37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="9.140625" style="15"/>
+    <col min="2" max="2" width="26.140625" style="15" customWidth="1"/>
+    <col min="3" max="3" width="26.42578125" style="15" customWidth="1"/>
+    <col min="4" max="4" width="16.5703125" style="15" customWidth="1"/>
+    <col min="5" max="5" width="18" style="24" customWidth="1"/>
+    <col min="6" max="6" width="31.28515625" customWidth="1"/>
+    <col min="7" max="7" width="33.7109375" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>138</v>
-      </c>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="25" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" s="19" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A2" s="26" t="s">
+        <v>66</v>
+      </c>
+      <c r="B2" s="26" t="s">
+        <v>68</v>
+      </c>
+      <c r="C2" s="26" t="s">
+        <v>69</v>
+      </c>
+      <c r="D2" s="26" t="s">
+        <v>67</v>
+      </c>
+      <c r="E2" s="27" t="s">
+        <v>135</v>
+      </c>
+      <c r="F2" s="26" t="s">
+        <v>131</v>
+      </c>
+      <c r="G2" s="26" t="s">
+        <v>139</v>
+      </c>
+      <c r="H2" s="19" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="D3" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="E3" s="24" t="s">
+        <v>136</v>
+      </c>
+      <c r="F3" s="28" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="D4" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="E4" s="24" t="s">
+        <v>137</v>
+      </c>
+      <c r="F4" s="28" t="s">
+        <v>140</v>
+      </c>
+      <c r="G4" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="D5" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="E5" s="24" t="s">
+        <v>136</v>
+      </c>
+      <c r="F5" s="28" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="D6" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="E6" s="24" t="s">
+        <v>137</v>
+      </c>
+      <c r="F6" s="28" t="s">
+        <v>51</v>
+      </c>
+      <c r="G6" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>141</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="E7" s="24" t="s">
+        <v>136</v>
+      </c>
+      <c r="F7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>141</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="E8" s="24" t="s">
+        <v>137</v>
+      </c>
+      <c r="F8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G8">
+        <v>0.316</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>141</v>
+      </c>
+      <c r="D9" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="E9" s="24" t="s">
+        <v>136</v>
+      </c>
+      <c r="F9" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>141</v>
+      </c>
+      <c r="D10" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="E10" s="24" t="s">
+        <v>137</v>
+      </c>
+      <c r="F10" t="s">
+        <v>53</v>
+      </c>
+      <c r="G10">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="B11" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="D11" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="E11" s="24" t="s">
+        <v>136</v>
+      </c>
+      <c r="F11" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="B12" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="C12" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="D12" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="E12" s="24" t="s">
+        <v>137</v>
+      </c>
+      <c r="F12" t="s">
+        <v>38</v>
+      </c>
+      <c r="G12">
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="B13" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="D13" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="E13" s="24" t="s">
+        <v>136</v>
+      </c>
+      <c r="F13" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="B14" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="D14" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="E14" s="24" t="s">
+        <v>137</v>
+      </c>
+      <c r="F14" t="s">
+        <v>54</v>
+      </c>
+      <c r="G14">
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="B15" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C15" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="D15" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="E15" s="24" t="s">
+        <v>136</v>
+      </c>
+      <c r="F15" s="15" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="B16" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="D16" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="E16" s="24" t="s">
+        <v>137</v>
+      </c>
+      <c r="F16" t="s">
+        <v>40</v>
+      </c>
+      <c r="G16" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="B17" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C17" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="D17" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="E17" s="24" t="s">
+        <v>136</v>
+      </c>
+      <c r="F17" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="B18" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C18" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="D18" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="E18" s="24" t="s">
+        <v>137</v>
+      </c>
+      <c r="F18" t="s">
+        <v>57</v>
+      </c>
+      <c r="G18" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="B19" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="C19" s="16"/>
+      <c r="D19" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="E19" s="24" t="s">
+        <v>136</v>
+      </c>
+      <c r="F19" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="B20" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="C20" s="16"/>
+      <c r="D20" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="E20" s="24" t="s">
+        <v>137</v>
+      </c>
+      <c r="F20" t="s">
+        <v>41</v>
+      </c>
+      <c r="G20">
+        <v>0.998</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="B21" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="C21" s="16"/>
+      <c r="D21" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="E21" s="24" t="s">
+        <v>136</v>
+      </c>
+      <c r="F21" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="B22" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="C22" s="16"/>
+      <c r="D22" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="E22" s="24" t="s">
+        <v>137</v>
+      </c>
+      <c r="F22" t="s">
+        <v>58</v>
+      </c>
+      <c r="G22">
+        <v>0.997</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="B23" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C23" s="16"/>
+      <c r="D23" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="E23" s="24" t="s">
+        <v>136</v>
+      </c>
+      <c r="F23" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="B24" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C24" s="16"/>
+      <c r="D24" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="E24" s="24" t="s">
+        <v>137</v>
+      </c>
+      <c r="F24" t="s">
+        <v>42</v>
+      </c>
+      <c r="G24">
+        <v>0.92200000000000004</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="B25" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C25" s="16"/>
+      <c r="D25" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="E25" s="24" t="s">
+        <v>136</v>
+      </c>
+      <c r="F25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="B26" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C26" s="16"/>
+      <c r="D26" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="E26" s="24" t="s">
+        <v>137</v>
+      </c>
+      <c r="F26">
+        <v>5</v>
+      </c>
+      <c r="G26">
+        <v>0.92200000000000004</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="B27" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="C27" s="16"/>
+      <c r="D27" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="E27" s="24" t="s">
+        <v>136</v>
+      </c>
+      <c r="F27" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="B28" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="C28" s="16"/>
+      <c r="D28" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="E28" s="24" t="s">
+        <v>137</v>
+      </c>
+      <c r="F28" t="s">
+        <v>43</v>
+      </c>
+      <c r="G28">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="B29" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="C29" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="D29" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="E29" s="24" t="s">
+        <v>136</v>
+      </c>
+      <c r="F29" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="B30" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="C30" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="D30" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="E30" s="24" t="s">
+        <v>137</v>
+      </c>
+      <c r="F30" t="s">
+        <v>44</v>
+      </c>
+      <c r="G30">
+        <v>0.97799999999999998</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="B31" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="C31" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="D31" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="E31" s="24" t="s">
+        <v>136</v>
+      </c>
+      <c r="F31" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="B32" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="C32" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="D32" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="E32" s="24" t="s">
+        <v>137</v>
+      </c>
+      <c r="F32" t="s">
+        <v>44</v>
+      </c>
+      <c r="G32">
+        <v>0.98599999999999999</v>
+      </c>
+    </row>
+    <row r="33" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C33" s="16"/>
+    </row>
+    <row r="34" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C34" s="16"/>
+    </row>
+    <row r="35" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C35" s="16"/>
+    </row>
+    <row r="36" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C36" s="16"/>
+    </row>
+    <row r="37" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C37" s="16"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B8038DA-5443-4C6F-A4A9-CF8645419CF8}">
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="15.5703125" customWidth="1"/>
+    <col min="3" max="3" width="18.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="63" x14ac:dyDescent="0.25">
+      <c r="A1" s="26" t="s">
+        <v>66</v>
+      </c>
+      <c r="B1" s="26" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1" s="26" t="s">
+        <v>69</v>
+      </c>
+      <c r="D1" s="26" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>145</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:A9"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" s="12" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>119</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80039399-BA6C-4D9A-804C-21A5BB782000}">
+  <dimension ref="A6:G8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G6" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>134</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2891,398 +3735,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31B77331-D835-4B41-9157-C8D156985AE1}">
-  <dimension ref="A1:G36"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="9.140625" style="15"/>
-    <col min="2" max="2" width="26.140625" style="15" customWidth="1"/>
-    <col min="3" max="3" width="26.42578125" style="15" customWidth="1"/>
-    <col min="4" max="4" width="23.85546875" style="15" customWidth="1"/>
-    <col min="5" max="5" width="23.85546875" style="25" customWidth="1"/>
-    <col min="6" max="6" width="62.85546875" style="28" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="B1" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1" s="14" t="s">
-        <v>69</v>
-      </c>
-      <c r="D1" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="E1" s="24" t="s">
-        <v>135</v>
-      </c>
-      <c r="F1" s="26" t="s">
-        <v>131</v>
-      </c>
-      <c r="G1" s="26" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="B2" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="16" t="s">
-        <v>86</v>
-      </c>
-      <c r="D2" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="E2" s="25" t="s">
-        <v>136</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="B3" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="16" t="s">
-        <v>86</v>
-      </c>
-      <c r="D3" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="E3" s="25" t="s">
-        <v>137</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="G3" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="B4" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="16" t="s">
-        <v>86</v>
-      </c>
-      <c r="D4" s="15" t="s">
-        <v>74</v>
-      </c>
-      <c r="E4" s="25" t="s">
-        <v>136</v>
-      </c>
-      <c r="F4" s="27" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="B5" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="16" t="s">
-        <v>86</v>
-      </c>
-      <c r="D5" s="15" t="s">
-        <v>74</v>
-      </c>
-      <c r="E5" s="25" t="s">
-        <v>137</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="G5" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="B6" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="15" t="s">
-        <v>141</v>
-      </c>
-      <c r="D6" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="E6" s="25" t="s">
-        <v>136</v>
-      </c>
-      <c r="F6" s="28" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="B7" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="15" t="s">
-        <v>141</v>
-      </c>
-      <c r="D7" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="E7" s="25" t="s">
-        <v>137</v>
-      </c>
-      <c r="F7" s="28" t="s">
-        <v>37</v>
-      </c>
-      <c r="G7">
-        <v>0.316</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="B8" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" s="15" t="s">
-        <v>141</v>
-      </c>
-      <c r="D8" s="15" t="s">
-        <v>74</v>
-      </c>
-      <c r="E8" s="25" t="s">
-        <v>136</v>
-      </c>
-      <c r="F8" s="28" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="B9" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="C9" s="15" t="s">
-        <v>141</v>
-      </c>
-      <c r="D9" s="15" t="s">
-        <v>74</v>
-      </c>
-      <c r="E9" s="25" t="s">
-        <v>137</v>
-      </c>
-      <c r="F9" s="28" t="s">
-        <v>53</v>
-      </c>
-      <c r="G9">
-        <v>0.86</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B10" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10" s="16"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B11" s="15" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="C12" s="16"/>
-      <c r="E12" s="25" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B13" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="C13" s="16"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B14" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="C14" s="16"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B15" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="C15" s="16"/>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C16" s="16"/>
-    </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="C17" s="16"/>
-      <c r="D17" s="29" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B18" s="16"/>
-      <c r="C18" s="16"/>
-    </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="C19" s="16"/>
-    </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B20" s="13"/>
-      <c r="C20" s="16"/>
-    </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="C21" s="16"/>
-    </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="C22" s="16"/>
-    </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="C23" s="16"/>
-    </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="C24" s="16"/>
-    </row>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="C25" s="16"/>
-    </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="C26" s="16"/>
-    </row>
-    <row r="27" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="C27" s="16"/>
-    </row>
-    <row r="28" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="C28" s="16"/>
-    </row>
-    <row r="29" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="C29" s="16"/>
-    </row>
-    <row r="30" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="C30" s="16"/>
-    </row>
-    <row r="31" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="C31" s="16"/>
-    </row>
-    <row r="32" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="C32" s="16"/>
-    </row>
-    <row r="33" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C33" s="16"/>
-    </row>
-    <row r="34" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C34" s="16"/>
-    </row>
-    <row r="35" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C35" s="16"/>
-    </row>
-    <row r="36" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C36" s="16"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:A9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" s="12" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>119</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80039399-BA6C-4D9A-804C-21A5BB782000}">
-  <dimension ref="A6:G8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="G6" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>134</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/other/input/regulatory_limits/master_reg_limits.xlsx
+++ b/other/input/regulatory_limits/master_reg_limits.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26924"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C3A15DA-CD30-480C-BC36-5F04729807E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{3C3A15DA-CD30-480C-BC36-5F04729807E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A91C77E7-F620-43D1-A12F-2E293D2EBAA9}"/>
   <bookViews>
-    <workbookView xWindow="120" yWindow="585" windowWidth="21600" windowHeight="14670" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1320" yWindow="2775" windowWidth="26370" windowHeight="12705" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ReadMe" sheetId="8" r:id="rId1"/>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="615" uniqueCount="146">
   <si>
     <t>alkalinity (as CaCO3)</t>
   </si>
@@ -489,9 +489,6 @@
   </si>
   <si>
     <t>--&gt; see pg 29 of adec criteria manual at https://dec.alaska.gov/water/water-quality/standards/</t>
-  </si>
-  <si>
-    <t>set up in dplyr read in way</t>
   </si>
   <si>
     <t>Chromium III</t>
@@ -1015,7 +1012,7 @@
     </row>
     <row r="3" spans="1:1" ht="18" x14ac:dyDescent="0.25">
       <c r="A3" s="29" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
   </sheetData>
@@ -2069,7 +2066,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31B77331-D835-4B41-9157-C8D156985AE1}">
-  <dimension ref="A1:H37"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="15"/>
@@ -2081,12 +2078,12 @@
     <col min="7" max="7" width="33.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="25" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="2" spans="1:8" s="19" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" s="19" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A2" s="26" t="s">
         <v>66</v>
       </c>
@@ -2108,11 +2105,8 @@
       <c r="G2" s="26" t="s">
         <v>139</v>
       </c>
-      <c r="H2" s="19" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
         <v>73</v>
       </c>
@@ -2132,7 +2126,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="15" t="s">
         <v>73</v>
       </c>
@@ -2155,7 +2149,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="15" t="s">
         <v>73</v>
       </c>
@@ -2175,7 +2169,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="15" t="s">
         <v>73</v>
       </c>
@@ -2198,7 +2192,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="15" t="s">
         <v>73</v>
       </c>
@@ -2218,7 +2212,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="15" t="s">
         <v>73</v>
       </c>
@@ -2241,7 +2235,7 @@
         <v>0.316</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="15" t="s">
         <v>73</v>
       </c>
@@ -2261,7 +2255,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="15" t="s">
         <v>73</v>
       </c>
@@ -2284,7 +2278,7 @@
         <v>0.86</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="15" t="s">
         <v>73</v>
       </c>
@@ -2304,7 +2298,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="15" t="s">
         <v>73</v>
       </c>
@@ -2327,7 +2321,7 @@
         <v>0.96</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="15" t="s">
         <v>73</v>
       </c>
@@ -2347,7 +2341,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="15" t="s">
         <v>73</v>
       </c>
@@ -2370,7 +2364,7 @@
         <v>0.96</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="15" t="s">
         <v>73</v>
       </c>
@@ -2390,7 +2384,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="15" t="s">
         <v>73</v>
       </c>
@@ -2766,7 +2760,7 @@
     <col min="3" max="3" width="18.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="63" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A1" s="26" t="s">
         <v>66</v>
       </c>
@@ -2795,12 +2789,12 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
   </sheetData>

--- a/other/input/regulatory_limits/master_reg_limits.xlsx
+++ b/other/input/regulatory_limits/master_reg_limits.xlsx
@@ -3,23 +3,34 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26924"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{3C3A15DA-CD30-480C-BC36-5F04729807E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A91C77E7-F620-43D1-A12F-2E293D2EBAA9}"/>
+  <xr:revisionPtr revIDLastSave="109" documentId="13_ncr:1_{3C3A15DA-CD30-480C-BC36-5F04729807E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2126A698-32E5-4D40-A258-574FB9787024}"/>
   <bookViews>
-    <workbookView xWindow="1320" yWindow="2775" windowWidth="26370" windowHeight="12705" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-26490" yWindow="2565" windowWidth="26385" windowHeight="12120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ReadMe" sheetId="8" r:id="rId1"/>
     <sheet name="static_regulatory_values" sheetId="2" r:id="rId2"/>
     <sheet name="calculated_regulatory_values" sheetId="4" r:id="rId3"/>
-    <sheet name="Sheet2" sheetId="9" r:id="rId4"/>
+    <sheet name="diss_metals_hard_parameters" sheetId="9" r:id="rId4"/>
     <sheet name="pick_list" sheetId="3" r:id="rId5"/>
     <sheet name="questions" sheetId="6" r:id="rId6"/>
     <sheet name="Sheet1" sheetId="1" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -60,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="615" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="638" uniqueCount="158">
   <si>
     <t>alkalinity (as CaCO3)</t>
   </si>
@@ -494,10 +505,46 @@
     <t>Chromium III</t>
   </si>
   <si>
-    <t>Chr</t>
-  </si>
-  <si>
     <t>all units in micrograms per liter (ug/L)</t>
+  </si>
+  <si>
+    <t>m_a</t>
+  </si>
+  <si>
+    <t>b_a</t>
+  </si>
+  <si>
+    <t>m_c</t>
+  </si>
+  <si>
+    <t>b_c</t>
+  </si>
+  <si>
+    <t>fw_acute_convert</t>
+  </si>
+  <si>
+    <t>fw_chronic_convert</t>
+  </si>
+  <si>
+    <t>Chromium VI</t>
+  </si>
+  <si>
+    <t>[MERCURY]</t>
+  </si>
+  <si>
+    <t>[0.85]</t>
+  </si>
+  <si>
+    <t>1.46203 -[(ln hardness)(0.145712)]</t>
+  </si>
+  <si>
+    <t>1.136672-[(ln hardness) (0.041838)]</t>
+  </si>
+  <si>
+    <t>From page 29 of Alaska Water Quality Criteria Manual for Toxic and other Deleterious Organic and Inorganic Substances (page 29)</t>
+  </si>
+  <si>
+    <t>characteristic_name</t>
   </si>
 </sst>
 </file>
@@ -737,6 +784,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1012,7 +1063,7 @@
     </row>
     <row r="3" spans="1:1" ht="18" x14ac:dyDescent="0.25">
       <c r="A3" s="29" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
   </sheetData>
@@ -2753,48 +2804,250 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B8038DA-5443-4C6F-A4A9-CF8645419CF8}">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="15.5703125" customWidth="1"/>
-    <col min="3" max="3" width="18.28515625" customWidth="1"/>
+    <col min="1" max="2" width="13.28515625" customWidth="1"/>
+    <col min="3" max="3" width="15.5703125" customWidth="1"/>
+    <col min="4" max="4" width="18.28515625" customWidth="1"/>
+    <col min="7" max="7" width="22.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="26" t="s">
-        <v>66</v>
-      </c>
-      <c r="B1" s="26" t="s">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" s="12" customFormat="1" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A2" s="26" t="s">
         <v>68</v>
       </c>
-      <c r="C1" s="26" t="s">
-        <v>69</v>
-      </c>
-      <c r="D1" s="26" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>73</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="B2" s="26" t="s">
+        <v>157</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="E2" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="F2" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="G2" s="26" t="s">
+        <v>149</v>
+      </c>
+      <c r="H2" s="26" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
+        <v>82</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C4">
+        <v>1.0165999999999999</v>
+      </c>
+      <c r="D4">
+        <v>-3.9239999999999999</v>
+      </c>
+      <c r="E4">
+        <v>0.7409</v>
+      </c>
+      <c r="F4">
+        <v>-4.7190000000000003</v>
+      </c>
+      <c r="G4" s="19" t="s">
+        <v>155</v>
+      </c>
+      <c r="H4" t="s">
+        <v>52</v>
+      </c>
+      <c r="L4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>144</v>
+        <v>70</v>
+      </c>
+      <c r="C5">
+        <v>0.81899999999999995</v>
+      </c>
+      <c r="D5">
+        <v>3.7256</v>
+      </c>
+      <c r="E5">
+        <v>0.81899999999999995</v>
+      </c>
+      <c r="F5">
+        <v>0.68479999999999996</v>
+      </c>
+      <c r="G5">
+        <v>0.316</v>
+      </c>
+      <c r="H5">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>151</v>
+      </c>
+      <c r="G6">
+        <v>0.98199999999999998</v>
+      </c>
+      <c r="H6">
+        <v>0.96199999999999997</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>88</v>
+      </c>
+      <c r="B7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C7">
+        <v>0.94220000000000004</v>
+      </c>
+      <c r="D7">
+        <v>-1.7</v>
+      </c>
+      <c r="E7">
+        <v>0.85450000000000004</v>
+      </c>
+      <c r="F7">
+        <v>-1.702</v>
+      </c>
+      <c r="G7">
+        <v>0.96</v>
+      </c>
+      <c r="H7">
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>92</v>
+      </c>
+      <c r="B8" t="s">
+        <v>92</v>
+      </c>
+      <c r="C8">
+        <v>1.2729999999999999</v>
+      </c>
+      <c r="D8">
+        <v>-1.46</v>
+      </c>
+      <c r="E8">
+        <v>1.2729999999999999</v>
+      </c>
+      <c r="F8">
+        <v>-4.7050000000000001</v>
+      </c>
+      <c r="G8" t="s">
+        <v>154</v>
+      </c>
+      <c r="H8" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>152</v>
+      </c>
+      <c r="G9" t="s">
+        <v>153</v>
+      </c>
+      <c r="H9" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>94</v>
+      </c>
+      <c r="C10">
+        <v>0.84599999999999997</v>
+      </c>
+      <c r="D10">
+        <v>2.2549999999999999</v>
+      </c>
+      <c r="E10">
+        <v>0.84599999999999997</v>
+      </c>
+      <c r="F10">
+        <v>5.8400000000000001E-2</v>
+      </c>
+      <c r="G10">
+        <v>0.998</v>
+      </c>
+      <c r="H10">
+        <v>0.997</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>101</v>
+      </c>
+      <c r="C11">
+        <v>1.72</v>
+      </c>
+      <c r="D11">
+        <v>-6.59</v>
+      </c>
+      <c r="G11">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>112</v>
+      </c>
+      <c r="B12" t="s">
+        <v>112</v>
+      </c>
+      <c r="C12">
+        <v>0.84730000000000005</v>
+      </c>
+      <c r="D12">
+        <v>0.88400000000000001</v>
+      </c>
+      <c r="E12">
+        <v>0.84730000000000005</v>
+      </c>
+      <c r="F12">
+        <v>0.88400000000000001</v>
+      </c>
+      <c r="G12">
+        <v>0.97799999999999998</v>
+      </c>
+      <c r="H12">
+        <v>0.98599999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/other/input/regulatory_limits/master_reg_limits.xlsx
+++ b/other/input/regulatory_limits/master_reg_limits.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26924"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="109" documentId="13_ncr:1_{3C3A15DA-CD30-480C-BC36-5F04729807E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2126A698-32E5-4D40-A258-574FB9787024}"/>
+  <xr:revisionPtr revIDLastSave="111" documentId="13_ncr:1_{3C3A15DA-CD30-480C-BC36-5F04729807E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{142A8BEA-A097-4E17-B4C7-15753667DA4C}"/>
   <bookViews>
-    <workbookView xWindow="-26490" yWindow="2565" windowWidth="26385" windowHeight="12120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2730" yWindow="1305" windowWidth="21600" windowHeight="12720" tabRatio="795" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ReadMe" sheetId="8" r:id="rId1"/>
@@ -71,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="638" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="640" uniqueCount="158">
   <si>
     <t>alkalinity (as CaCO3)</t>
   </si>
@@ -2991,6 +2991,9 @@
       <c r="A10" t="s">
         <v>94</v>
       </c>
+      <c r="B10" t="s">
+        <v>94</v>
+      </c>
       <c r="C10">
         <v>0.84599999999999997</v>
       </c>
@@ -3012,6 +3015,9 @@
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>101</v>
+      </c>
+      <c r="B11" t="s">
         <v>101</v>
       </c>
       <c r="C11">

--- a/other/input/regulatory_limits/master_reg_limits.xlsx
+++ b/other/input/regulatory_limits/master_reg_limits.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26924"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="111" documentId="13_ncr:1_{3C3A15DA-CD30-480C-BC36-5F04729807E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{142A8BEA-A097-4E17-B4C7-15753667DA4C}"/>
+  <xr:revisionPtr revIDLastSave="158" documentId="13_ncr:1_{3C3A15DA-CD30-480C-BC36-5F04729807E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CA0EADAD-E491-4387-B693-5E38B4989DD4}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="1305" windowWidth="21600" windowHeight="12720" tabRatio="795" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-26805" yWindow="1425" windowWidth="21600" windowHeight="11295" tabRatio="795" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ReadMe" sheetId="8" r:id="rId1"/>
@@ -71,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="640" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="657" uniqueCount="168">
   <si>
     <t>alkalinity (as CaCO3)</t>
   </si>
@@ -545,6 +545,38 @@
   </si>
   <si>
     <t>characteristic_name</t>
+  </si>
+  <si>
+    <t>BTEX</t>
+  </si>
+  <si>
+    <t>aquaculture</t>
+  </si>
+  <si>
+    <t>18 AAC 70</t>
+  </si>
+  <si>
+    <t>BM 20231129</t>
+  </si>
+  <si>
+    <t>https://www.epa.gov/system/files/documents/2023-05/akwqs-chapter70-2023.pdf</t>
+  </si>
+  <si>
+    <t>Benzene, toluene, ethyl benzene, xylenes mix</t>
+  </si>
+  <si>
+    <t>No general standard, but see 18 AAC 70.236(b)
+WATERSHED, Anchorage WWTP, 1.9 μg/l (acute)
+measured as dissolved metal</t>
+  </si>
+  <si>
+    <t>part of BTEX</t>
+  </si>
+  <si>
+    <t>https://dec.alaska.gov/media/q5njdzbc/alaska-water-quality-criteria-manual-for-toxic-and-other-deleterious-organic-and-inorganic-substances-2022.pdf</t>
+  </si>
+  <si>
+    <t>Total Nitrate and Nitrite (as nitrogen)</t>
   </si>
 </sst>
 </file>
@@ -554,7 +586,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -625,6 +657,11 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -691,7 +728,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -769,6 +806,10 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -784,10 +825,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1073,7 +1110,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:O49"/>
+  <dimension ref="A1:O50"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="15"/>
@@ -1084,7 +1121,8 @@
     <col min="6" max="6" width="15.5703125" style="15" customWidth="1"/>
     <col min="7" max="7" width="9.140625" style="15"/>
     <col min="8" max="9" width="26.5703125" style="15" customWidth="1"/>
-    <col min="10" max="16384" width="9.140625" style="15"/>
+    <col min="10" max="10" width="17.42578125" style="15" customWidth="1"/>
+    <col min="11" max="16384" width="9.140625" style="15"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" s="14" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
@@ -1449,26 +1487,29 @@
       <c r="A15" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="B15" s="15" t="s">
-        <v>7</v>
+      <c r="B15" s="30" t="s">
+        <v>163</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>86</v>
+        <v>158</v>
       </c>
       <c r="D15" s="15" t="s">
-        <v>115</v>
+        <v>159</v>
       </c>
       <c r="F15" s="15">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G15" s="15" t="s">
         <v>124</v>
       </c>
       <c r="H15" s="15" t="s">
-        <v>80</v>
+        <v>160</v>
+      </c>
+      <c r="I15" s="15" t="s">
+        <v>162</v>
       </c>
       <c r="J15" s="15" t="s">
-        <v>120</v>
+        <v>161</v>
       </c>
     </row>
     <row r="16" spans="1:15" ht="14.25" x14ac:dyDescent="0.2">
@@ -1482,10 +1523,10 @@
         <v>86</v>
       </c>
       <c r="D16" s="15" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="F16" s="15">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G16" s="15" t="s">
         <v>124</v>
@@ -1508,7 +1549,7 @@
         <v>86</v>
       </c>
       <c r="D17" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F17" s="15">
         <v>10</v>
@@ -1523,21 +1564,21 @@
         <v>120</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A18" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="B18" s="13" t="s">
+      <c r="B18" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="D18" s="15" t="s">
+        <v>119</v>
+      </c>
+      <c r="F18" s="15">
         <v>10</v>
-      </c>
-      <c r="C18" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="D18" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="F18" s="15">
-        <v>100</v>
       </c>
       <c r="G18" s="15" t="s">
         <v>124</v>
@@ -1545,9 +1586,6 @@
       <c r="H18" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="I18" s="15" t="s">
-        <v>125</v>
-      </c>
       <c r="J18" s="15" t="s">
         <v>120</v>
       </c>
@@ -1563,7 +1601,7 @@
         <v>70</v>
       </c>
       <c r="D19" s="15" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="F19" s="15">
         <v>100</v>
@@ -1574,25 +1612,28 @@
       <c r="H19" s="15" t="s">
         <v>80</v>
       </c>
+      <c r="I19" s="15" t="s">
+        <v>125</v>
+      </c>
       <c r="J19" s="15" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A20" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="B20" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="C20" s="16" t="s">
-        <v>87</v>
+      <c r="B20" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C20" s="15" t="s">
+        <v>70</v>
       </c>
       <c r="D20" s="15" t="s">
         <v>119</v>
       </c>
       <c r="F20" s="15">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="G20" s="15" t="s">
         <v>124</v>
@@ -1609,16 +1650,16 @@
         <v>73</v>
       </c>
       <c r="B21" s="15" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C21" s="16" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D21" s="15" t="s">
         <v>119</v>
       </c>
       <c r="F21" s="15">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="G21" s="15" t="s">
         <v>124</v>
@@ -1631,8 +1672,26 @@
       </c>
     </row>
     <row r="22" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A22" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="B22" s="15" t="s">
+        <v>14</v>
+      </c>
       <c r="C22" s="16" t="s">
-        <v>89</v>
+        <v>88</v>
+      </c>
+      <c r="D22" s="15" t="s">
+        <v>119</v>
+      </c>
+      <c r="F22" s="15">
+        <v>200</v>
+      </c>
+      <c r="G22" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="H22" s="15" t="s">
+        <v>80</v>
       </c>
       <c r="J22" s="15" t="s">
         <v>120</v>
@@ -1640,53 +1699,35 @@
     </row>
     <row r="23" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C23" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="J23" s="15" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="C24" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="J23" s="15" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A24" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="B24" s="15" t="s">
+      <c r="J24" s="15" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A25" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="B25" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="C24" s="15" t="s">
+      <c r="C25" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="D24" s="15" t="s">
+      <c r="D25" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="F24" s="15">
+      <c r="F25" s="15">
         <v>5000</v>
-      </c>
-      <c r="G24" s="15" t="s">
-        <v>124</v>
-      </c>
-      <c r="H24" s="15" t="s">
-        <v>80</v>
-      </c>
-      <c r="J24" s="15" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A25" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="B25" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="C25" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="D25" s="15" t="s">
-        <v>118</v>
-      </c>
-      <c r="F25" s="15">
-        <v>50</v>
       </c>
       <c r="G25" s="15" t="s">
         <v>124</v>
@@ -1709,13 +1750,10 @@
         <v>92</v>
       </c>
       <c r="D26" s="15" t="s">
-        <v>119</v>
-      </c>
-      <c r="E26" s="15" t="s">
-        <v>33</v>
+        <v>118</v>
       </c>
       <c r="F26" s="15">
-        <v>5000</v>
+        <v>50</v>
       </c>
       <c r="G26" s="15" t="s">
         <v>124</v>
@@ -1732,16 +1770,19 @@
         <v>73</v>
       </c>
       <c r="B27" s="15" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C27" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D27" s="15" t="s">
         <v>119</v>
       </c>
+      <c r="E27" s="15" t="s">
+        <v>33</v>
+      </c>
       <c r="F27" s="15">
-        <v>10</v>
+        <v>5000</v>
       </c>
       <c r="G27" s="15" t="s">
         <v>124</v>
@@ -1758,16 +1799,16 @@
         <v>73</v>
       </c>
       <c r="B28" s="15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C28" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D28" s="15" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="F28" s="15">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="G28" s="15" t="s">
         <v>124</v>
@@ -1790,10 +1831,10 @@
         <v>94</v>
       </c>
       <c r="D29" s="15" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="F29" s="15">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G29" s="15" t="s">
         <v>124</v>
@@ -1810,10 +1851,22 @@
         <v>73</v>
       </c>
       <c r="B30" s="15" t="s">
-        <v>126</v>
+        <v>24</v>
       </c>
       <c r="C30" s="16" t="s">
-        <v>95</v>
+        <v>94</v>
+      </c>
+      <c r="D30" s="15" t="s">
+        <v>119</v>
+      </c>
+      <c r="F30" s="15">
+        <v>200</v>
+      </c>
+      <c r="G30" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="H30" s="15" t="s">
+        <v>80</v>
       </c>
       <c r="J30" s="15" t="s">
         <v>120</v>
@@ -1823,11 +1876,11 @@
       <c r="A31" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="B31" s="16" t="s">
-        <v>96</v>
+      <c r="B31" s="15" t="s">
+        <v>126</v>
       </c>
       <c r="C31" s="16" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J31" s="15" t="s">
         <v>120</v>
@@ -1837,11 +1890,11 @@
       <c r="A32" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="B32" s="15" t="s">
-        <v>127</v>
+      <c r="B32" s="16" t="s">
+        <v>96</v>
       </c>
       <c r="C32" s="16" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J32" s="15" t="s">
         <v>120</v>
@@ -1851,11 +1904,11 @@
       <c r="A33" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="B33" s="13" t="s">
-        <v>128</v>
+      <c r="B33" s="15" t="s">
+        <v>127</v>
       </c>
       <c r="C33" s="16" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="J33" s="15" t="s">
         <v>120</v>
@@ -1865,23 +1918,11 @@
       <c r="A34" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="B34" s="15" t="s">
-        <v>28</v>
+      <c r="B34" s="13" t="s">
+        <v>128</v>
       </c>
       <c r="C34" s="16" t="s">
-        <v>99</v>
-      </c>
-      <c r="D34" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="F34" s="15">
-        <v>50</v>
-      </c>
-      <c r="G34" s="15" t="s">
-        <v>124</v>
-      </c>
-      <c r="H34" s="15" t="s">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="J34" s="15" t="s">
         <v>120</v>
@@ -1898,10 +1939,10 @@
         <v>99</v>
       </c>
       <c r="D35" s="15" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="F35" s="15">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="G35" s="15" t="s">
         <v>124</v>
@@ -1924,10 +1965,10 @@
         <v>99</v>
       </c>
       <c r="D36" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F36" s="15">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G36" s="15" t="s">
         <v>124</v>
@@ -1940,8 +1981,26 @@
       </c>
     </row>
     <row r="37" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A37" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="B37" s="15" t="s">
+        <v>28</v>
+      </c>
       <c r="C37" s="16" t="s">
-        <v>100</v>
+        <v>99</v>
+      </c>
+      <c r="D37" s="15" t="s">
+        <v>119</v>
+      </c>
+      <c r="F37" s="15">
+        <v>20</v>
+      </c>
+      <c r="G37" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="H37" s="15" t="s">
+        <v>80</v>
       </c>
       <c r="J37" s="15" t="s">
         <v>120</v>
@@ -1949,49 +2008,55 @@
     </row>
     <row r="38" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C38" s="16" t="s">
+        <v>100</v>
+      </c>
+      <c r="J38" s="15" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" ht="63.75" x14ac:dyDescent="0.2">
+      <c r="A39" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C39" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="J38" s="15" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="C39" s="16" t="s">
+      <c r="I39" s="31" t="s">
+        <v>164</v>
+      </c>
+      <c r="J39" s="15" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="C40" s="16" t="s">
         <v>102</v>
       </c>
-      <c r="J39" s="15" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A40" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="B40" s="15" t="s">
+      <c r="J40" s="15" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A41" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="B41" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="C40" s="16" t="s">
+      <c r="C41" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="D40" s="15" t="s">
+      <c r="D41" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="F40" s="15">
+      <c r="F41" s="15">
         <v>2</v>
       </c>
-      <c r="G40" s="15" t="s">
+      <c r="G41" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="H40" s="15" t="s">
+      <c r="H41" s="15" t="s">
         <v>80</v>
-      </c>
-      <c r="J40" s="15" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="C41" s="16" t="s">
-        <v>104</v>
       </c>
       <c r="J41" s="15" t="s">
         <v>120</v>
@@ -1999,7 +2064,7 @@
     </row>
     <row r="42" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C42" s="16" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J42" s="15" t="s">
         <v>120</v>
@@ -2007,7 +2072,7 @@
     </row>
     <row r="43" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C43" s="16" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="J43" s="15" t="s">
         <v>120</v>
@@ -2015,103 +2080,120 @@
     </row>
     <row r="44" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C44" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="I44" s="15" t="s">
+        <v>165</v>
+      </c>
+      <c r="J44" s="15" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A45" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="B45" s="15" t="s">
+        <v>167</v>
+      </c>
+      <c r="C45" s="16" t="s">
         <v>107</v>
       </c>
-      <c r="J44" s="15" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="C45" s="16" t="s">
-        <v>108</v>
+      <c r="D45" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="F45" s="15">
+        <v>10000</v>
+      </c>
+      <c r="G45" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="H45" s="15" t="s">
+        <v>166</v>
       </c>
       <c r="J45" s="15" t="s">
-        <v>120</v>
+        <v>161</v>
       </c>
     </row>
     <row r="46" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C46" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="J46" s="15" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="C47" s="16" t="s">
         <v>109</v>
       </c>
-      <c r="J46" s="15" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A47" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="B47" s="15" t="s">
+      <c r="J47" s="15" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A48" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="B48" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="C47" s="16" t="s">
+      <c r="C48" s="16" t="s">
         <v>110</v>
       </c>
-      <c r="D47" s="15" t="s">
+      <c r="D48" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="F47" s="15">
+      <c r="F48" s="15">
         <v>100</v>
       </c>
-      <c r="G47" s="15" t="s">
+      <c r="G48" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="H47" s="15" t="s">
+      <c r="H48" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="J47" s="15" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="C48" s="16" t="s">
+      <c r="J48" s="15" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="C49" s="16" t="s">
         <v>111</v>
       </c>
-      <c r="J48" s="15" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A49" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="B49" s="15" t="s">
+      <c r="J49" s="15" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A50" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="B50" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="C49" s="16" t="s">
+      <c r="C50" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="D49" s="15" t="s">
+      <c r="D50" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="F49" s="15">
+      <c r="F50" s="15">
         <v>2000</v>
       </c>
-      <c r="G49" s="15" t="s">
+      <c r="G50" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="H49" s="15" t="s">
+      <c r="H50" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="J49" s="15" t="s">
+      <c r="J50" s="15" t="s">
         <v>120</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" showDropDown="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000000000000}">
-          <x14:formula1>
-            <xm:f>pick_list!$A$2:$A$9</xm:f>
-          </x14:formula1>
-          <xm:sqref>D24:D1048576 D1:D22</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3064,7 +3146,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:A9"/>
+  <dimension ref="A1:A10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
@@ -3110,6 +3192,11 @@
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>119</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>159</v>
       </c>
     </row>
   </sheetData>

--- a/other/input/regulatory_limits/master_reg_limits.xlsx
+++ b/other/input/regulatory_limits/master_reg_limits.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26924"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28129"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="158" documentId="13_ncr:1_{3C3A15DA-CD30-480C-BC36-5F04729807E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CA0EADAD-E491-4387-B693-5E38B4989DD4}"/>
+  <xr:revisionPtr revIDLastSave="201" documentId="13_ncr:1_{3C3A15DA-CD30-480C-BC36-5F04729807E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{237E512B-E0FD-4A1C-A15D-AC096E426421}"/>
   <bookViews>
-    <workbookView xWindow="-26805" yWindow="1425" windowWidth="21600" windowHeight="11295" tabRatio="795" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="34500" yWindow="-2175" windowWidth="21420" windowHeight="13920" tabRatio="795" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ReadMe" sheetId="8" r:id="rId1"/>
@@ -71,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="657" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="668" uniqueCount="172">
   <si>
     <t>alkalinity (as CaCO3)</t>
   </si>
@@ -573,10 +573,22 @@
     <t>part of BTEX</t>
   </si>
   <si>
-    <t>https://dec.alaska.gov/media/q5njdzbc/alaska-water-quality-criteria-manual-for-toxic-and-other-deleterious-organic-and-inorganic-substances-2022.pdf</t>
-  </si>
-  <si>
     <t>Total Nitrate and Nitrite (as nitrogen)</t>
+  </si>
+  <si>
+    <t>pH</t>
+  </si>
+  <si>
+    <t>drinking_water_minimum</t>
+  </si>
+  <si>
+    <t>drinking_water_maximum</t>
+  </si>
+  <si>
+    <t>18 AAC 70 Water Quality Standards April 26, 2024</t>
+  </si>
+  <si>
+    <t>https://dec.alaska.gov/media/eovgrgs5/18-aac-70.pdf</t>
   </si>
 </sst>
 </file>
@@ -586,7 +598,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -662,6 +674,14 @@
       <name val="Segoe UI"/>
       <family val="2"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -725,10 +745,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -810,8 +831,10 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -825,6 +848,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1110,12 +1137,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:O50"/>
+  <dimension ref="A1:O63"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="15"/>
     <col min="2" max="2" width="26.140625" style="15" customWidth="1"/>
-    <col min="3" max="3" width="26.42578125" style="15" customWidth="1"/>
+    <col min="3" max="3" width="38.42578125" style="15" customWidth="1"/>
     <col min="4" max="4" width="23.85546875" style="15" customWidth="1"/>
     <col min="5" max="5" width="16.7109375" style="15" customWidth="1"/>
     <col min="6" max="6" width="15.5703125" style="15" customWidth="1"/>
@@ -2089,12 +2116,12 @@
         <v>120</v>
       </c>
     </row>
-    <row r="45" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:10" ht="15" x14ac:dyDescent="0.25">
       <c r="A45" s="15" t="s">
         <v>73</v>
       </c>
       <c r="B45" s="15" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C45" s="16" t="s">
         <v>107</v>
@@ -2108,8 +2135,8 @@
       <c r="G45" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="H45" s="15" t="s">
-        <v>166</v>
+      <c r="H45" s="32" t="s">
+        <v>170</v>
       </c>
       <c r="J45" s="15" t="s">
         <v>161</v>
@@ -2191,9 +2218,57 @@
         <v>120</v>
       </c>
     </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A52" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="B52" s="15" t="s">
+        <v>167</v>
+      </c>
+      <c r="C52" s="15" t="s">
+        <v>167</v>
+      </c>
+      <c r="D52" s="15" t="s">
+        <v>168</v>
+      </c>
+      <c r="F52" s="15">
+        <v>6</v>
+      </c>
+      <c r="H52" s="15" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A53" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="B53" s="15" t="s">
+        <v>167</v>
+      </c>
+      <c r="C53" s="15" t="s">
+        <v>167</v>
+      </c>
+      <c r="D53" s="15" t="s">
+        <v>169</v>
+      </c>
+      <c r="F53" s="15">
+        <v>8.5</v>
+      </c>
+      <c r="H53" s="15" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="H63" s="15" t="s">
+        <v>33</v>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="H45" r:id="rId1" xr:uid="{CCC25BD0-B084-4035-97DA-BBC7C0D198E2}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>
 

--- a/other/input/regulatory_limits/master_reg_limits.xlsx
+++ b/other/input/regulatory_limits/master_reg_limits.xlsx
@@ -1,11 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28129"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="201" documentId="13_ncr:1_{3C3A15DA-CD30-480C-BC36-5F04729807E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{237E512B-E0FD-4A1C-A15D-AC096E426421}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="34500" yWindow="-2175" windowWidth="21420" windowHeight="13920" tabRatio="795" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="34500" yWindow="-2172" windowWidth="21420" windowHeight="13920" tabRatio="795" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="ReadMe" sheetId="8" r:id="rId1"/>
@@ -16,7 +15,7 @@
     <sheet name="questions" sheetId="6" r:id="rId6"/>
     <sheet name="Sheet1" sheetId="1" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -37,12 +36,12 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Author</author>
   </authors>
   <commentList>
-    <comment ref="I16" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="I16" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -579,22 +578,22 @@
     <t>pH</t>
   </si>
   <si>
-    <t>drinking_water_minimum</t>
-  </si>
-  <si>
-    <t>drinking_water_maximum</t>
-  </si>
-  <si>
     <t>18 AAC 70 Water Quality Standards April 26, 2024</t>
   </si>
   <si>
     <t>https://dec.alaska.gov/media/eovgrgs5/18-aac-70.pdf</t>
+  </si>
+  <si>
+    <t>aquaculture_minimum</t>
+  </si>
+  <si>
+    <t>aquaculture_maximum</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
@@ -1116,16 +1115,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C524EC06-ADD2-401E-AE7E-9D4059DEE3B4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="3" spans="1:1" ht="18" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A3" s="29" t="s">
         <v>144</v>
       </c>
@@ -1136,23 +1135,23 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:O63"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="15"/>
-    <col min="2" max="2" width="26.140625" style="15" customWidth="1"/>
-    <col min="3" max="3" width="38.42578125" style="15" customWidth="1"/>
-    <col min="4" max="4" width="23.85546875" style="15" customWidth="1"/>
-    <col min="5" max="5" width="16.7109375" style="15" customWidth="1"/>
-    <col min="6" max="6" width="15.5703125" style="15" customWidth="1"/>
-    <col min="7" max="7" width="9.140625" style="15"/>
-    <col min="8" max="9" width="26.5703125" style="15" customWidth="1"/>
-    <col min="10" max="10" width="17.42578125" style="15" customWidth="1"/>
-    <col min="11" max="16384" width="9.140625" style="15"/>
+    <col min="1" max="1" width="9.109375" style="15"/>
+    <col min="2" max="2" width="26.109375" style="15" customWidth="1"/>
+    <col min="3" max="3" width="38.44140625" style="15" customWidth="1"/>
+    <col min="4" max="4" width="23.88671875" style="15" customWidth="1"/>
+    <col min="5" max="5" width="16.6640625" style="15" customWidth="1"/>
+    <col min="6" max="6" width="15.5546875" style="15" customWidth="1"/>
+    <col min="7" max="7" width="9.109375" style="15"/>
+    <col min="8" max="9" width="26.5546875" style="15" customWidth="1"/>
+    <col min="10" max="10" width="17.44140625" style="15" customWidth="1"/>
+    <col min="11" max="16384" width="9.109375" style="15"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="14" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" s="14" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="14" t="s">
         <v>66</v>
       </c>
@@ -1184,7 +1183,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:15" ht="15" x14ac:dyDescent="0.3">
       <c r="A2" s="15" t="s">
         <v>73</v>
       </c>
@@ -1210,7 +1209,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:15" ht="15" x14ac:dyDescent="0.3">
       <c r="A3" s="15" t="s">
         <v>73</v>
       </c>
@@ -1239,7 +1238,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:15" ht="15" x14ac:dyDescent="0.3">
       <c r="A4" s="15" t="s">
         <v>73</v>
       </c>
@@ -1265,7 +1264,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" ht="15" x14ac:dyDescent="0.3">
       <c r="A5" s="15" t="s">
         <v>73</v>
       </c>
@@ -1291,7 +1290,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" ht="15" x14ac:dyDescent="0.3">
       <c r="A6" s="15" t="s">
         <v>73</v>
       </c>
@@ -1317,7 +1316,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" ht="15" x14ac:dyDescent="0.3">
       <c r="A7" s="15" t="s">
         <v>73</v>
       </c>
@@ -1343,7 +1342,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15" ht="15" x14ac:dyDescent="0.3">
       <c r="A8" s="15" t="s">
         <v>73</v>
       </c>
@@ -1369,7 +1368,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:15" ht="15" x14ac:dyDescent="0.3">
       <c r="A9" s="15" t="s">
         <v>73</v>
       </c>
@@ -1395,7 +1394,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:15" ht="15" x14ac:dyDescent="0.3">
       <c r="A10" s="15" t="s">
         <v>73</v>
       </c>
@@ -1421,7 +1420,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:15" ht="15" x14ac:dyDescent="0.3">
       <c r="C11" s="16" t="s">
         <v>84</v>
       </c>
@@ -1429,7 +1428,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:15" ht="15" x14ac:dyDescent="0.3">
       <c r="A12" s="15" t="s">
         <v>73</v>
       </c>
@@ -1458,7 +1457,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="13" spans="1:15" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:15" ht="15" x14ac:dyDescent="0.3">
       <c r="A13" s="15" t="s">
         <v>73</v>
       </c>
@@ -1484,7 +1483,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="14" spans="1:15" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:15" ht="15" x14ac:dyDescent="0.3">
       <c r="A14" s="15" t="s">
         <v>73</v>
       </c>
@@ -1510,7 +1509,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="15" spans="1:15" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:15" ht="15" x14ac:dyDescent="0.3">
       <c r="A15" s="15" t="s">
         <v>73</v>
       </c>
@@ -1539,7 +1538,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="16" spans="1:15" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:15" ht="15" x14ac:dyDescent="0.3">
       <c r="A16" s="15" t="s">
         <v>73</v>
       </c>
@@ -1565,7 +1564,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:10" ht="15" x14ac:dyDescent="0.3">
       <c r="A17" s="15" t="s">
         <v>73</v>
       </c>
@@ -1591,7 +1590,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:10" ht="15" x14ac:dyDescent="0.3">
       <c r="A18" s="15" t="s">
         <v>73</v>
       </c>
@@ -1617,7 +1616,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" s="15" t="s">
         <v>73</v>
       </c>
@@ -1646,7 +1645,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" s="15" t="s">
         <v>73</v>
       </c>
@@ -1672,7 +1671,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:10" ht="15" x14ac:dyDescent="0.3">
       <c r="A21" s="15" t="s">
         <v>73</v>
       </c>
@@ -1698,7 +1697,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:10" ht="15" x14ac:dyDescent="0.3">
       <c r="A22" s="15" t="s">
         <v>73</v>
       </c>
@@ -1724,7 +1723,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:10" ht="15" x14ac:dyDescent="0.3">
       <c r="C23" s="16" t="s">
         <v>89</v>
       </c>
@@ -1732,7 +1731,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:10" ht="15" x14ac:dyDescent="0.3">
       <c r="C24" s="16" t="s">
         <v>90</v>
       </c>
@@ -1740,7 +1739,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="15" t="s">
         <v>73</v>
       </c>
@@ -1766,7 +1765,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="26" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:10" ht="15" x14ac:dyDescent="0.3">
       <c r="A26" s="15" t="s">
         <v>73</v>
       </c>
@@ -1792,7 +1791,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="27" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:10" ht="15" x14ac:dyDescent="0.3">
       <c r="A27" s="15" t="s">
         <v>73</v>
       </c>
@@ -1821,7 +1820,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="28" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:10" ht="15" x14ac:dyDescent="0.3">
       <c r="A28" s="15" t="s">
         <v>73</v>
       </c>
@@ -1847,7 +1846,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="29" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:10" ht="15" x14ac:dyDescent="0.3">
       <c r="A29" s="15" t="s">
         <v>73</v>
       </c>
@@ -1873,7 +1872,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="30" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:10" ht="15" x14ac:dyDescent="0.3">
       <c r="A30" s="15" t="s">
         <v>73</v>
       </c>
@@ -1899,7 +1898,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="31" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:10" ht="15" x14ac:dyDescent="0.3">
       <c r="A31" s="15" t="s">
         <v>73</v>
       </c>
@@ -1913,7 +1912,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="32" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:10" ht="15" x14ac:dyDescent="0.3">
       <c r="A32" s="15" t="s">
         <v>73</v>
       </c>
@@ -1927,7 +1926,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="33" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:10" ht="15" x14ac:dyDescent="0.3">
       <c r="A33" s="15" t="s">
         <v>73</v>
       </c>
@@ -1941,7 +1940,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="34" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:10" ht="15" x14ac:dyDescent="0.3">
       <c r="A34" s="15" t="s">
         <v>73</v>
       </c>
@@ -1955,7 +1954,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="35" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:10" ht="15" x14ac:dyDescent="0.3">
       <c r="A35" s="15" t="s">
         <v>73</v>
       </c>
@@ -1981,7 +1980,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="36" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:10" ht="15" x14ac:dyDescent="0.3">
       <c r="A36" s="15" t="s">
         <v>73</v>
       </c>
@@ -2007,7 +2006,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="37" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:10" ht="15" x14ac:dyDescent="0.3">
       <c r="A37" s="15" t="s">
         <v>73</v>
       </c>
@@ -2033,7 +2032,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="38" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:10" ht="15" x14ac:dyDescent="0.3">
       <c r="C38" s="16" t="s">
         <v>100</v>
       </c>
@@ -2041,7 +2040,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="39" spans="1:10" ht="63.75" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:10" ht="69" x14ac:dyDescent="0.3">
       <c r="A39" s="15" t="s">
         <v>73</v>
       </c>
@@ -2055,7 +2054,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="40" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:10" ht="15" x14ac:dyDescent="0.3">
       <c r="C40" s="16" t="s">
         <v>102</v>
       </c>
@@ -2063,7 +2062,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="41" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:10" ht="15" x14ac:dyDescent="0.3">
       <c r="A41" s="15" t="s">
         <v>73</v>
       </c>
@@ -2089,7 +2088,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="42" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:10" ht="15" x14ac:dyDescent="0.3">
       <c r="C42" s="16" t="s">
         <v>104</v>
       </c>
@@ -2097,7 +2096,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="43" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:10" ht="15" x14ac:dyDescent="0.3">
       <c r="C43" s="16" t="s">
         <v>105</v>
       </c>
@@ -2105,7 +2104,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="44" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:10" ht="15" x14ac:dyDescent="0.3">
       <c r="C44" s="16" t="s">
         <v>106</v>
       </c>
@@ -2116,7 +2115,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="45" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:10" ht="15" x14ac:dyDescent="0.3">
       <c r="A45" s="15" t="s">
         <v>73</v>
       </c>
@@ -2136,13 +2135,13 @@
         <v>124</v>
       </c>
       <c r="H45" s="32" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="J45" s="15" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="46" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:10" ht="15" x14ac:dyDescent="0.3">
       <c r="C46" s="16" t="s">
         <v>108</v>
       </c>
@@ -2150,7 +2149,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="47" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:10" ht="15" x14ac:dyDescent="0.3">
       <c r="C47" s="16" t="s">
         <v>109</v>
       </c>
@@ -2158,7 +2157,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="48" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:10" ht="15" x14ac:dyDescent="0.3">
       <c r="A48" s="15" t="s">
         <v>73</v>
       </c>
@@ -2184,7 +2183,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="49" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:10" ht="15" x14ac:dyDescent="0.3">
       <c r="C49" s="16" t="s">
         <v>111</v>
       </c>
@@ -2192,7 +2191,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="50" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:10" ht="15" x14ac:dyDescent="0.3">
       <c r="A50" s="15" t="s">
         <v>73</v>
       </c>
@@ -2218,7 +2217,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52" s="15" t="s">
         <v>73</v>
       </c>
@@ -2229,16 +2228,16 @@
         <v>167</v>
       </c>
       <c r="D52" s="15" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="F52" s="15">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="H52" s="15" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.2">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53" s="15" t="s">
         <v>73</v>
       </c>
@@ -2249,23 +2248,23 @@
         <v>167</v>
       </c>
       <c r="D53" s="15" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F53" s="15">
         <v>8.5</v>
       </c>
       <c r="H53" s="15" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.2">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="H63" s="15" t="s">
         <v>33</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="H45" r:id="rId1" xr:uid="{CCC25BD0-B084-4035-97DA-BBC7C0D198E2}"/>
+    <hyperlink ref="H45" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId2"/>
@@ -2273,25 +2272,25 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31B77331-D835-4B41-9157-C8D156985AE1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G37"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="15"/>
-    <col min="2" max="2" width="26.140625" style="15" customWidth="1"/>
-    <col min="3" max="3" width="26.42578125" style="15" customWidth="1"/>
-    <col min="4" max="4" width="16.5703125" style="15" customWidth="1"/>
+    <col min="1" max="1" width="9.109375" style="15"/>
+    <col min="2" max="2" width="26.109375" style="15" customWidth="1"/>
+    <col min="3" max="3" width="26.44140625" style="15" customWidth="1"/>
+    <col min="4" max="4" width="16.5546875" style="15" customWidth="1"/>
     <col min="5" max="5" width="18" style="24" customWidth="1"/>
-    <col min="6" max="6" width="31.28515625" customWidth="1"/>
-    <col min="7" max="7" width="33.7109375" customWidth="1"/>
+    <col min="6" max="6" width="31.33203125" customWidth="1"/>
+    <col min="7" max="7" width="33.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="25" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="2" spans="1:7" s="19" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" s="19" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="26" t="s">
         <v>66</v>
       </c>
@@ -2314,7 +2313,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A3" s="15" t="s">
         <v>73</v>
       </c>
@@ -2334,7 +2333,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A4" s="15" t="s">
         <v>73</v>
       </c>
@@ -2357,7 +2356,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A5" s="15" t="s">
         <v>73</v>
       </c>
@@ -2377,7 +2376,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A6" s="15" t="s">
         <v>73</v>
       </c>
@@ -2400,7 +2399,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="15" t="s">
         <v>73</v>
       </c>
@@ -2420,7 +2419,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="15" t="s">
         <v>73</v>
       </c>
@@ -2443,7 +2442,7 @@
         <v>0.316</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="15" t="s">
         <v>73</v>
       </c>
@@ -2463,7 +2462,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="15" t="s">
         <v>73</v>
       </c>
@@ -2486,7 +2485,7 @@
         <v>0.86</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A11" s="15" t="s">
         <v>73</v>
       </c>
@@ -2506,7 +2505,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A12" s="15" t="s">
         <v>73</v>
       </c>
@@ -2529,7 +2528,7 @@
         <v>0.96</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A13" s="15" t="s">
         <v>73</v>
       </c>
@@ -2549,7 +2548,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A14" s="15" t="s">
         <v>73</v>
       </c>
@@ -2572,7 +2571,7 @@
         <v>0.96</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A15" s="15" t="s">
         <v>73</v>
       </c>
@@ -2592,7 +2591,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A16" s="15" t="s">
         <v>73</v>
       </c>
@@ -2615,7 +2614,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A17" s="15" t="s">
         <v>73</v>
       </c>
@@ -2635,7 +2634,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A18" s="15" t="s">
         <v>73</v>
       </c>
@@ -2658,7 +2657,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A19" s="15" t="s">
         <v>73</v>
       </c>
@@ -2676,7 +2675,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A20" s="15" t="s">
         <v>73</v>
       </c>
@@ -2697,7 +2696,7 @@
         <v>0.998</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A21" s="15" t="s">
         <v>73</v>
       </c>
@@ -2715,7 +2714,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A22" s="15" t="s">
         <v>73</v>
       </c>
@@ -2736,7 +2735,7 @@
         <v>0.997</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A23" s="15" t="s">
         <v>73</v>
       </c>
@@ -2754,7 +2753,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A24" s="15" t="s">
         <v>73</v>
       </c>
@@ -2775,7 +2774,7 @@
         <v>0.92200000000000004</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A25" s="15" t="s">
         <v>73</v>
       </c>
@@ -2793,7 +2792,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A26" s="15" t="s">
         <v>73</v>
       </c>
@@ -2814,7 +2813,7 @@
         <v>0.92200000000000004</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A27" s="15" t="s">
         <v>73</v>
       </c>
@@ -2832,7 +2831,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A28" s="15" t="s">
         <v>73</v>
       </c>
@@ -2853,7 +2852,7 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A29" s="15" t="s">
         <v>73</v>
       </c>
@@ -2873,7 +2872,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A30" s="15" t="s">
         <v>73</v>
       </c>
@@ -2896,7 +2895,7 @@
         <v>0.97799999999999998</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A31" s="15" t="s">
         <v>73</v>
       </c>
@@ -2916,7 +2915,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A32" s="15" t="s">
         <v>73</v>
       </c>
@@ -2939,19 +2938,19 @@
         <v>0.98599999999999999</v>
       </c>
     </row>
-    <row r="33" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="3:3" ht="15" x14ac:dyDescent="0.3">
       <c r="C33" s="16"/>
     </row>
-    <row r="34" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="3:3" ht="15" x14ac:dyDescent="0.3">
       <c r="C34" s="16"/>
     </row>
-    <row r="35" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="3:3" ht="15" x14ac:dyDescent="0.3">
       <c r="C35" s="16"/>
     </row>
-    <row r="36" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="3:3" ht="15" x14ac:dyDescent="0.3">
       <c r="C36" s="16"/>
     </row>
-    <row r="37" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="3:3" ht="15" x14ac:dyDescent="0.3">
       <c r="C37" s="16"/>
     </row>
   </sheetData>
@@ -2960,22 +2959,22 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B8038DA-5443-4C6F-A4A9-CF8645419CF8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="13.28515625" customWidth="1"/>
-    <col min="3" max="3" width="15.5703125" customWidth="1"/>
-    <col min="4" max="4" width="18.28515625" customWidth="1"/>
-    <col min="7" max="7" width="22.85546875" customWidth="1"/>
+    <col min="1" max="2" width="13.33203125" customWidth="1"/>
+    <col min="3" max="3" width="15.5546875" customWidth="1"/>
+    <col min="4" max="4" width="18.33203125" customWidth="1"/>
+    <col min="7" max="7" width="22.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="2" spans="1:12" s="12" customFormat="1" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" s="12" customFormat="1" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A2" s="26" t="s">
         <v>68</v>
       </c>
@@ -3001,7 +3000,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>82</v>
       </c>
@@ -3015,7 +3014,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>86</v>
       </c>
@@ -3044,7 +3043,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>143</v>
       </c>
@@ -3070,7 +3069,7 @@
         <v>0.86</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>151</v>
       </c>
@@ -3081,7 +3080,7 @@
         <v>0.96199999999999997</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>88</v>
       </c>
@@ -3107,7 +3106,7 @@
         <v>0.96</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>92</v>
       </c>
@@ -3133,7 +3132,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>152</v>
       </c>
@@ -3144,7 +3143,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>94</v>
       </c>
@@ -3170,7 +3169,7 @@
         <v>0.997</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>101</v>
       </c>
@@ -3187,7 +3186,7 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>112</v>
       </c>
@@ -3220,56 +3219,56 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:A10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="12" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>159</v>
       </c>
@@ -3280,16 +3279,16 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80039399-BA6C-4D9A-804C-21A5BB782000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A6:G8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="G6" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>134</v>
       </c>
@@ -3300,22 +3299,22 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L36"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="27.28515625" customWidth="1"/>
-    <col min="3" max="3" width="28.5703125" customWidth="1"/>
-    <col min="4" max="4" width="33.28515625" customWidth="1"/>
+    <col min="2" max="2" width="27.33203125" customWidth="1"/>
+    <col min="3" max="3" width="28.5546875" customWidth="1"/>
+    <col min="4" max="4" width="33.33203125" customWidth="1"/>
     <col min="6" max="6" width="50" customWidth="1"/>
-    <col min="7" max="7" width="24.7109375" customWidth="1"/>
-    <col min="8" max="8" width="7.7109375" customWidth="1"/>
-    <col min="9" max="9" width="31.5703125" customWidth="1"/>
-    <col min="10" max="10" width="12.5703125" customWidth="1"/>
-    <col min="11" max="11" width="19.42578125" customWidth="1"/>
+    <col min="7" max="7" width="24.6640625" customWidth="1"/>
+    <col min="8" max="8" width="7.6640625" customWidth="1"/>
+    <col min="9" max="9" width="31.5546875" customWidth="1"/>
+    <col min="10" max="10" width="12.5546875" customWidth="1"/>
+    <col min="11" max="11" width="19.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="19" customFormat="1" ht="76.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" s="19" customFormat="1" ht="76.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="19" t="s">
         <v>129</v>
       </c>
@@ -3351,15 +3350,15 @@
         <v>65</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" ht="16.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B2" s="1"/>
       <c r="C2" s="6"/>
     </row>
-    <row r="3" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" ht="16.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="1"/>
       <c r="C3" s="6"/>
     </row>
-    <row r="4" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" ht="16.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>130</v>
       </c>
@@ -3379,7 +3378,7 @@
       <c r="K4" s="2"/>
       <c r="L4" s="2"/>
     </row>
-    <row r="5" spans="1:12" ht="19.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" ht="18.600000000000001" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>130</v>
       </c>
@@ -3401,7 +3400,7 @@
       <c r="K5" s="2"/>
       <c r="L5" s="2"/>
     </row>
-    <row r="6" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" ht="16.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>130</v>
       </c>
@@ -3421,7 +3420,7 @@
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
     </row>
-    <row r="7" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" ht="16.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>130</v>
       </c>
@@ -3457,7 +3456,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" ht="16.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>130</v>
       </c>
@@ -3477,7 +3476,7 @@
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
     </row>
-    <row r="9" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" ht="16.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>130</v>
       </c>
@@ -3499,7 +3498,7 @@
       <c r="K9" s="2"/>
       <c r="L9" s="2"/>
     </row>
-    <row r="10" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" ht="16.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>130</v>
       </c>
@@ -3517,7 +3516,7 @@
       <c r="K10" s="2"/>
       <c r="L10" s="2"/>
     </row>
-    <row r="11" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" ht="16.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>133</v>
       </c>
@@ -3553,7 +3552,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" ht="16.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>130</v>
       </c>
@@ -3581,7 +3580,7 @@
       <c r="K12" s="2"/>
       <c r="L12" s="2"/>
     </row>
-    <row r="13" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" ht="16.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>130</v>
       </c>
@@ -3603,7 +3602,7 @@
       <c r="K13" s="2"/>
       <c r="L13" s="2"/>
     </row>
-    <row r="14" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" ht="16.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>130</v>
       </c>
@@ -3623,7 +3622,7 @@
       <c r="K14" s="2"/>
       <c r="L14" s="2"/>
     </row>
-    <row r="15" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" ht="16.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>133</v>
       </c>
@@ -3657,7 +3656,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" ht="16.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>130</v>
       </c>
@@ -3683,7 +3682,7 @@
       <c r="K16" s="2"/>
       <c r="L16" s="2"/>
     </row>
-    <row r="17" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" ht="16.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>130</v>
       </c>
@@ -3701,7 +3700,7 @@
       <c r="K17" s="2"/>
       <c r="L17" s="2"/>
     </row>
-    <row r="18" spans="1:12" s="23" customFormat="1" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" s="23" customFormat="1" ht="16.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>133</v>
       </c>
@@ -3735,7 +3734,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="19" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" ht="16.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>130</v>
       </c>
@@ -3759,7 +3758,7 @@
       <c r="K19" s="2"/>
       <c r="L19" s="2"/>
     </row>
-    <row r="20" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" ht="16.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>130</v>
       </c>
@@ -3779,7 +3778,7 @@
       <c r="K20" s="2"/>
       <c r="L20" s="2"/>
     </row>
-    <row r="21" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" ht="16.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>130</v>
       </c>
@@ -3799,7 +3798,7 @@
       <c r="K21" s="2"/>
       <c r="L21" s="2"/>
     </row>
-    <row r="22" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" ht="16.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>133</v>
       </c>
@@ -3833,7 +3832,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="23" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" ht="16.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>130</v>
       </c>
@@ -3851,7 +3850,7 @@
       <c r="K23" s="2"/>
       <c r="L23" s="2"/>
     </row>
-    <row r="24" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" ht="16.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>130</v>
       </c>
@@ -3869,7 +3868,7 @@
       <c r="K24" s="2"/>
       <c r="L24" s="2"/>
     </row>
-    <row r="25" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" ht="16.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>130</v>
       </c>
@@ -3897,7 +3896,7 @@
       <c r="K25" s="2"/>
       <c r="L25" s="2"/>
     </row>
-    <row r="26" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" ht="16.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>130</v>
       </c>
@@ -3915,7 +3914,7 @@
       <c r="K26" s="2"/>
       <c r="L26" s="2"/>
     </row>
-    <row r="27" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" ht="16.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>133</v>
       </c>
@@ -3951,7 +3950,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="28" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" ht="16.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>130</v>
       </c>
@@ -3971,7 +3970,7 @@
       <c r="K28" s="2"/>
       <c r="L28" s="2"/>
     </row>
-    <row r="29" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12" ht="16.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>130</v>
       </c>
@@ -3991,7 +3990,7 @@
       <c r="K29" s="2"/>
       <c r="L29" s="2"/>
     </row>
-    <row r="30" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:12" ht="16.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>130</v>
       </c>
@@ -4011,7 +4010,7 @@
       <c r="K30" s="2"/>
       <c r="L30" s="2"/>
     </row>
-    <row r="31" spans="1:12" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:12" ht="31.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>133</v>
       </c>
@@ -4047,7 +4046,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="32" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12" ht="16.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>133</v>
       </c>
@@ -4073,7 +4072,7 @@
       <c r="K32" s="11"/>
       <c r="L32" s="2"/>
     </row>
-    <row r="33" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:12" ht="16.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>130</v>
       </c>
@@ -4093,7 +4092,7 @@
       <c r="K33" s="2"/>
       <c r="L33" s="2"/>
     </row>
-    <row r="34" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:12" ht="16.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>130</v>
       </c>
@@ -4111,7 +4110,7 @@
       <c r="K34" s="2"/>
       <c r="L34" s="2"/>
     </row>
-    <row r="35" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:12" ht="16.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>133</v>
       </c>
@@ -4145,7 +4144,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="36" spans="1:12" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="36" spans="1:12" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>

--- a/other/input/regulatory_limits/master_reg_limits.xlsx
+++ b/other/input/regulatory_limits/master_reg_limits.xlsx
@@ -70,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="668" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="720" uniqueCount="179">
   <si>
     <t>alkalinity (as CaCO3)</t>
   </si>
@@ -544,9 +544,6 @@
   </si>
   <si>
     <t>characteristic_name</t>
-  </si>
-  <si>
-    <t>BTEX</t>
   </si>
   <si>
     <t>aquaculture</t>
@@ -584,10 +581,34 @@
     <t>https://dec.alaska.gov/media/eovgrgs5/18-aac-70.pdf</t>
   </si>
   <si>
-    <t>aquaculture_minimum</t>
-  </si>
-  <si>
-    <t>aquaculture_maximum</t>
+    <t>static_metals</t>
+  </si>
+  <si>
+    <t>hydocarbons</t>
+  </si>
+  <si>
+    <t>hydrocarbons</t>
+  </si>
+  <si>
+    <t>bacteria</t>
+  </si>
+  <si>
+    <t>nutrients</t>
+  </si>
+  <si>
+    <t>other</t>
+  </si>
+  <si>
+    <t>static_category</t>
+  </si>
+  <si>
+    <t>aquaculture_water</t>
+  </si>
+  <si>
+    <t>aquaculture_minimum_water</t>
+  </si>
+  <si>
+    <t>aquaculture_maximum_water</t>
   </si>
 </sst>
 </file>
@@ -1136,1135 +1157,1292 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O63"/>
+  <dimension ref="A1:P62"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.109375" style="15"/>
-    <col min="2" max="2" width="26.109375" style="15" customWidth="1"/>
-    <col min="3" max="3" width="38.44140625" style="15" customWidth="1"/>
-    <col min="4" max="4" width="23.88671875" style="15" customWidth="1"/>
-    <col min="5" max="5" width="16.6640625" style="15" customWidth="1"/>
-    <col min="6" max="6" width="15.5546875" style="15" customWidth="1"/>
-    <col min="7" max="7" width="9.109375" style="15"/>
-    <col min="8" max="9" width="26.5546875" style="15" customWidth="1"/>
-    <col min="10" max="10" width="17.44140625" style="15" customWidth="1"/>
-    <col min="11" max="16384" width="9.109375" style="15"/>
+    <col min="1" max="1" width="18.88671875" style="15" customWidth="1"/>
+    <col min="2" max="2" width="9.109375" style="15"/>
+    <col min="3" max="3" width="26.109375" style="15" customWidth="1"/>
+    <col min="4" max="4" width="38.44140625" style="15" customWidth="1"/>
+    <col min="5" max="5" width="23.88671875" style="15" customWidth="1"/>
+    <col min="6" max="6" width="16.6640625" style="15" customWidth="1"/>
+    <col min="7" max="7" width="15.5546875" style="15" customWidth="1"/>
+    <col min="8" max="8" width="9.109375" style="15"/>
+    <col min="9" max="10" width="26.5546875" style="15" customWidth="1"/>
+    <col min="11" max="11" width="17.44140625" style="15" customWidth="1"/>
+    <col min="12" max="16384" width="9.109375" style="15"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="14" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" s="14" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="B1" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="C1" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="D1" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="E1" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="F1" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="G1" s="14" t="s">
         <v>121</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="H1" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="I1" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="I1" s="14" t="s">
+      <c r="J1" s="14" t="s">
         <v>114</v>
       </c>
-      <c r="J1" s="14" t="s">
+      <c r="K1" s="14" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="15" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" ht="15" x14ac:dyDescent="0.3">
       <c r="A2" s="15" t="s">
-        <v>73</v>
+        <v>169</v>
       </c>
       <c r="B2" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C2" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="C2" s="16" t="s">
+      <c r="D2" s="16" t="s">
         <v>78</v>
       </c>
-      <c r="D2" s="15" t="s">
+      <c r="E2" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="F2" s="15">
+      <c r="G2" s="15">
         <v>750</v>
       </c>
-      <c r="G2" s="15" t="s">
+      <c r="H2" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="H2" s="15" t="s">
+      <c r="I2" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="J2" s="15" t="s">
+      <c r="K2" s="15" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="15" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" ht="15" x14ac:dyDescent="0.3">
       <c r="A3" s="15" t="s">
-        <v>73</v>
+        <v>169</v>
       </c>
       <c r="B3" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C3" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="C3" s="16" t="s">
+      <c r="D3" s="16" t="s">
         <v>78</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="E3" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="F3" s="15">
+      <c r="G3" s="15">
         <v>87</v>
       </c>
-      <c r="G3" s="15" t="s">
+      <c r="H3" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="H3" s="15" t="s">
+      <c r="I3" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="I3" s="15" t="s">
+      <c r="J3" s="15" t="s">
         <v>113</v>
       </c>
-      <c r="J3" s="15" t="s">
+      <c r="K3" s="15" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="15" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" ht="15" x14ac:dyDescent="0.3">
       <c r="A4" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="B4" s="13" t="s">
+        <v>169</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C4" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="D4" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="D4" s="15" t="s">
+      <c r="E4" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="F4" s="15">
+      <c r="G4" s="15">
         <v>6</v>
       </c>
-      <c r="G4" s="15" t="s">
+      <c r="H4" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="H4" s="15" t="s">
+      <c r="I4" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="J4" s="15" t="s">
+      <c r="K4" s="15" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="15" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" ht="15" x14ac:dyDescent="0.3">
       <c r="A5" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="B5" s="13" t="s">
+        <v>169</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C5" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="16" t="s">
+      <c r="D5" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="E5" s="15" t="s">
         <v>116</v>
       </c>
-      <c r="F5" s="15">
+      <c r="G5" s="15">
         <v>14</v>
       </c>
-      <c r="G5" s="15" t="s">
+      <c r="H5" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="H5" s="15" t="s">
+      <c r="I5" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="J5" s="15" t="s">
+      <c r="K5" s="15" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="15" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16" ht="15" x14ac:dyDescent="0.3">
       <c r="A6" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="B6" s="13" t="s">
+        <v>169</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C6" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="16" t="s">
+      <c r="D6" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="D6" s="15" t="s">
+      <c r="E6" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="F6" s="15">
+      <c r="G6" s="15">
         <v>4300</v>
       </c>
-      <c r="G6" s="15" t="s">
+      <c r="H6" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="H6" s="15" t="s">
+      <c r="I6" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="J6" s="15" t="s">
+      <c r="K6" s="15" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="15" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:16" ht="15" x14ac:dyDescent="0.3">
       <c r="A7" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="B7" s="13" t="s">
+        <v>169</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C7" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="16" t="s">
+      <c r="D7" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="D7" s="15" t="s">
+      <c r="E7" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="F7" s="15">
+      <c r="G7" s="15">
         <v>10</v>
       </c>
-      <c r="G7" s="15" t="s">
+      <c r="H7" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="H7" s="15" t="s">
+      <c r="I7" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="J7" s="15" t="s">
+      <c r="K7" s="15" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="15" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:16" ht="15" x14ac:dyDescent="0.3">
       <c r="A8" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="B8" s="13" t="s">
+        <v>169</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C8" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="C8" s="16" t="s">
+      <c r="D8" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="D8" s="15" t="s">
+      <c r="E8" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="F8" s="15">
+      <c r="G8" s="15">
         <v>50</v>
       </c>
-      <c r="G8" s="15" t="s">
+      <c r="H8" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="H8" s="15" t="s">
+      <c r="I8" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="J8" s="15" t="s">
+      <c r="K8" s="15" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="15" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16" ht="15" x14ac:dyDescent="0.3">
       <c r="A9" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="B9" s="13" t="s">
+        <v>169</v>
+      </c>
+      <c r="B9" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C9" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="C9" s="16" t="s">
+      <c r="D9" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="D9" s="15" t="s">
+      <c r="E9" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="F9" s="15">
+      <c r="G9" s="15">
         <v>100</v>
       </c>
-      <c r="G9" s="15" t="s">
+      <c r="H9" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="H9" s="15" t="s">
+      <c r="I9" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="J9" s="15" t="s">
+      <c r="K9" s="15" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="15" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16" ht="15" x14ac:dyDescent="0.3">
       <c r="A10" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="B10" s="13" t="s">
+        <v>169</v>
+      </c>
+      <c r="B10" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C10" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="C10" s="16" t="s">
+      <c r="D10" s="16" t="s">
         <v>83</v>
       </c>
-      <c r="D10" s="15" t="s">
+      <c r="E10" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="F10" s="15">
+      <c r="G10" s="15">
         <v>2000</v>
       </c>
-      <c r="G10" s="15" t="s">
+      <c r="H10" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="H10" s="15" t="s">
+      <c r="I10" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="J10" s="15" t="s">
+      <c r="K10" s="15" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="15" x14ac:dyDescent="0.3">
-      <c r="C11" s="16" t="s">
+    <row r="11" spans="1:16" ht="15" x14ac:dyDescent="0.3">
+      <c r="A11" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="D11" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="J11" s="15" t="s">
+      <c r="K11" s="15" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="15" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16" ht="15" x14ac:dyDescent="0.3">
       <c r="A12" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="B12" s="13" t="s">
+        <v>169</v>
+      </c>
+      <c r="B12" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C12" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="C12" s="16" t="s">
+      <c r="D12" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="D12" s="15" t="s">
+      <c r="E12" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="F12" s="15">
+      <c r="G12" s="15">
         <v>4</v>
       </c>
-      <c r="G12" s="15" t="s">
+      <c r="H12" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="H12" s="15" t="s">
+      <c r="I12" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="J12" s="15" t="s">
+      <c r="K12" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="O12" s="15" t="s">
+      <c r="P12" s="15" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="13" spans="1:15" ht="15" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:16" ht="15" x14ac:dyDescent="0.3">
       <c r="A13" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="B13" s="13" t="s">
+        <v>169</v>
+      </c>
+      <c r="B13" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C13" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="C13" s="16" t="s">
+      <c r="D13" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="D13" s="15" t="s">
+      <c r="E13" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="F13" s="15">
+      <c r="G13" s="15">
         <v>100</v>
       </c>
-      <c r="G13" s="15" t="s">
+      <c r="H13" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="H13" s="15" t="s">
+      <c r="I13" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="J13" s="15" t="s">
+      <c r="K13" s="15" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="14" spans="1:15" ht="15" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16" ht="15" x14ac:dyDescent="0.3">
       <c r="A14" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="B14" s="13" t="s">
+        <v>169</v>
+      </c>
+      <c r="B14" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C14" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="C14" s="16" t="s">
+      <c r="D14" s="16" t="s">
         <v>122</v>
       </c>
-      <c r="D14" s="15" t="s">
+      <c r="E14" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="F14" s="15">
+      <c r="G14" s="15">
         <v>750</v>
       </c>
-      <c r="G14" s="15" t="s">
+      <c r="H14" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="H14" s="15" t="s">
+      <c r="I14" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="J14" s="15" t="s">
+      <c r="K14" s="15" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="15" spans="1:15" ht="15" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A15" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="B15" s="30" t="s">
-        <v>163</v>
-      </c>
-      <c r="C15" s="16" t="s">
-        <v>158</v>
-      </c>
-      <c r="D15" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="B15" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C15" s="30" t="s">
+        <v>162</v>
+      </c>
+      <c r="D15" s="30" t="s">
+        <v>162</v>
+      </c>
+      <c r="E15" s="15" t="s">
+        <v>176</v>
+      </c>
+      <c r="G15" s="15">
+        <v>10</v>
+      </c>
+      <c r="H15" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="I15" s="15" t="s">
         <v>159</v>
-      </c>
-      <c r="F15" s="15">
-        <v>10</v>
-      </c>
-      <c r="G15" s="15" t="s">
-        <v>124</v>
-      </c>
-      <c r="H15" s="15" t="s">
-        <v>160</v>
-      </c>
-      <c r="I15" s="15" t="s">
-        <v>162</v>
       </c>
       <c r="J15" s="15" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" ht="15" x14ac:dyDescent="0.3">
+      <c r="K15" s="15" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="15" x14ac:dyDescent="0.3">
       <c r="A16" s="15" t="s">
-        <v>73</v>
+        <v>169</v>
       </c>
       <c r="B16" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C16" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="C16" s="16" t="s">
+      <c r="D16" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="D16" s="15" t="s">
+      <c r="E16" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="F16" s="15">
+      <c r="G16" s="15">
         <v>5</v>
       </c>
-      <c r="G16" s="15" t="s">
+      <c r="H16" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="H16" s="15" t="s">
+      <c r="I16" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="J16" s="15" t="s">
+      <c r="K16" s="15" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="15" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" ht="15" x14ac:dyDescent="0.3">
       <c r="A17" s="15" t="s">
-        <v>73</v>
+        <v>169</v>
       </c>
       <c r="B17" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C17" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="C17" s="16" t="s">
+      <c r="D17" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="D17" s="15" t="s">
+      <c r="E17" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="F17" s="15">
+      <c r="G17" s="15">
         <v>10</v>
       </c>
-      <c r="G17" s="15" t="s">
+      <c r="H17" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="H17" s="15" t="s">
+      <c r="I17" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="J17" s="15" t="s">
+      <c r="K17" s="15" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="15" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" ht="15" x14ac:dyDescent="0.3">
       <c r="A18" s="15" t="s">
-        <v>73</v>
+        <v>169</v>
       </c>
       <c r="B18" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C18" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="C18" s="16" t="s">
+      <c r="D18" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="D18" s="15" t="s">
+      <c r="E18" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="F18" s="15">
+      <c r="G18" s="15">
         <v>10</v>
       </c>
-      <c r="G18" s="15" t="s">
+      <c r="H18" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="H18" s="15" t="s">
+      <c r="I18" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="J18" s="15" t="s">
+      <c r="K18" s="15" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="B19" s="13" t="s">
+        <v>169</v>
+      </c>
+      <c r="B19" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C19" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="C19" s="15" t="s">
+      <c r="D19" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="D19" s="15" t="s">
+      <c r="E19" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="F19" s="15">
+      <c r="G19" s="15">
         <v>100</v>
       </c>
-      <c r="G19" s="15" t="s">
+      <c r="H19" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="H19" s="15" t="s">
+      <c r="I19" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="I19" s="15" t="s">
+      <c r="J19" s="15" t="s">
         <v>125</v>
       </c>
-      <c r="J19" s="15" t="s">
+      <c r="K19" s="15" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="B20" s="13" t="s">
+        <v>169</v>
+      </c>
+      <c r="B20" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C20" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="C20" s="15" t="s">
+      <c r="D20" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="D20" s="15" t="s">
+      <c r="E20" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="F20" s="15">
+      <c r="G20" s="15">
         <v>100</v>
       </c>
-      <c r="G20" s="15" t="s">
+      <c r="H20" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="H20" s="15" t="s">
+      <c r="I20" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="J20" s="15" t="s">
+      <c r="K20" s="15" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="15" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11" ht="15" x14ac:dyDescent="0.3">
       <c r="A21" s="15" t="s">
-        <v>73</v>
+        <v>169</v>
       </c>
       <c r="B21" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C21" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="C21" s="16" t="s">
+      <c r="D21" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="D21" s="15" t="s">
+      <c r="E21" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="F21" s="15">
+      <c r="G21" s="15">
         <v>50</v>
       </c>
-      <c r="G21" s="15" t="s">
+      <c r="H21" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="H21" s="15" t="s">
+      <c r="I21" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="J21" s="15" t="s">
+      <c r="K21" s="15" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="15" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:11" ht="15" x14ac:dyDescent="0.3">
       <c r="A22" s="15" t="s">
-        <v>73</v>
+        <v>169</v>
       </c>
       <c r="B22" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C22" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="C22" s="16" t="s">
+      <c r="D22" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="D22" s="15" t="s">
+      <c r="E22" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="F22" s="15">
+      <c r="G22" s="15">
         <v>200</v>
       </c>
-      <c r="G22" s="15" t="s">
+      <c r="H22" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="H22" s="15" t="s">
+      <c r="I22" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="J22" s="15" t="s">
+      <c r="K22" s="15" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="15" x14ac:dyDescent="0.3">
-      <c r="C23" s="16" t="s">
+    <row r="23" spans="1:11" ht="15" x14ac:dyDescent="0.3">
+      <c r="A23" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="D23" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="J23" s="15" t="s">
+      <c r="K23" s="15" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="15" x14ac:dyDescent="0.3">
-      <c r="C24" s="16" t="s">
+    <row r="24" spans="1:11" ht="15" x14ac:dyDescent="0.3">
+      <c r="A24" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="D24" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="J24" s="15" t="s">
+      <c r="K24" s="15" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" s="15" t="s">
-        <v>73</v>
+        <v>169</v>
       </c>
       <c r="B25" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C25" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="C25" s="15" t="s">
+      <c r="D25" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="D25" s="15" t="s">
+      <c r="E25" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="F25" s="15">
+      <c r="G25" s="15">
         <v>5000</v>
       </c>
-      <c r="G25" s="15" t="s">
+      <c r="H25" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="H25" s="15" t="s">
+      <c r="I25" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="J25" s="15" t="s">
+      <c r="K25" s="15" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="26" spans="1:10" ht="15" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:11" ht="15" x14ac:dyDescent="0.3">
       <c r="A26" s="15" t="s">
-        <v>73</v>
+        <v>169</v>
       </c>
       <c r="B26" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C26" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="C26" s="16" t="s">
+      <c r="D26" s="16" t="s">
         <v>92</v>
       </c>
-      <c r="D26" s="15" t="s">
+      <c r="E26" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="F26" s="15">
+      <c r="G26" s="15">
         <v>50</v>
       </c>
-      <c r="G26" s="15" t="s">
+      <c r="H26" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="H26" s="15" t="s">
+      <c r="I26" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="J26" s="15" t="s">
+      <c r="K26" s="15" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="27" spans="1:10" ht="15" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:11" ht="15" x14ac:dyDescent="0.3">
       <c r="A27" s="15" t="s">
-        <v>73</v>
+        <v>169</v>
       </c>
       <c r="B27" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C27" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="C27" s="16" t="s">
+      <c r="D27" s="16" t="s">
         <v>92</v>
       </c>
-      <c r="D27" s="15" t="s">
+      <c r="E27" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="E27" s="15" t="s">
+      <c r="F27" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="F27" s="15">
+      <c r="G27" s="15">
         <v>5000</v>
       </c>
-      <c r="G27" s="15" t="s">
+      <c r="H27" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="H27" s="15" t="s">
+      <c r="I27" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="J27" s="15" t="s">
+      <c r="K27" s="15" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="28" spans="1:10" ht="15" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:11" ht="15" x14ac:dyDescent="0.3">
       <c r="A28" s="15" t="s">
-        <v>73</v>
+        <v>169</v>
       </c>
       <c r="B28" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C28" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="C28" s="16" t="s">
+      <c r="D28" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="D28" s="15" t="s">
+      <c r="E28" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="F28" s="15">
+      <c r="G28" s="15">
         <v>10</v>
       </c>
-      <c r="G28" s="15" t="s">
+      <c r="H28" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="H28" s="15" t="s">
+      <c r="I28" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="J28" s="15" t="s">
+      <c r="K28" s="15" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="29" spans="1:10" ht="15" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:11" ht="15" x14ac:dyDescent="0.3">
       <c r="A29" s="15" t="s">
-        <v>73</v>
+        <v>169</v>
       </c>
       <c r="B29" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C29" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="C29" s="16" t="s">
+      <c r="D29" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="D29" s="15" t="s">
+      <c r="E29" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="F29" s="15">
+      <c r="G29" s="15">
         <v>100</v>
       </c>
-      <c r="G29" s="15" t="s">
+      <c r="H29" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="H29" s="15" t="s">
+      <c r="I29" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="J29" s="15" t="s">
+      <c r="K29" s="15" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="30" spans="1:10" ht="15" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:11" ht="15" x14ac:dyDescent="0.3">
       <c r="A30" s="15" t="s">
-        <v>73</v>
+        <v>169</v>
       </c>
       <c r="B30" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C30" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="C30" s="16" t="s">
+      <c r="D30" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="D30" s="15" t="s">
+      <c r="E30" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="F30" s="15">
+      <c r="G30" s="15">
         <v>200</v>
       </c>
-      <c r="G30" s="15" t="s">
+      <c r="H30" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="H30" s="15" t="s">
+      <c r="I30" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="J30" s="15" t="s">
+      <c r="K30" s="15" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="31" spans="1:10" ht="15" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:11" ht="15" x14ac:dyDescent="0.3">
       <c r="A31" s="15" t="s">
-        <v>73</v>
+        <v>171</v>
       </c>
       <c r="B31" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C31" s="15" t="s">
         <v>126</v>
       </c>
-      <c r="C31" s="16" t="s">
+      <c r="D31" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="J31" s="15" t="s">
+      <c r="K31" s="15" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="32" spans="1:10" ht="15" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:11" ht="15" x14ac:dyDescent="0.3">
       <c r="A32" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="B32" s="16" t="s">
-        <v>96</v>
+        <v>171</v>
+      </c>
+      <c r="B32" s="15" t="s">
+        <v>73</v>
       </c>
       <c r="C32" s="16" t="s">
         <v>96</v>
       </c>
-      <c r="J32" s="15" t="s">
+      <c r="D32" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="K32" s="15" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="33" spans="1:10" ht="15" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:11" ht="15" x14ac:dyDescent="0.3">
       <c r="A33" s="15" t="s">
-        <v>73</v>
+        <v>173</v>
       </c>
       <c r="B33" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C33" s="15" t="s">
         <v>127</v>
       </c>
-      <c r="C33" s="16" t="s">
+      <c r="D33" s="16" t="s">
         <v>97</v>
       </c>
-      <c r="J33" s="15" t="s">
+      <c r="K33" s="15" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="34" spans="1:10" ht="15" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:11" ht="15" x14ac:dyDescent="0.3">
       <c r="A34" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="B34" s="13" t="s">
+        <v>173</v>
+      </c>
+      <c r="B34" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C34" s="13" t="s">
         <v>128</v>
       </c>
-      <c r="C34" s="16" t="s">
+      <c r="D34" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="J34" s="15" t="s">
+      <c r="K34" s="15" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="35" spans="1:10" ht="15" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:11" ht="15" x14ac:dyDescent="0.3">
       <c r="A35" s="15" t="s">
-        <v>73</v>
+        <v>169</v>
       </c>
       <c r="B35" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C35" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="C35" s="16" t="s">
+      <c r="D35" s="16" t="s">
         <v>99</v>
       </c>
-      <c r="D35" s="15" t="s">
+      <c r="E35" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="F35" s="15">
+      <c r="G35" s="15">
         <v>50</v>
       </c>
-      <c r="G35" s="15" t="s">
+      <c r="H35" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="H35" s="15" t="s">
+      <c r="I35" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="J35" s="15" t="s">
+      <c r="K35" s="15" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="36" spans="1:10" ht="15" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:11" ht="15" x14ac:dyDescent="0.3">
       <c r="A36" s="15" t="s">
-        <v>73</v>
+        <v>169</v>
       </c>
       <c r="B36" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C36" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="C36" s="16" t="s">
+      <c r="D36" s="16" t="s">
         <v>99</v>
       </c>
-      <c r="D36" s="15" t="s">
+      <c r="E36" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="F36" s="15">
+      <c r="G36" s="15">
         <v>10</v>
       </c>
-      <c r="G36" s="15" t="s">
+      <c r="H36" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="H36" s="15" t="s">
+      <c r="I36" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="J36" s="15" t="s">
+      <c r="K36" s="15" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="37" spans="1:10" ht="15" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:11" ht="15" x14ac:dyDescent="0.3">
       <c r="A37" s="15" t="s">
-        <v>73</v>
+        <v>169</v>
       </c>
       <c r="B37" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C37" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="C37" s="16" t="s">
+      <c r="D37" s="16" t="s">
         <v>99</v>
       </c>
-      <c r="D37" s="15" t="s">
+      <c r="E37" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="F37" s="15">
+      <c r="G37" s="15">
         <v>20</v>
       </c>
-      <c r="G37" s="15" t="s">
+      <c r="H37" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="H37" s="15" t="s">
+      <c r="I37" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="J37" s="15" t="s">
+      <c r="K37" s="15" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="38" spans="1:10" ht="15" x14ac:dyDescent="0.3">
-      <c r="C38" s="16" t="s">
+    <row r="38" spans="1:11" ht="15" x14ac:dyDescent="0.3">
+      <c r="A38" s="15" t="s">
+        <v>169</v>
+      </c>
+      <c r="D38" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="J38" s="15" t="s">
+      <c r="K38" s="15" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="39" spans="1:10" ht="69" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:11" ht="69" x14ac:dyDescent="0.3">
       <c r="A39" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="C39" s="16" t="s">
+        <v>169</v>
+      </c>
+      <c r="B39" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="D39" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="I39" s="31" t="s">
+      <c r="J39" s="31" t="s">
+        <v>163</v>
+      </c>
+      <c r="K39" s="15" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" ht="15" x14ac:dyDescent="0.3">
+      <c r="A40" s="15" t="s">
+        <v>169</v>
+      </c>
+      <c r="D40" s="16" t="s">
+        <v>102</v>
+      </c>
+      <c r="K40" s="15" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" ht="15" x14ac:dyDescent="0.3">
+      <c r="A41" s="15" t="s">
+        <v>169</v>
+      </c>
+      <c r="B41" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C41" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="D41" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="E41" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="G41" s="15">
+        <v>2</v>
+      </c>
+      <c r="H41" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="I41" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="K41" s="15" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" ht="15" x14ac:dyDescent="0.3">
+      <c r="A42" s="15" t="s">
+        <v>169</v>
+      </c>
+      <c r="D42" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="K42" s="15" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" ht="15" x14ac:dyDescent="0.3">
+      <c r="A43" s="15" t="s">
+        <v>169</v>
+      </c>
+      <c r="D43" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="K43" s="15" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" ht="15" x14ac:dyDescent="0.3">
+      <c r="A44" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="D44" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="J44" s="15" t="s">
         <v>164</v>
       </c>
-      <c r="J39" s="15" t="s">
+      <c r="K44" s="15" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="40" spans="1:10" ht="15" x14ac:dyDescent="0.3">
-      <c r="C40" s="16" t="s">
-        <v>102</v>
-      </c>
-      <c r="J40" s="15" t="s">
+    <row r="45" spans="1:11" ht="15" x14ac:dyDescent="0.3">
+      <c r="A45" s="15" t="s">
+        <v>173</v>
+      </c>
+      <c r="B45" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C45" s="15" t="s">
+        <v>165</v>
+      </c>
+      <c r="D45" s="16" t="s">
+        <v>107</v>
+      </c>
+      <c r="E45" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="G45" s="15">
+        <v>10000</v>
+      </c>
+      <c r="H45" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="I45" s="32" t="s">
+        <v>167</v>
+      </c>
+      <c r="K45" s="15" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" ht="15" x14ac:dyDescent="0.3">
+      <c r="A46" s="15" t="s">
+        <v>173</v>
+      </c>
+      <c r="D46" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="K46" s="15" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="41" spans="1:10" ht="15" x14ac:dyDescent="0.3">
-      <c r="A41" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="B41" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="C41" s="16" t="s">
-        <v>103</v>
-      </c>
-      <c r="D41" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="F41" s="15">
-        <v>2</v>
-      </c>
-      <c r="G41" s="15" t="s">
+    <row r="47" spans="1:11" ht="15" x14ac:dyDescent="0.3">
+      <c r="A47" s="15" t="s">
+        <v>174</v>
+      </c>
+      <c r="D47" s="16" t="s">
+        <v>109</v>
+      </c>
+      <c r="K47" s="15" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" ht="15" x14ac:dyDescent="0.3">
+      <c r="A48" s="15" t="s">
+        <v>169</v>
+      </c>
+      <c r="B48" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C48" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="D48" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="E48" s="15" t="s">
+        <v>119</v>
+      </c>
+      <c r="G48" s="15">
+        <v>100</v>
+      </c>
+      <c r="H48" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="H41" s="15" t="s">
+      <c r="I48" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="J41" s="15" t="s">
+      <c r="K48" s="15" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="42" spans="1:10" ht="15" x14ac:dyDescent="0.3">
-      <c r="C42" s="16" t="s">
-        <v>104</v>
-      </c>
-      <c r="J42" s="15" t="s">
+    <row r="49" spans="1:11" ht="15" x14ac:dyDescent="0.3">
+      <c r="A49" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="D49" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="K49" s="15" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="43" spans="1:10" ht="15" x14ac:dyDescent="0.3">
-      <c r="C43" s="16" t="s">
-        <v>105</v>
-      </c>
-      <c r="J43" s="15" t="s">
+    <row r="50" spans="1:11" ht="15" x14ac:dyDescent="0.3">
+      <c r="A50" s="15" t="s">
+        <v>169</v>
+      </c>
+      <c r="B50" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C50" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="D50" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="E50" s="15" t="s">
+        <v>119</v>
+      </c>
+      <c r="G50" s="15">
+        <v>2000</v>
+      </c>
+      <c r="H50" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="I50" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="K50" s="15" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="44" spans="1:10" ht="15" x14ac:dyDescent="0.3">
-      <c r="C44" s="16" t="s">
-        <v>106</v>
-      </c>
-      <c r="I44" s="15" t="s">
-        <v>165</v>
-      </c>
-      <c r="J44" s="15" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10" ht="15" x14ac:dyDescent="0.3">
-      <c r="A45" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="B45" s="15" t="s">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A51" s="15" t="s">
+        <v>174</v>
+      </c>
+      <c r="B51" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C51" s="15" t="s">
         <v>166</v>
       </c>
-      <c r="C45" s="16" t="s">
-        <v>107</v>
-      </c>
-      <c r="D45" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="F45" s="15">
-        <v>10000</v>
-      </c>
-      <c r="G45" s="15" t="s">
-        <v>124</v>
-      </c>
-      <c r="H45" s="32" t="s">
+      <c r="D51" s="15" t="s">
+        <v>166</v>
+      </c>
+      <c r="E51" s="15" t="s">
+        <v>177</v>
+      </c>
+      <c r="G51" s="15">
+        <v>6.5</v>
+      </c>
+      <c r="I51" s="15" t="s">
         <v>168</v>
       </c>
-      <c r="J45" s="15" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10" ht="15" x14ac:dyDescent="0.3">
-      <c r="C46" s="16" t="s">
-        <v>108</v>
-      </c>
-      <c r="J46" s="15" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10" ht="15" x14ac:dyDescent="0.3">
-      <c r="C47" s="16" t="s">
-        <v>109</v>
-      </c>
-      <c r="J47" s="15" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10" ht="15" x14ac:dyDescent="0.3">
-      <c r="A48" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="B48" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="C48" s="16" t="s">
-        <v>110</v>
-      </c>
-      <c r="D48" s="15" t="s">
-        <v>119</v>
-      </c>
-      <c r="F48" s="15">
-        <v>100</v>
-      </c>
-      <c r="G48" s="15" t="s">
-        <v>124</v>
-      </c>
-      <c r="H48" s="15" t="s">
-        <v>80</v>
-      </c>
-      <c r="J48" s="15" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10" ht="15" x14ac:dyDescent="0.3">
-      <c r="C49" s="16" t="s">
-        <v>111</v>
-      </c>
-      <c r="J49" s="15" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10" ht="15" x14ac:dyDescent="0.3">
-      <c r="A50" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="B50" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="C50" s="16" t="s">
-        <v>112</v>
-      </c>
-      <c r="D50" s="15" t="s">
-        <v>119</v>
-      </c>
-      <c r="F50" s="15">
-        <v>2000</v>
-      </c>
-      <c r="G50" s="15" t="s">
-        <v>124</v>
-      </c>
-      <c r="H50" s="15" t="s">
-        <v>80</v>
-      </c>
-      <c r="J50" s="15" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A52" s="15" t="s">
-        <v>73</v>
+        <v>174</v>
       </c>
       <c r="B52" s="15" t="s">
-        <v>167</v>
+        <v>73</v>
       </c>
       <c r="C52" s="15" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D52" s="15" t="s">
-        <v>170</v>
-      </c>
-      <c r="F52" s="15">
-        <v>6.5</v>
-      </c>
-      <c r="H52" s="15" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A53" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="B53" s="15" t="s">
-        <v>167</v>
-      </c>
-      <c r="C53" s="15" t="s">
-        <v>167</v>
-      </c>
-      <c r="D53" s="15" t="s">
-        <v>171</v>
-      </c>
-      <c r="F53" s="15">
+        <v>166</v>
+      </c>
+      <c r="E52" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="G52" s="15">
         <v>8.5</v>
       </c>
-      <c r="H53" s="15" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="H63" s="15" t="s">
+      <c r="I52" s="15" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="I62" s="15" t="s">
         <v>33</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="H45" r:id="rId1"/>
+    <hyperlink ref="I45" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId2"/>
@@ -3270,7 +3448,7 @@
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
   </sheetData>

--- a/other/input/regulatory_limits/master_reg_limits.xlsx
+++ b/other/input/regulatory_limits/master_reg_limits.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28324"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="20" documentId="11_F3222DCEA08A4C9A6976DB97F14DE766E6606446" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8DC640F5-1A12-4723-AF93-54493970D9DD}"/>
   <bookViews>
-    <workbookView xWindow="34500" yWindow="-2172" windowWidth="21420" windowHeight="13920" tabRatio="795" activeTab="1"/>
+    <workbookView xWindow="31875" yWindow="1065" windowWidth="21600" windowHeight="11295" tabRatio="795" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ReadMe" sheetId="8" r:id="rId1"/>
@@ -20,28 +21,17 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Author</author>
   </authors>
   <commentList>
-    <comment ref="I16" authorId="0" shapeId="0">
+    <comment ref="I16" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-000001000000}">
       <text>
         <r>
           <rPr>
@@ -70,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="720" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="732" uniqueCount="185">
   <si>
     <t>alkalinity (as CaCO3)</t>
   </si>
@@ -609,12 +599,30 @@
   </si>
   <si>
     <t>aquaculture_maximum_water</t>
+  </si>
+  <si>
+    <t>Fecal Coliform</t>
+  </si>
+  <si>
+    <t>secondary_water_recreation</t>
+  </si>
+  <si>
+    <t>harvest_aquatic_life</t>
+  </si>
+  <si>
+    <t>cfu/100ml</t>
+  </si>
+  <si>
+    <t>https://dec.alaska.gov/water/water-quality/standards/</t>
+  </si>
+  <si>
+    <t>BM 20250115</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
@@ -1136,16 +1144,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="3" spans="1:1" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" ht="18" x14ac:dyDescent="0.25">
       <c r="A3" s="29" t="s">
         <v>144</v>
       </c>
@@ -1156,24 +1164,24 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P62"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:P63"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="18.88671875" style="15" customWidth="1"/>
-    <col min="2" max="2" width="9.109375" style="15"/>
-    <col min="3" max="3" width="26.109375" style="15" customWidth="1"/>
-    <col min="4" max="4" width="38.44140625" style="15" customWidth="1"/>
-    <col min="5" max="5" width="23.88671875" style="15" customWidth="1"/>
-    <col min="6" max="6" width="16.6640625" style="15" customWidth="1"/>
-    <col min="7" max="7" width="15.5546875" style="15" customWidth="1"/>
-    <col min="8" max="8" width="9.109375" style="15"/>
-    <col min="9" max="10" width="26.5546875" style="15" customWidth="1"/>
-    <col min="11" max="11" width="17.44140625" style="15" customWidth="1"/>
-    <col min="12" max="16384" width="9.109375" style="15"/>
+    <col min="1" max="1" width="18.85546875" style="15" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" style="15"/>
+    <col min="3" max="3" width="26.140625" style="15" customWidth="1"/>
+    <col min="4" max="4" width="38.42578125" style="15" customWidth="1"/>
+    <col min="5" max="5" width="23.85546875" style="15" customWidth="1"/>
+    <col min="6" max="6" width="16.7109375" style="15" customWidth="1"/>
+    <col min="7" max="7" width="15.5703125" style="15" customWidth="1"/>
+    <col min="8" max="8" width="9.140625" style="15"/>
+    <col min="9" max="10" width="26.5703125" style="15" customWidth="1"/>
+    <col min="11" max="11" width="17.42578125" style="15" customWidth="1"/>
+    <col min="12" max="16384" width="9.140625" style="15"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="14" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" s="14" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="14" t="s">
         <v>175</v>
       </c>
@@ -1208,7 +1216,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="15" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A2" s="15" t="s">
         <v>169</v>
       </c>
@@ -1237,7 +1245,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="3" spans="1:16" ht="15" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A3" s="15" t="s">
         <v>169</v>
       </c>
@@ -1269,7 +1277,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="4" spans="1:16" ht="15" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A4" s="15" t="s">
         <v>169</v>
       </c>
@@ -1298,7 +1306,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="15" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A5" s="15" t="s">
         <v>169</v>
       </c>
@@ -1327,7 +1335,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="6" spans="1:16" ht="15" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A6" s="15" t="s">
         <v>169</v>
       </c>
@@ -1356,7 +1364,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="7" spans="1:16" ht="15" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:16" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A7" s="15" t="s">
         <v>169</v>
       </c>
@@ -1385,7 +1393,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="8" spans="1:16" ht="15" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:16" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A8" s="15" t="s">
         <v>169</v>
       </c>
@@ -1414,7 +1422,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="9" spans="1:16" ht="15" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A9" s="15" t="s">
         <v>169</v>
       </c>
@@ -1443,7 +1451,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="10" spans="1:16" ht="15" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A10" s="15" t="s">
         <v>169</v>
       </c>
@@ -1472,7 +1480,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="11" spans="1:16" ht="15" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:16" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A11" s="15" t="s">
         <v>170</v>
       </c>
@@ -1483,7 +1491,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="12" spans="1:16" ht="15" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A12" s="15" t="s">
         <v>169</v>
       </c>
@@ -1515,7 +1523,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="13" spans="1:16" ht="15" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:16" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A13" s="15" t="s">
         <v>169</v>
       </c>
@@ -1544,7 +1552,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="14" spans="1:16" ht="15" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A14" s="15" t="s">
         <v>169</v>
       </c>
@@ -1573,7 +1581,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A15" s="15" t="s">
         <v>171</v>
       </c>
@@ -1605,7 +1613,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="16" spans="1:16" ht="15" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:16" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A16" s="15" t="s">
         <v>169</v>
       </c>
@@ -1634,7 +1642,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="15" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A17" s="15" t="s">
         <v>169</v>
       </c>
@@ -1663,7 +1671,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="18" spans="1:11" ht="15" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A18" s="15" t="s">
         <v>169</v>
       </c>
@@ -1692,7 +1700,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19" s="15" t="s">
         <v>169</v>
       </c>
@@ -1724,7 +1732,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20" s="15" t="s">
         <v>169</v>
       </c>
@@ -1753,7 +1761,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="21" spans="1:11" ht="15" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A21" s="15" t="s">
         <v>169</v>
       </c>
@@ -1782,7 +1790,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="22" spans="1:11" ht="15" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A22" s="15" t="s">
         <v>169</v>
       </c>
@@ -1811,7 +1819,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="23" spans="1:11" ht="15" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A23" s="15" t="s">
         <v>171</v>
       </c>
@@ -1822,47 +1830,59 @@
         <v>120</v>
       </c>
     </row>
-    <row r="24" spans="1:11" ht="15" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A24" s="15" t="s">
         <v>172</v>
       </c>
+      <c r="B24" s="15" t="s">
+        <v>73</v>
+      </c>
       <c r="D24" s="16" t="s">
         <v>90</v>
       </c>
+      <c r="E24" s="15" t="s">
+        <v>180</v>
+      </c>
+      <c r="G24" s="15">
+        <v>400</v>
+      </c>
+      <c r="H24" s="15" t="s">
+        <v>182</v>
+      </c>
+      <c r="I24" s="15" t="s">
+        <v>183</v>
+      </c>
       <c r="K24" s="15" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A25" s="15" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="B25" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="C25" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="D25" s="15" t="s">
-        <v>91</v>
+      <c r="D25" s="16" t="s">
+        <v>179</v>
       </c>
       <c r="E25" s="15" t="s">
-        <v>119</v>
+        <v>181</v>
       </c>
       <c r="G25" s="15">
-        <v>5000</v>
+        <v>31</v>
       </c>
       <c r="H25" s="15" t="s">
-        <v>124</v>
+        <v>182</v>
       </c>
       <c r="I25" s="15" t="s">
-        <v>80</v>
+        <v>183</v>
       </c>
       <c r="K25" s="15" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" ht="15" x14ac:dyDescent="0.3">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A26" s="15" t="s">
         <v>169</v>
       </c>
@@ -1870,16 +1890,16 @@
         <v>73</v>
       </c>
       <c r="C26" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="D26" s="16" t="s">
-        <v>92</v>
+        <v>18</v>
+      </c>
+      <c r="D26" s="15" t="s">
+        <v>91</v>
       </c>
       <c r="E26" s="15" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G26" s="15">
-        <v>50</v>
+        <v>5000</v>
       </c>
       <c r="H26" s="15" t="s">
         <v>124</v>
@@ -1891,7 +1911,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="27" spans="1:11" ht="15" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A27" s="15" t="s">
         <v>169</v>
       </c>
@@ -1905,13 +1925,10 @@
         <v>92</v>
       </c>
       <c r="E27" s="15" t="s">
-        <v>119</v>
-      </c>
-      <c r="F27" s="15" t="s">
-        <v>33</v>
+        <v>118</v>
       </c>
       <c r="G27" s="15">
-        <v>5000</v>
+        <v>50</v>
       </c>
       <c r="H27" s="15" t="s">
         <v>124</v>
@@ -1923,7 +1940,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="28" spans="1:11" ht="15" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A28" s="15" t="s">
         <v>169</v>
       </c>
@@ -1931,16 +1948,19 @@
         <v>73</v>
       </c>
       <c r="C28" s="15" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D28" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E28" s="15" t="s">
         <v>119</v>
       </c>
+      <c r="F28" s="15" t="s">
+        <v>33</v>
+      </c>
       <c r="G28" s="15">
-        <v>10</v>
+        <v>5000</v>
       </c>
       <c r="H28" s="15" t="s">
         <v>124</v>
@@ -1952,7 +1972,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="29" spans="1:11" ht="15" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A29" s="15" t="s">
         <v>169</v>
       </c>
@@ -1960,16 +1980,16 @@
         <v>73</v>
       </c>
       <c r="C29" s="15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D29" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E29" s="15" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G29" s="15">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="H29" s="15" t="s">
         <v>124</v>
@@ -1981,7 +2001,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="30" spans="1:11" ht="15" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A30" s="15" t="s">
         <v>169</v>
       </c>
@@ -1995,10 +2015,10 @@
         <v>94</v>
       </c>
       <c r="E30" s="15" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="G30" s="15">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="H30" s="15" t="s">
         <v>124</v>
@@ -2010,104 +2030,107 @@
         <v>120</v>
       </c>
     </row>
-    <row r="31" spans="1:11" ht="15" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A31" s="15" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B31" s="15" t="s">
         <v>73</v>
       </c>
       <c r="C31" s="15" t="s">
-        <v>126</v>
+        <v>24</v>
       </c>
       <c r="D31" s="16" t="s">
-        <v>95</v>
+        <v>94</v>
+      </c>
+      <c r="E31" s="15" t="s">
+        <v>119</v>
+      </c>
+      <c r="G31" s="15">
+        <v>200</v>
+      </c>
+      <c r="H31" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="I31" s="15" t="s">
+        <v>80</v>
       </c>
       <c r="K31" s="15" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="32" spans="1:11" ht="15" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A32" s="15" t="s">
         <v>171</v>
       </c>
       <c r="B32" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="C32" s="16" t="s">
-        <v>96</v>
+      <c r="C32" s="15" t="s">
+        <v>126</v>
       </c>
       <c r="D32" s="16" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K32" s="15" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="33" spans="1:11" ht="15" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A33" s="15" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B33" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="C33" s="15" t="s">
-        <v>127</v>
+      <c r="C33" s="16" t="s">
+        <v>96</v>
       </c>
       <c r="D33" s="16" t="s">
-        <v>97</v>
+        <v>96</v>
+      </c>
+      <c r="I33" s="15" t="s">
+        <v>33</v>
       </c>
       <c r="K33" s="15" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="34" spans="1:11" ht="15" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A34" s="15" t="s">
         <v>173</v>
       </c>
       <c r="B34" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="C34" s="13" t="s">
-        <v>128</v>
+      <c r="C34" s="15" t="s">
+        <v>127</v>
       </c>
       <c r="D34" s="16" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K34" s="15" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="35" spans="1:11" ht="15" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A35" s="15" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="B35" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="C35" s="15" t="s">
-        <v>28</v>
+      <c r="C35" s="13" t="s">
+        <v>128</v>
       </c>
       <c r="D35" s="16" t="s">
-        <v>99</v>
-      </c>
-      <c r="E35" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="G35" s="15">
-        <v>50</v>
-      </c>
-      <c r="H35" s="15" t="s">
-        <v>124</v>
-      </c>
-      <c r="I35" s="15" t="s">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="K35" s="15" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="36" spans="1:11" ht="15" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A36" s="15" t="s">
         <v>169</v>
       </c>
@@ -2121,10 +2144,10 @@
         <v>99</v>
       </c>
       <c r="E36" s="15" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="G36" s="15">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="H36" s="15" t="s">
         <v>124</v>
@@ -2136,7 +2159,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="37" spans="1:11" ht="15" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A37" s="15" t="s">
         <v>169</v>
       </c>
@@ -2150,10 +2173,10 @@
         <v>99</v>
       </c>
       <c r="E37" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G37" s="15">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H37" s="15" t="s">
         <v>124</v>
@@ -2165,254 +2188,260 @@
         <v>120</v>
       </c>
     </row>
-    <row r="38" spans="1:11" ht="15" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A38" s="15" t="s">
         <v>169</v>
       </c>
+      <c r="B38" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C38" s="15" t="s">
+        <v>28</v>
+      </c>
       <c r="D38" s="16" t="s">
-        <v>100</v>
+        <v>99</v>
+      </c>
+      <c r="E38" s="15" t="s">
+        <v>119</v>
+      </c>
+      <c r="G38" s="15">
+        <v>20</v>
+      </c>
+      <c r="H38" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="I38" s="15" t="s">
+        <v>80</v>
       </c>
       <c r="K38" s="15" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="39" spans="1:11" ht="69" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A39" s="15" t="s">
         <v>169</v>
       </c>
-      <c r="B39" s="15" t="s">
-        <v>73</v>
-      </c>
       <c r="D39" s="16" t="s">
-        <v>101</v>
-      </c>
-      <c r="J39" s="31" t="s">
-        <v>163</v>
+        <v>100</v>
       </c>
       <c r="K39" s="15" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="40" spans="1:11" ht="15" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:11" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A40" s="15" t="s">
         <v>169</v>
       </c>
+      <c r="B40" s="15" t="s">
+        <v>73</v>
+      </c>
       <c r="D40" s="16" t="s">
-        <v>102</v>
+        <v>101</v>
+      </c>
+      <c r="J40" s="31" t="s">
+        <v>163</v>
       </c>
       <c r="K40" s="15" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="41" spans="1:11" ht="15" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A41" s="15" t="s">
         <v>169</v>
       </c>
-      <c r="B41" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="C41" s="15" t="s">
-        <v>30</v>
-      </c>
       <c r="D41" s="16" t="s">
-        <v>103</v>
-      </c>
-      <c r="E41" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="G41" s="15">
-        <v>2</v>
-      </c>
-      <c r="H41" s="15" t="s">
-        <v>124</v>
-      </c>
-      <c r="I41" s="15" t="s">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="K41" s="15" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="42" spans="1:11" ht="15" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A42" s="15" t="s">
         <v>169</v>
       </c>
+      <c r="B42" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C42" s="15" t="s">
+        <v>30</v>
+      </c>
       <c r="D42" s="16" t="s">
-        <v>104</v>
+        <v>103</v>
+      </c>
+      <c r="E42" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="G42" s="15">
+        <v>2</v>
+      </c>
+      <c r="H42" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="I42" s="15" t="s">
+        <v>80</v>
       </c>
       <c r="K42" s="15" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="43" spans="1:11" ht="15" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A43" s="15" t="s">
         <v>169</v>
       </c>
       <c r="D43" s="16" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K43" s="15" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="44" spans="1:11" ht="15" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A44" s="15" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D44" s="16" t="s">
-        <v>106</v>
-      </c>
-      <c r="J44" s="15" t="s">
-        <v>164</v>
+        <v>105</v>
       </c>
       <c r="K44" s="15" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="45" spans="1:11" ht="15" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A45" s="15" t="s">
-        <v>173</v>
-      </c>
-      <c r="B45" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="C45" s="15" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="D45" s="16" t="s">
-        <v>107</v>
-      </c>
-      <c r="E45" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="G45" s="15">
-        <v>10000</v>
-      </c>
-      <c r="H45" s="15" t="s">
-        <v>124</v>
-      </c>
-      <c r="I45" s="32" t="s">
-        <v>167</v>
+        <v>106</v>
+      </c>
+      <c r="J45" s="15" t="s">
+        <v>164</v>
       </c>
       <c r="K45" s="15" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="46" spans="1:11" ht="15" x14ac:dyDescent="0.3">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" ht="15" x14ac:dyDescent="0.25">
       <c r="A46" s="15" t="s">
         <v>173</v>
       </c>
+      <c r="B46" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C46" s="15" t="s">
+        <v>165</v>
+      </c>
       <c r="D46" s="16" t="s">
+        <v>107</v>
+      </c>
+      <c r="E46" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="G46" s="15">
+        <v>10000</v>
+      </c>
+      <c r="H46" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="I46" s="32" t="s">
+        <v>167</v>
+      </c>
+      <c r="K46" s="15" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A47" s="15" t="s">
+        <v>173</v>
+      </c>
+      <c r="D47" s="16" t="s">
         <v>108</v>
-      </c>
-      <c r="K46" s="15" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="47" spans="1:11" ht="15" x14ac:dyDescent="0.3">
-      <c r="A47" s="15" t="s">
-        <v>174</v>
-      </c>
-      <c r="D47" s="16" t="s">
-        <v>109</v>
       </c>
       <c r="K47" s="15" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="48" spans="1:11" ht="15" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A48" s="15" t="s">
-        <v>169</v>
-      </c>
-      <c r="B48" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="C48" s="15" t="s">
-        <v>31</v>
+        <v>174</v>
       </c>
       <c r="D48" s="16" t="s">
-        <v>110</v>
-      </c>
-      <c r="E48" s="15" t="s">
-        <v>119</v>
-      </c>
-      <c r="G48" s="15">
-        <v>100</v>
-      </c>
-      <c r="H48" s="15" t="s">
-        <v>124</v>
-      </c>
-      <c r="I48" s="15" t="s">
-        <v>80</v>
+        <v>109</v>
       </c>
       <c r="K48" s="15" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="49" spans="1:11" ht="15" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A49" s="15" t="s">
-        <v>171</v>
+        <v>169</v>
+      </c>
+      <c r="B49" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C49" s="15" t="s">
+        <v>31</v>
       </c>
       <c r="D49" s="16" t="s">
-        <v>111</v>
+        <v>110</v>
+      </c>
+      <c r="E49" s="15" t="s">
+        <v>119</v>
+      </c>
+      <c r="G49" s="15">
+        <v>100</v>
+      </c>
+      <c r="H49" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="I49" s="15" t="s">
+        <v>80</v>
       </c>
       <c r="K49" s="15" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="50" spans="1:11" ht="15" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A50" s="15" t="s">
-        <v>169</v>
-      </c>
-      <c r="B50" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="C50" s="15" t="s">
-        <v>32</v>
+        <v>171</v>
       </c>
       <c r="D50" s="16" t="s">
-        <v>112</v>
-      </c>
-      <c r="E50" s="15" t="s">
-        <v>119</v>
-      </c>
-      <c r="G50" s="15">
-        <v>2000</v>
-      </c>
-      <c r="H50" s="15" t="s">
-        <v>124</v>
-      </c>
-      <c r="I50" s="15" t="s">
-        <v>80</v>
+        <v>111</v>
       </c>
       <c r="K50" s="15" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A51" s="15" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="B51" s="15" t="s">
         <v>73</v>
       </c>
       <c r="C51" s="15" t="s">
-        <v>166</v>
-      </c>
-      <c r="D51" s="15" t="s">
-        <v>166</v>
+        <v>32</v>
+      </c>
+      <c r="D51" s="16" t="s">
+        <v>112</v>
       </c>
       <c r="E51" s="15" t="s">
-        <v>177</v>
+        <v>119</v>
       </c>
       <c r="G51" s="15">
-        <v>6.5</v>
+        <v>2000</v>
+      </c>
+      <c r="H51" s="15" t="s">
+        <v>124</v>
       </c>
       <c r="I51" s="15" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
+        <v>80</v>
+      </c>
+      <c r="K51" s="15" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A52" s="15" t="s">
         <v>174</v>
       </c>
@@ -2426,23 +2455,46 @@
         <v>166</v>
       </c>
       <c r="E52" s="15" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G52" s="15">
-        <v>8.5</v>
+        <v>6.5</v>
       </c>
       <c r="I52" s="15" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="I62" s="15" t="s">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A53" s="15" t="s">
+        <v>174</v>
+      </c>
+      <c r="B53" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C53" s="15" t="s">
+        <v>166</v>
+      </c>
+      <c r="D53" s="15" t="s">
+        <v>166</v>
+      </c>
+      <c r="E53" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="G53" s="15">
+        <v>8.5</v>
+      </c>
+      <c r="I53" s="15" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="I63" s="15" t="s">
         <v>33</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="I45" r:id="rId1"/>
+    <hyperlink ref="I46" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId2"/>
@@ -2450,25 +2502,25 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:G37"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.109375" style="15"/>
-    <col min="2" max="2" width="26.109375" style="15" customWidth="1"/>
-    <col min="3" max="3" width="26.44140625" style="15" customWidth="1"/>
-    <col min="4" max="4" width="16.5546875" style="15" customWidth="1"/>
+    <col min="1" max="1" width="9.140625" style="15"/>
+    <col min="2" max="2" width="26.140625" style="15" customWidth="1"/>
+    <col min="3" max="3" width="26.42578125" style="15" customWidth="1"/>
+    <col min="4" max="4" width="16.5703125" style="15" customWidth="1"/>
     <col min="5" max="5" width="18" style="24" customWidth="1"/>
-    <col min="6" max="6" width="31.33203125" customWidth="1"/>
-    <col min="7" max="7" width="33.6640625" customWidth="1"/>
+    <col min="6" max="6" width="31.28515625" customWidth="1"/>
+    <col min="7" max="7" width="33.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="25" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="2" spans="1:7" s="19" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" s="19" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A2" s="26" t="s">
         <v>66</v>
       </c>
@@ -2491,7 +2543,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="15" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
         <v>73</v>
       </c>
@@ -2511,7 +2563,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="15" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="15" t="s">
         <v>73</v>
       </c>
@@ -2534,7 +2586,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="15" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="15" t="s">
         <v>73</v>
       </c>
@@ -2554,7 +2606,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="15" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="15" t="s">
         <v>73</v>
       </c>
@@ -2577,7 +2629,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="15" t="s">
         <v>73</v>
       </c>
@@ -2597,7 +2649,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="15" t="s">
         <v>73</v>
       </c>
@@ -2620,7 +2672,7 @@
         <v>0.316</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="15" t="s">
         <v>73</v>
       </c>
@@ -2640,7 +2692,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="15" t="s">
         <v>73</v>
       </c>
@@ -2663,7 +2715,7 @@
         <v>0.86</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="15" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="15" t="s">
         <v>73</v>
       </c>
@@ -2683,7 +2735,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="15" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="15" t="s">
         <v>73</v>
       </c>
@@ -2706,7 +2758,7 @@
         <v>0.96</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="15" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="15" t="s">
         <v>73</v>
       </c>
@@ -2726,7 +2778,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="15" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="15" t="s">
         <v>73</v>
       </c>
@@ -2749,7 +2801,7 @@
         <v>0.96</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="15" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="15" t="s">
         <v>73</v>
       </c>
@@ -2769,7 +2821,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="15" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="15" t="s">
         <v>73</v>
       </c>
@@ -2792,7 +2844,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="15" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="15" t="s">
         <v>73</v>
       </c>
@@ -2812,7 +2864,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="15" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="15" t="s">
         <v>73</v>
       </c>
@@ -2835,7 +2887,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="15" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="15" t="s">
         <v>73</v>
       </c>
@@ -2853,7 +2905,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="15" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="15" t="s">
         <v>73</v>
       </c>
@@ -2874,7 +2926,7 @@
         <v>0.998</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="15" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="15" t="s">
         <v>73</v>
       </c>
@@ -2892,7 +2944,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="15" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="15" t="s">
         <v>73</v>
       </c>
@@ -2913,7 +2965,7 @@
         <v>0.997</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="15" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="15" t="s">
         <v>73</v>
       </c>
@@ -2931,7 +2983,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="15" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="15" t="s">
         <v>73</v>
       </c>
@@ -2952,7 +3004,7 @@
         <v>0.92200000000000004</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="15" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="15" t="s">
         <v>73</v>
       </c>
@@ -2970,7 +3022,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="15" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="15" t="s">
         <v>73</v>
       </c>
@@ -2991,7 +3043,7 @@
         <v>0.92200000000000004</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="15" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="15" t="s">
         <v>73</v>
       </c>
@@ -3009,7 +3061,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="15" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="15" t="s">
         <v>73</v>
       </c>
@@ -3030,7 +3082,7 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="15" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
         <v>73</v>
       </c>
@@ -3050,7 +3102,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="15" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="15" t="s">
         <v>73</v>
       </c>
@@ -3073,7 +3125,7 @@
         <v>0.97799999999999998</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="15" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="15" t="s">
         <v>73</v>
       </c>
@@ -3093,7 +3145,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="15" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="15" t="s">
         <v>73</v>
       </c>
@@ -3116,19 +3168,19 @@
         <v>0.98599999999999999</v>
       </c>
     </row>
-    <row r="33" spans="3:3" ht="15" x14ac:dyDescent="0.3">
+    <row r="33" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C33" s="16"/>
     </row>
-    <row r="34" spans="3:3" ht="15" x14ac:dyDescent="0.3">
+    <row r="34" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C34" s="16"/>
     </row>
-    <row r="35" spans="3:3" ht="15" x14ac:dyDescent="0.3">
+    <row r="35" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C35" s="16"/>
     </row>
-    <row r="36" spans="3:3" ht="15" x14ac:dyDescent="0.3">
+    <row r="36" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C36" s="16"/>
     </row>
-    <row r="37" spans="3:3" ht="15" x14ac:dyDescent="0.3">
+    <row r="37" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C37" s="16"/>
     </row>
   </sheetData>
@@ -3137,22 +3189,22 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:L12"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="13.33203125" customWidth="1"/>
-    <col min="3" max="3" width="15.5546875" customWidth="1"/>
-    <col min="4" max="4" width="18.33203125" customWidth="1"/>
-    <col min="7" max="7" width="22.88671875" customWidth="1"/>
+    <col min="1" max="2" width="13.28515625" customWidth="1"/>
+    <col min="3" max="3" width="15.5703125" customWidth="1"/>
+    <col min="4" max="4" width="18.28515625" customWidth="1"/>
+    <col min="7" max="7" width="22.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="2" spans="1:12" s="12" customFormat="1" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" s="12" customFormat="1" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A2" s="26" t="s">
         <v>68</v>
       </c>
@@ -3178,7 +3230,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>82</v>
       </c>
@@ -3192,7 +3244,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>86</v>
       </c>
@@ -3221,7 +3273,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>143</v>
       </c>
@@ -3247,7 +3299,7 @@
         <v>0.86</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>151</v>
       </c>
@@ -3258,7 +3310,7 @@
         <v>0.96199999999999997</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>88</v>
       </c>
@@ -3284,7 +3336,7 @@
         <v>0.96</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>92</v>
       </c>
@@ -3310,7 +3362,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>152</v>
       </c>
@@ -3321,7 +3373,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>94</v>
       </c>
@@ -3347,7 +3399,7 @@
         <v>0.997</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>101</v>
       </c>
@@ -3364,7 +3416,7 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>112</v>
       </c>
@@ -3397,56 +3449,56 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:A10"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>158</v>
       </c>
@@ -3457,16 +3509,16 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A6:G8"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="G6" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>134</v>
       </c>
@@ -3477,22 +3529,22 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:L36"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="27.33203125" customWidth="1"/>
-    <col min="3" max="3" width="28.5546875" customWidth="1"/>
-    <col min="4" max="4" width="33.33203125" customWidth="1"/>
+    <col min="2" max="2" width="27.28515625" customWidth="1"/>
+    <col min="3" max="3" width="28.5703125" customWidth="1"/>
+    <col min="4" max="4" width="33.28515625" customWidth="1"/>
     <col min="6" max="6" width="50" customWidth="1"/>
-    <col min="7" max="7" width="24.6640625" customWidth="1"/>
-    <col min="8" max="8" width="7.6640625" customWidth="1"/>
-    <col min="9" max="9" width="31.5546875" customWidth="1"/>
-    <col min="10" max="10" width="12.5546875" customWidth="1"/>
-    <col min="11" max="11" width="19.44140625" customWidth="1"/>
+    <col min="7" max="7" width="24.7109375" customWidth="1"/>
+    <col min="8" max="8" width="7.7109375" customWidth="1"/>
+    <col min="9" max="9" width="31.5703125" customWidth="1"/>
+    <col min="10" max="10" width="12.5703125" customWidth="1"/>
+    <col min="11" max="11" width="19.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="19" customFormat="1" ht="76.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" s="19" customFormat="1" ht="76.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
         <v>129</v>
       </c>
@@ -3528,15 +3580,15 @@
         <v>65</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="16.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="1"/>
       <c r="C2" s="6"/>
     </row>
-    <row r="3" spans="1:12" ht="16.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="1"/>
       <c r="C3" s="6"/>
     </row>
-    <row r="4" spans="1:12" ht="16.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>130</v>
       </c>
@@ -3556,7 +3608,7 @@
       <c r="K4" s="2"/>
       <c r="L4" s="2"/>
     </row>
-    <row r="5" spans="1:12" ht="18.600000000000001" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:12" ht="19.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>130</v>
       </c>
@@ -3578,7 +3630,7 @@
       <c r="K5" s="2"/>
       <c r="L5" s="2"/>
     </row>
-    <row r="6" spans="1:12" ht="16.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>130</v>
       </c>
@@ -3598,7 +3650,7 @@
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
     </row>
-    <row r="7" spans="1:12" ht="16.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>130</v>
       </c>
@@ -3634,7 +3686,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="16.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>130</v>
       </c>
@@ -3654,7 +3706,7 @@
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
     </row>
-    <row r="9" spans="1:12" ht="16.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>130</v>
       </c>
@@ -3676,7 +3728,7 @@
       <c r="K9" s="2"/>
       <c r="L9" s="2"/>
     </row>
-    <row r="10" spans="1:12" ht="16.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>130</v>
       </c>
@@ -3694,7 +3746,7 @@
       <c r="K10" s="2"/>
       <c r="L10" s="2"/>
     </row>
-    <row r="11" spans="1:12" ht="16.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>133</v>
       </c>
@@ -3730,7 +3782,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="16.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>130</v>
       </c>
@@ -3758,7 +3810,7 @@
       <c r="K12" s="2"/>
       <c r="L12" s="2"/>
     </row>
-    <row r="13" spans="1:12" ht="16.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>130</v>
       </c>
@@ -3780,7 +3832,7 @@
       <c r="K13" s="2"/>
       <c r="L13" s="2"/>
     </row>
-    <row r="14" spans="1:12" ht="16.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>130</v>
       </c>
@@ -3800,7 +3852,7 @@
       <c r="K14" s="2"/>
       <c r="L14" s="2"/>
     </row>
-    <row r="15" spans="1:12" ht="16.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>133</v>
       </c>
@@ -3834,7 +3886,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="16.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>130</v>
       </c>
@@ -3860,7 +3912,7 @@
       <c r="K16" s="2"/>
       <c r="L16" s="2"/>
     </row>
-    <row r="17" spans="1:12" ht="16.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>130</v>
       </c>
@@ -3878,7 +3930,7 @@
       <c r="K17" s="2"/>
       <c r="L17" s="2"/>
     </row>
-    <row r="18" spans="1:12" s="23" customFormat="1" ht="16.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:12" s="23" customFormat="1" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>133</v>
       </c>
@@ -3912,7 +3964,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="19" spans="1:12" ht="16.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>130</v>
       </c>
@@ -3936,7 +3988,7 @@
       <c r="K19" s="2"/>
       <c r="L19" s="2"/>
     </row>
-    <row r="20" spans="1:12" ht="16.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>130</v>
       </c>
@@ -3956,7 +4008,7 @@
       <c r="K20" s="2"/>
       <c r="L20" s="2"/>
     </row>
-    <row r="21" spans="1:12" ht="16.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>130</v>
       </c>
@@ -3976,7 +4028,7 @@
       <c r="K21" s="2"/>
       <c r="L21" s="2"/>
     </row>
-    <row r="22" spans="1:12" ht="16.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>133</v>
       </c>
@@ -4010,7 +4062,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="23" spans="1:12" ht="16.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>130</v>
       </c>
@@ -4028,7 +4080,7 @@
       <c r="K23" s="2"/>
       <c r="L23" s="2"/>
     </row>
-    <row r="24" spans="1:12" ht="16.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>130</v>
       </c>
@@ -4046,7 +4098,7 @@
       <c r="K24" s="2"/>
       <c r="L24" s="2"/>
     </row>
-    <row r="25" spans="1:12" ht="16.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>130</v>
       </c>
@@ -4074,7 +4126,7 @@
       <c r="K25" s="2"/>
       <c r="L25" s="2"/>
     </row>
-    <row r="26" spans="1:12" ht="16.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>130</v>
       </c>
@@ -4092,7 +4144,7 @@
       <c r="K26" s="2"/>
       <c r="L26" s="2"/>
     </row>
-    <row r="27" spans="1:12" ht="16.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>133</v>
       </c>
@@ -4128,7 +4180,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="28" spans="1:12" ht="16.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>130</v>
       </c>
@@ -4148,7 +4200,7 @@
       <c r="K28" s="2"/>
       <c r="L28" s="2"/>
     </row>
-    <row r="29" spans="1:12" ht="16.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>130</v>
       </c>
@@ -4168,7 +4220,7 @@
       <c r="K29" s="2"/>
       <c r="L29" s="2"/>
     </row>
-    <row r="30" spans="1:12" ht="16.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>130</v>
       </c>
@@ -4188,7 +4240,7 @@
       <c r="K30" s="2"/>
       <c r="L30" s="2"/>
     </row>
-    <row r="31" spans="1:12" ht="31.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:12" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>133</v>
       </c>
@@ -4224,7 +4276,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="32" spans="1:12" ht="16.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>133</v>
       </c>
@@ -4250,7 +4302,7 @@
       <c r="K32" s="11"/>
       <c r="L32" s="2"/>
     </row>
-    <row r="33" spans="1:12" ht="16.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>130</v>
       </c>
@@ -4270,7 +4322,7 @@
       <c r="K33" s="2"/>
       <c r="L33" s="2"/>
     </row>
-    <row r="34" spans="1:12" ht="16.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>130</v>
       </c>
@@ -4288,7 +4340,7 @@
       <c r="K34" s="2"/>
       <c r="L34" s="2"/>
     </row>
-    <row r="35" spans="1:12" ht="16.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>133</v>
       </c>
@@ -4322,7 +4374,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="36" spans="1:12" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
+    <row r="36" spans="1:12" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>

--- a/other/input/regulatory_limits/master_reg_limits.xlsx
+++ b/other/input/regulatory_limits/master_reg_limits.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28324"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="20" documentId="11_F3222DCEA08A4C9A6976DB97F14DE766E6606446" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8DC640F5-1A12-4723-AF93-54493970D9DD}"/>
+  <xr:revisionPtr revIDLastSave="22" documentId="11_F3222DCEA08A4C9A6976DB97F14DE766E6606446" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{33C3B079-7004-419E-8489-F8A9E5413390}"/>
   <bookViews>
-    <workbookView xWindow="31875" yWindow="1065" windowWidth="21600" windowHeight="11295" tabRatio="795" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30840" yWindow="-1335" windowWidth="21600" windowHeight="11295" tabRatio="795" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ReadMe" sheetId="8" r:id="rId1"/>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="732" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="724" uniqueCount="185">
   <si>
     <t>alkalinity (as CaCO3)</t>
   </si>
@@ -333,9 +333,6 @@
   </si>
   <si>
     <t>Fecal Coliform</t>
-  </si>
-  <si>
-    <t>Iron</t>
   </si>
   <si>
     <t>Lead</t>
@@ -617,6 +614,9 @@
   </si>
   <si>
     <t>BM 20250115</t>
+  </si>
+  <si>
+    <t>Benzene, toluene, ethyl benzene, xylenes mix</t>
   </si>
 </sst>
 </file>
@@ -1150,12 +1150,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="3" spans="1:1" ht="18" x14ac:dyDescent="0.25">
       <c r="A3" s="29" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
   </sheetData>
@@ -1165,7 +1165,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:P63"/>
+  <dimension ref="A1:P62"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.85546875" style="15" customWidth="1"/>
@@ -1183,7 +1183,7 @@
   <sheetData>
     <row r="1" spans="1:16" s="14" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="14" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B1" s="14" t="s">
         <v>66</v>
@@ -1201,16 +1201,16 @@
         <v>72</v>
       </c>
       <c r="G1" s="14" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H1" s="14" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I1" s="14" t="s">
         <v>79</v>
       </c>
       <c r="J1" s="14" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="K1" s="14" t="s">
         <v>75</v>
@@ -1218,7 +1218,7 @@
     </row>
     <row r="2" spans="1:16" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A2" s="15" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B2" s="15" t="s">
         <v>73</v>
@@ -1236,7 +1236,7 @@
         <v>750</v>
       </c>
       <c r="H2" s="15" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I2" s="15" t="s">
         <v>80</v>
@@ -1247,7 +1247,7 @@
     </row>
     <row r="3" spans="1:16" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A3" s="15" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B3" s="15" t="s">
         <v>73</v>
@@ -1265,13 +1265,13 @@
         <v>87</v>
       </c>
       <c r="H3" s="15" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I3" s="15" t="s">
         <v>80</v>
       </c>
       <c r="J3" s="15" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K3" s="15" t="s">
         <v>76</v>
@@ -1279,7 +1279,7 @@
     </row>
     <row r="4" spans="1:16" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A4" s="15" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B4" s="15" t="s">
         <v>73</v>
@@ -1291,13 +1291,13 @@
         <v>81</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G4" s="15">
         <v>6</v>
       </c>
       <c r="H4" s="15" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I4" s="15" t="s">
         <v>80</v>
@@ -1308,7 +1308,7 @@
     </row>
     <row r="5" spans="1:16" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A5" s="15" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B5" s="15" t="s">
         <v>73</v>
@@ -1320,13 +1320,13 @@
         <v>81</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G5" s="15">
         <v>14</v>
       </c>
       <c r="H5" s="15" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I5" s="15" t="s">
         <v>80</v>
@@ -1337,7 +1337,7 @@
     </row>
     <row r="6" spans="1:16" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A6" s="15" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B6" s="15" t="s">
         <v>73</v>
@@ -1349,13 +1349,13 @@
         <v>81</v>
       </c>
       <c r="E6" s="15" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G6" s="15">
         <v>4300</v>
       </c>
       <c r="H6" s="15" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I6" s="15" t="s">
         <v>80</v>
@@ -1366,7 +1366,7 @@
     </row>
     <row r="7" spans="1:16" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A7" s="15" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B7" s="15" t="s">
         <v>73</v>
@@ -1378,24 +1378,24 @@
         <v>82</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G7" s="15">
         <v>10</v>
       </c>
       <c r="H7" s="15" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I7" s="15" t="s">
         <v>80</v>
       </c>
       <c r="K7" s="15" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="8" spans="1:16" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A8" s="15" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B8" s="15" t="s">
         <v>73</v>
@@ -1407,24 +1407,24 @@
         <v>82</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G8" s="15">
         <v>50</v>
       </c>
       <c r="H8" s="15" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I8" s="15" t="s">
         <v>80</v>
       </c>
       <c r="K8" s="15" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="9" spans="1:16" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A9" s="15" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B9" s="15" t="s">
         <v>73</v>
@@ -1436,24 +1436,24 @@
         <v>82</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G9" s="15">
         <v>100</v>
       </c>
       <c r="H9" s="15" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I9" s="15" t="s">
         <v>80</v>
       </c>
       <c r="K9" s="15" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="10" spans="1:16" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A10" s="15" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B10" s="15" t="s">
         <v>73</v>
@@ -1465,35 +1465,35 @@
         <v>83</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G10" s="15">
         <v>2000</v>
       </c>
       <c r="H10" s="15" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I10" s="15" t="s">
         <v>80</v>
       </c>
       <c r="K10" s="15" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="11" spans="1:16" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A11" s="15" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D11" s="16" t="s">
         <v>84</v>
       </c>
       <c r="K11" s="15" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="12" spans="1:16" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A12" s="15" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B12" s="15" t="s">
         <v>73</v>
@@ -1505,19 +1505,19 @@
         <v>85</v>
       </c>
       <c r="E12" s="15" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G12" s="15">
         <v>4</v>
       </c>
       <c r="H12" s="15" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I12" s="15" t="s">
         <v>80</v>
       </c>
       <c r="K12" s="15" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="P12" s="15" t="s">
         <v>33</v>
@@ -1525,7 +1525,7 @@
     </row>
     <row r="13" spans="1:16" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A13" s="15" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B13" s="15" t="s">
         <v>73</v>
@@ -1537,24 +1537,24 @@
         <v>85</v>
       </c>
       <c r="E13" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G13" s="15">
         <v>100</v>
       </c>
       <c r="H13" s="15" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I13" s="15" t="s">
         <v>80</v>
       </c>
       <c r="K13" s="15" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="14" spans="1:16" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A14" s="15" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B14" s="15" t="s">
         <v>73</v>
@@ -1563,59 +1563,59 @@
         <v>6</v>
       </c>
       <c r="D14" s="16" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G14" s="15">
         <v>750</v>
       </c>
       <c r="H14" s="15" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I14" s="15" t="s">
         <v>80</v>
       </c>
       <c r="K14" s="15" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A15" s="15" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B15" s="15" t="s">
         <v>73</v>
       </c>
       <c r="C15" s="30" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D15" s="30" t="s">
-        <v>162</v>
+        <v>184</v>
       </c>
       <c r="E15" s="15" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G15" s="15">
         <v>10</v>
       </c>
       <c r="H15" s="15" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I15" s="15" t="s">
+        <v>158</v>
+      </c>
+      <c r="J15" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="K15" s="15" t="s">
         <v>159</v>
-      </c>
-      <c r="J15" s="15" t="s">
-        <v>161</v>
-      </c>
-      <c r="K15" s="15" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="16" spans="1:16" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A16" s="15" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B16" s="15" t="s">
         <v>73</v>
@@ -1627,24 +1627,24 @@
         <v>86</v>
       </c>
       <c r="E16" s="15" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G16" s="15">
         <v>5</v>
       </c>
       <c r="H16" s="15" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I16" s="15" t="s">
         <v>80</v>
       </c>
       <c r="K16" s="15" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A17" s="15" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B17" s="15" t="s">
         <v>73</v>
@@ -1656,24 +1656,24 @@
         <v>86</v>
       </c>
       <c r="E17" s="15" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G17" s="15">
         <v>10</v>
       </c>
       <c r="H17" s="15" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I17" s="15" t="s">
         <v>80</v>
       </c>
       <c r="K17" s="15" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A18" s="15" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B18" s="15" t="s">
         <v>73</v>
@@ -1685,24 +1685,24 @@
         <v>86</v>
       </c>
       <c r="E18" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G18" s="15">
         <v>10</v>
       </c>
       <c r="H18" s="15" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I18" s="15" t="s">
         <v>80</v>
       </c>
       <c r="K18" s="15" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19" s="15" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B19" s="15" t="s">
         <v>73</v>
@@ -1714,27 +1714,27 @@
         <v>70</v>
       </c>
       <c r="E19" s="15" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G19" s="15">
         <v>100</v>
       </c>
       <c r="H19" s="15" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I19" s="15" t="s">
         <v>80</v>
       </c>
       <c r="J19" s="15" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="K19" s="15" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20" s="15" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B20" s="15" t="s">
         <v>73</v>
@@ -1746,24 +1746,24 @@
         <v>70</v>
       </c>
       <c r="E20" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G20" s="15">
         <v>100</v>
       </c>
       <c r="H20" s="15" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I20" s="15" t="s">
         <v>80</v>
       </c>
       <c r="K20" s="15" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A21" s="15" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B21" s="15" t="s">
         <v>73</v>
@@ -1775,24 +1775,24 @@
         <v>87</v>
       </c>
       <c r="E21" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G21" s="15">
         <v>50</v>
       </c>
       <c r="H21" s="15" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I21" s="15" t="s">
         <v>80</v>
       </c>
       <c r="K21" s="15" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A22" s="15" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B22" s="15" t="s">
         <v>73</v>
@@ -1804,35 +1804,35 @@
         <v>88</v>
       </c>
       <c r="E22" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G22" s="15">
         <v>200</v>
       </c>
       <c r="H22" s="15" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I22" s="15" t="s">
         <v>80</v>
       </c>
       <c r="K22" s="15" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="23" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A23" s="15" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D23" s="16" t="s">
         <v>89</v>
       </c>
       <c r="K23" s="15" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="24" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A24" s="15" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B24" s="15" t="s">
         <v>73</v>
@@ -1841,79 +1841,79 @@
         <v>90</v>
       </c>
       <c r="E24" s="15" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G24" s="15">
         <v>400</v>
       </c>
       <c r="H24" s="15" t="s">
+        <v>181</v>
+      </c>
+      <c r="I24" s="15" t="s">
         <v>182</v>
       </c>
-      <c r="I24" s="15" t="s">
+      <c r="K24" s="15" t="s">
         <v>183</v>
-      </c>
-      <c r="K24" s="15" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="25" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A25" s="15" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B25" s="15" t="s">
         <v>73</v>
       </c>
       <c r="D25" s="16" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E25" s="15" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G25" s="15">
         <v>31</v>
       </c>
       <c r="H25" s="15" t="s">
+        <v>181</v>
+      </c>
+      <c r="I25" s="15" t="s">
         <v>182</v>
       </c>
-      <c r="I25" s="15" t="s">
+      <c r="K25" s="15" t="s">
         <v>183</v>
       </c>
-      <c r="K25" s="15" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
+    </row>
+    <row r="26" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A26" s="15" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B26" s="15" t="s">
         <v>73</v>
       </c>
       <c r="C26" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="D26" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="D26" s="16" t="s">
         <v>91</v>
       </c>
       <c r="E26" s="15" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="G26" s="15">
-        <v>5000</v>
+        <v>50</v>
       </c>
       <c r="H26" s="15" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I26" s="15" t="s">
         <v>80</v>
       </c>
       <c r="K26" s="15" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="27" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A27" s="15" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B27" s="15" t="s">
         <v>73</v>
@@ -1922,88 +1922,88 @@
         <v>19</v>
       </c>
       <c r="D27" s="16" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E27" s="15" t="s">
         <v>118</v>
       </c>
+      <c r="F27" s="15" t="s">
+        <v>33</v>
+      </c>
       <c r="G27" s="15">
-        <v>50</v>
+        <v>5000</v>
       </c>
       <c r="H27" s="15" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I27" s="15" t="s">
         <v>80</v>
       </c>
       <c r="K27" s="15" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="28" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A28" s="15" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B28" s="15" t="s">
         <v>73</v>
       </c>
       <c r="C28" s="15" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D28" s="16" t="s">
         <v>92</v>
       </c>
       <c r="E28" s="15" t="s">
-        <v>119</v>
-      </c>
-      <c r="F28" s="15" t="s">
-        <v>33</v>
+        <v>118</v>
       </c>
       <c r="G28" s="15">
-        <v>5000</v>
+        <v>10</v>
       </c>
       <c r="H28" s="15" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I28" s="15" t="s">
         <v>80</v>
       </c>
       <c r="K28" s="15" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="29" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A29" s="15" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B29" s="15" t="s">
         <v>73</v>
       </c>
       <c r="C29" s="15" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D29" s="16" t="s">
         <v>93</v>
       </c>
       <c r="E29" s="15" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="G29" s="15">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="H29" s="15" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I29" s="15" t="s">
         <v>80</v>
       </c>
       <c r="K29" s="15" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="30" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A30" s="15" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B30" s="15" t="s">
         <v>73</v>
@@ -2012,127 +2012,127 @@
         <v>24</v>
       </c>
       <c r="D30" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E30" s="15" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="G30" s="15">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="H30" s="15" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I30" s="15" t="s">
         <v>80</v>
       </c>
       <c r="K30" s="15" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="31" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A31" s="15" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B31" s="15" t="s">
         <v>73</v>
       </c>
       <c r="C31" s="15" t="s">
-        <v>24</v>
+        <v>125</v>
       </c>
       <c r="D31" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="E31" s="15" t="s">
+      <c r="K31" s="15" t="s">
         <v>119</v>
-      </c>
-      <c r="G31" s="15">
-        <v>200</v>
-      </c>
-      <c r="H31" s="15" t="s">
-        <v>124</v>
-      </c>
-      <c r="I31" s="15" t="s">
-        <v>80</v>
-      </c>
-      <c r="K31" s="15" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="32" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A32" s="15" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B32" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="C32" s="15" t="s">
-        <v>126</v>
+      <c r="C32" s="16" t="s">
+        <v>95</v>
       </c>
       <c r="D32" s="16" t="s">
         <v>95</v>
       </c>
+      <c r="I32" s="15" t="s">
+        <v>33</v>
+      </c>
       <c r="K32" s="15" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="33" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A33" s="15" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B33" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="C33" s="16" t="s">
-        <v>96</v>
+      <c r="C33" s="15" t="s">
+        <v>126</v>
       </c>
       <c r="D33" s="16" t="s">
         <v>96</v>
       </c>
-      <c r="I33" s="15" t="s">
-        <v>33</v>
-      </c>
       <c r="K33" s="15" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="34" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A34" s="15" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B34" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="C34" s="15" t="s">
+      <c r="C34" s="13" t="s">
         <v>127</v>
       </c>
       <c r="D34" s="16" t="s">
         <v>97</v>
       </c>
       <c r="K34" s="15" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="35" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A35" s="15" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="B35" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="C35" s="13" t="s">
-        <v>128</v>
+      <c r="C35" s="15" t="s">
+        <v>28</v>
       </c>
       <c r="D35" s="16" t="s">
         <v>98</v>
       </c>
+      <c r="E35" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="G35" s="15">
+        <v>50</v>
+      </c>
+      <c r="H35" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="I35" s="15" t="s">
+        <v>80</v>
+      </c>
       <c r="K35" s="15" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="36" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A36" s="15" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B36" s="15" t="s">
         <v>73</v>
@@ -2141,27 +2141,27 @@
         <v>28</v>
       </c>
       <c r="D36" s="16" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E36" s="15" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G36" s="15">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="H36" s="15" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I36" s="15" t="s">
         <v>80</v>
       </c>
       <c r="K36" s="15" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="37" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A37" s="15" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B37" s="15" t="s">
         <v>73</v>
@@ -2170,184 +2170,166 @@
         <v>28</v>
       </c>
       <c r="D37" s="16" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E37" s="15" t="s">
         <v>118</v>
       </c>
       <c r="G37" s="15">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H37" s="15" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I37" s="15" t="s">
         <v>80</v>
       </c>
       <c r="K37" s="15" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="38" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A38" s="15" t="s">
-        <v>169</v>
-      </c>
-      <c r="B38" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="C38" s="15" t="s">
-        <v>28</v>
+        <v>168</v>
       </c>
       <c r="D38" s="16" t="s">
         <v>99</v>
       </c>
-      <c r="E38" s="15" t="s">
+      <c r="K38" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="G38" s="15">
-        <v>20</v>
-      </c>
-      <c r="H38" s="15" t="s">
-        <v>124</v>
-      </c>
-      <c r="I38" s="15" t="s">
-        <v>80</v>
-      </c>
-      <c r="K38" s="15" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="39" spans="1:11" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A39" s="15" t="s">
-        <v>169</v>
+        <v>168</v>
+      </c>
+      <c r="B39" s="15" t="s">
+        <v>73</v>
       </c>
       <c r="D39" s="16" t="s">
         <v>100</v>
       </c>
+      <c r="J39" s="31" t="s">
+        <v>162</v>
+      </c>
       <c r="K39" s="15" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11" ht="63.75" x14ac:dyDescent="0.2">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A40" s="15" t="s">
-        <v>169</v>
-      </c>
-      <c r="B40" s="15" t="s">
-        <v>73</v>
+        <v>168</v>
       </c>
       <c r="D40" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="J40" s="31" t="s">
-        <v>163</v>
-      </c>
       <c r="K40" s="15" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="41" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A41" s="15" t="s">
-        <v>169</v>
+        <v>168</v>
+      </c>
+      <c r="B41" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C41" s="15" t="s">
+        <v>30</v>
       </c>
       <c r="D41" s="16" t="s">
         <v>102</v>
       </c>
+      <c r="E41" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="G41" s="15">
+        <v>2</v>
+      </c>
+      <c r="H41" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="I41" s="15" t="s">
+        <v>80</v>
+      </c>
       <c r="K41" s="15" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="42" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A42" s="15" t="s">
-        <v>169</v>
-      </c>
-      <c r="B42" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="C42" s="15" t="s">
-        <v>30</v>
+        <v>168</v>
       </c>
       <c r="D42" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="E42" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="G42" s="15">
-        <v>2</v>
-      </c>
-      <c r="H42" s="15" t="s">
-        <v>124</v>
-      </c>
-      <c r="I42" s="15" t="s">
-        <v>80</v>
-      </c>
       <c r="K42" s="15" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="43" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A43" s="15" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D43" s="16" t="s">
         <v>104</v>
       </c>
       <c r="K43" s="15" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="44" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A44" s="15" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D44" s="16" t="s">
         <v>105</v>
       </c>
+      <c r="J44" s="15" t="s">
+        <v>163</v>
+      </c>
       <c r="K44" s="15" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="45" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" ht="15" x14ac:dyDescent="0.25">
       <c r="A45" s="15" t="s">
-        <v>171</v>
+        <v>172</v>
+      </c>
+      <c r="B45" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C45" s="15" t="s">
+        <v>164</v>
       </c>
       <c r="D45" s="16" t="s">
         <v>106</v>
       </c>
-      <c r="J45" s="15" t="s">
-        <v>164</v>
+      <c r="E45" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="G45" s="15">
+        <v>10000</v>
+      </c>
+      <c r="H45" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="I45" s="32" t="s">
+        <v>166</v>
       </c>
       <c r="K45" s="15" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="46" spans="1:11" ht="15" x14ac:dyDescent="0.25">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A46" s="15" t="s">
-        <v>173</v>
-      </c>
-      <c r="B46" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="C46" s="15" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="D46" s="16" t="s">
         <v>107</v>
       </c>
-      <c r="E46" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="G46" s="15">
-        <v>10000</v>
-      </c>
-      <c r="H46" s="15" t="s">
-        <v>124</v>
-      </c>
-      <c r="I46" s="32" t="s">
-        <v>167</v>
-      </c>
       <c r="K46" s="15" t="s">
-        <v>160</v>
+        <v>119</v>
       </c>
     </row>
     <row r="47" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
@@ -2358,143 +2340,132 @@
         <v>108</v>
       </c>
       <c r="K47" s="15" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="48" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A48" s="15" t="s">
-        <v>174</v>
+        <v>168</v>
+      </c>
+      <c r="B48" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C48" s="15" t="s">
+        <v>31</v>
       </c>
       <c r="D48" s="16" t="s">
         <v>109</v>
       </c>
+      <c r="E48" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="G48" s="15">
+        <v>100</v>
+      </c>
+      <c r="H48" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="I48" s="15" t="s">
+        <v>80</v>
+      </c>
       <c r="K48" s="15" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="49" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A49" s="15" t="s">
-        <v>169</v>
-      </c>
-      <c r="B49" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="C49" s="15" t="s">
-        <v>31</v>
+        <v>170</v>
       </c>
       <c r="D49" s="16" t="s">
         <v>110</v>
       </c>
-      <c r="E49" s="15" t="s">
+      <c r="K49" s="15" t="s">
         <v>119</v>
-      </c>
-      <c r="G49" s="15">
-        <v>100</v>
-      </c>
-      <c r="H49" s="15" t="s">
-        <v>124</v>
-      </c>
-      <c r="I49" s="15" t="s">
-        <v>80</v>
-      </c>
-      <c r="K49" s="15" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="50" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A50" s="15" t="s">
-        <v>171</v>
+        <v>168</v>
+      </c>
+      <c r="B50" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C50" s="15" t="s">
+        <v>32</v>
       </c>
       <c r="D50" s="16" t="s">
         <v>111</v>
       </c>
+      <c r="E50" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="G50" s="15">
+        <v>2000</v>
+      </c>
+      <c r="H50" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="I50" s="15" t="s">
+        <v>80</v>
+      </c>
       <c r="K50" s="15" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="51" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A51" s="15" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="B51" s="15" t="s">
         <v>73</v>
       </c>
       <c r="C51" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="D51" s="16" t="s">
-        <v>112</v>
+        <v>165</v>
+      </c>
+      <c r="D51" s="15" t="s">
+        <v>165</v>
       </c>
       <c r="E51" s="15" t="s">
-        <v>119</v>
+        <v>176</v>
       </c>
       <c r="G51" s="15">
-        <v>2000</v>
-      </c>
-      <c r="H51" s="15" t="s">
-        <v>124</v>
+        <v>6.5</v>
       </c>
       <c r="I51" s="15" t="s">
-        <v>80</v>
-      </c>
-      <c r="K51" s="15" t="s">
-        <v>120</v>
+        <v>167</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A52" s="15" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B52" s="15" t="s">
         <v>73</v>
       </c>
       <c r="C52" s="15" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D52" s="15" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E52" s="15" t="s">
         <v>177</v>
       </c>
       <c r="G52" s="15">
-        <v>6.5</v>
+        <v>8.5</v>
       </c>
       <c r="I52" s="15" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A53" s="15" t="s">
-        <v>174</v>
-      </c>
-      <c r="B53" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="C53" s="15" t="s">
-        <v>166</v>
-      </c>
-      <c r="D53" s="15" t="s">
-        <v>166</v>
-      </c>
-      <c r="E53" s="15" t="s">
-        <v>178</v>
-      </c>
-      <c r="G53" s="15">
-        <v>8.5</v>
-      </c>
-      <c r="I53" s="15" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="I63" s="15" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="I62" s="15" t="s">
         <v>33</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="I46" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
+    <hyperlink ref="I45" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId2"/>
@@ -2517,7 +2488,7 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="25" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="2" spans="1:7" s="19" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
@@ -2534,13 +2505,13 @@
         <v>67</v>
       </c>
       <c r="E2" s="27" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F2" s="26" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G2" s="26" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -2557,7 +2528,7 @@
         <v>71</v>
       </c>
       <c r="E3" s="24" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F3" s="28" t="s">
         <v>36</v>
@@ -2577,10 +2548,10 @@
         <v>71</v>
       </c>
       <c r="E4" s="24" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F4" s="28" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G4" t="s">
         <v>50</v>
@@ -2600,7 +2571,7 @@
         <v>74</v>
       </c>
       <c r="E5" s="24" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F5" s="28" t="s">
         <v>51</v>
@@ -2620,7 +2591,7 @@
         <v>74</v>
       </c>
       <c r="E6" s="24" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F6" s="28" t="s">
         <v>51</v>
@@ -2637,13 +2608,13 @@
         <v>11</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D7" s="15" t="s">
         <v>71</v>
       </c>
       <c r="E7" s="24" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F7" t="s">
         <v>37</v>
@@ -2657,13 +2628,13 @@
         <v>11</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D8" s="15" t="s">
         <v>71</v>
       </c>
       <c r="E8" s="24" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F8" t="s">
         <v>37</v>
@@ -2680,13 +2651,13 @@
         <v>11</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D9" s="15" t="s">
         <v>74</v>
       </c>
       <c r="E9" s="24" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F9" t="s">
         <v>53</v>
@@ -2700,13 +2671,13 @@
         <v>11</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D10" s="15" t="s">
         <v>74</v>
       </c>
       <c r="E10" s="24" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F10" t="s">
         <v>53</v>
@@ -2729,7 +2700,7 @@
         <v>71</v>
       </c>
       <c r="E11" s="24" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F11" t="s">
         <v>38</v>
@@ -2749,7 +2720,7 @@
         <v>71</v>
       </c>
       <c r="E12" s="24" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F12" t="s">
         <v>38</v>
@@ -2772,7 +2743,7 @@
         <v>74</v>
       </c>
       <c r="E13" s="24" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F13" t="s">
         <v>54</v>
@@ -2792,7 +2763,7 @@
         <v>74</v>
       </c>
       <c r="E14" s="24" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F14" t="s">
         <v>54</v>
@@ -2809,13 +2780,13 @@
         <v>19</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D15" s="15" t="s">
         <v>71</v>
       </c>
       <c r="E15" s="24" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F15" s="15" t="s">
         <v>40</v>
@@ -2829,13 +2800,13 @@
         <v>19</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D16" s="15" t="s">
         <v>71</v>
       </c>
       <c r="E16" s="24" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F16" t="s">
         <v>40</v>
@@ -2852,13 +2823,13 @@
         <v>19</v>
       </c>
       <c r="C17" s="16" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D17" s="15" t="s">
         <v>74</v>
       </c>
       <c r="E17" s="24" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F17" t="s">
         <v>57</v>
@@ -2872,13 +2843,13 @@
         <v>19</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D18" s="15" t="s">
         <v>74</v>
       </c>
       <c r="E18" s="24" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F18" t="s">
         <v>57</v>
@@ -2899,7 +2870,7 @@
         <v>71</v>
       </c>
       <c r="E19" s="24" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F19" t="s">
         <v>41</v>
@@ -2917,7 +2888,7 @@
         <v>71</v>
       </c>
       <c r="E20" s="24" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F20" t="s">
         <v>41</v>
@@ -2938,7 +2909,7 @@
         <v>74</v>
       </c>
       <c r="E21" s="24" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F21" t="s">
         <v>58</v>
@@ -2956,7 +2927,7 @@
         <v>74</v>
       </c>
       <c r="E22" s="24" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F22" t="s">
         <v>58</v>
@@ -2977,7 +2948,7 @@
         <v>71</v>
       </c>
       <c r="E23" s="24" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F23" t="s">
         <v>42</v>
@@ -2995,7 +2966,7 @@
         <v>71</v>
       </c>
       <c r="E24" s="24" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F24" t="s">
         <v>42</v>
@@ -3016,7 +2987,7 @@
         <v>74</v>
       </c>
       <c r="E25" s="24" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F25">
         <v>5</v>
@@ -3034,7 +3005,7 @@
         <v>74</v>
       </c>
       <c r="E26" s="24" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F26">
         <v>5</v>
@@ -3055,7 +3026,7 @@
         <v>71</v>
       </c>
       <c r="E27" s="24" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F27" t="s">
         <v>43</v>
@@ -3073,7 +3044,7 @@
         <v>71</v>
       </c>
       <c r="E28" s="24" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F28" t="s">
         <v>43</v>
@@ -3090,13 +3061,13 @@
         <v>32</v>
       </c>
       <c r="C29" s="16" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D29" s="15" t="s">
         <v>71</v>
       </c>
       <c r="E29" s="24" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F29" t="s">
         <v>44</v>
@@ -3110,13 +3081,13 @@
         <v>32</v>
       </c>
       <c r="C30" s="16" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D30" s="15" t="s">
         <v>71</v>
       </c>
       <c r="E30" s="24" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F30" t="s">
         <v>44</v>
@@ -3133,13 +3104,13 @@
         <v>32</v>
       </c>
       <c r="C31" s="16" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D31" s="15" t="s">
         <v>74</v>
       </c>
       <c r="E31" s="24" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F31" t="s">
         <v>44</v>
@@ -3153,13 +3124,13 @@
         <v>32</v>
       </c>
       <c r="C32" s="16" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D32" s="15" t="s">
         <v>74</v>
       </c>
       <c r="E32" s="24" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F32" t="s">
         <v>44</v>
@@ -3201,7 +3172,7 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="2" spans="1:12" s="12" customFormat="1" ht="47.25" x14ac:dyDescent="0.25">
@@ -3209,25 +3180,25 @@
         <v>68</v>
       </c>
       <c r="B2" s="26" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C2" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="D2" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="E2" s="12" t="s">
         <v>146</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="F2" s="12" t="s">
         <v>147</v>
       </c>
-      <c r="F2" s="12" t="s">
+      <c r="G2" s="26" t="s">
         <v>148</v>
       </c>
-      <c r="G2" s="26" t="s">
+      <c r="H2" s="26" t="s">
         <v>149</v>
-      </c>
-      <c r="H2" s="26" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
@@ -3264,7 +3235,7 @@
         <v>-4.7190000000000003</v>
       </c>
       <c r="G4" s="19" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H4" t="s">
         <v>52</v>
@@ -3275,7 +3246,7 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B5" t="s">
         <v>70</v>
@@ -3301,7 +3272,7 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G6">
         <v>0.98199999999999998</v>
@@ -3338,10 +3309,10 @@
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C8">
         <v>1.2729999999999999</v>
@@ -3356,7 +3327,7 @@
         <v>-4.7050000000000001</v>
       </c>
       <c r="G8" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H8" t="s">
         <v>56</v>
@@ -3364,21 +3335,21 @@
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>151</v>
+      </c>
+      <c r="G9" t="s">
         <v>152</v>
       </c>
-      <c r="G9" t="s">
-        <v>153</v>
-      </c>
       <c r="H9" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C10">
         <v>0.84599999999999997</v>
@@ -3401,10 +3372,10 @@
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C11">
         <v>1.72</v>
@@ -3418,10 +3389,10 @@
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B12" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C12">
         <v>0.84730000000000005</v>
@@ -3470,37 +3441,37 @@
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
   </sheetData>
@@ -3515,12 +3486,12 @@
   <sheetData>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="G6" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
   </sheetData>
@@ -3546,7 +3517,7 @@
   <sheetData>
     <row r="1" spans="1:12" s="19" customFormat="1" ht="76.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B1" s="17" t="s">
         <v>34</v>
@@ -3590,7 +3561,7 @@
     </row>
     <row r="4" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>0</v>
@@ -3610,7 +3581,7 @@
     </row>
     <row r="5" spans="1:12" ht="19.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>1</v>
@@ -3632,7 +3603,7 @@
     </row>
     <row r="6" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>2</v>
@@ -3652,7 +3623,7 @@
     </row>
     <row r="7" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>3</v>
@@ -3688,7 +3659,7 @@
     </row>
     <row r="8" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>4</v>
@@ -3708,7 +3679,7 @@
     </row>
     <row r="9" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>5</v>
@@ -3730,7 +3701,7 @@
     </row>
     <row r="10" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>6</v>
@@ -3748,7 +3719,7 @@
     </row>
     <row r="11" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>7</v>
@@ -3784,7 +3755,7 @@
     </row>
     <row r="12" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>8</v>
@@ -3812,7 +3783,7 @@
     </row>
     <row r="13" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>9</v>
@@ -3834,7 +3805,7 @@
     </row>
     <row r="14" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>10</v>
@@ -3854,7 +3825,7 @@
     </row>
     <row r="15" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>11</v>
@@ -3888,7 +3859,7 @@
     </row>
     <row r="16" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>12</v>
@@ -3914,7 +3885,7 @@
     </row>
     <row r="17" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>13</v>
@@ -3932,7 +3903,7 @@
     </row>
     <row r="18" spans="1:12" s="23" customFormat="1" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B18" s="20" t="s">
         <v>14</v>
@@ -3966,7 +3937,7 @@
     </row>
     <row r="19" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>15</v>
@@ -3990,7 +3961,7 @@
     </row>
     <row r="20" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>17</v>
@@ -4010,7 +3981,7 @@
     </row>
     <row r="21" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>18</v>
@@ -4030,7 +4001,7 @@
     </row>
     <row r="22" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>19</v>
@@ -4064,7 +4035,7 @@
     </row>
     <row r="23" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>20</v>
@@ -4082,7 +4053,7 @@
     </row>
     <row r="24" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>21</v>
@@ -4100,7 +4071,7 @@
     </row>
     <row r="25" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>22</v>
@@ -4128,7 +4099,7 @@
     </row>
     <row r="26" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>23</v>
@@ -4146,7 +4117,7 @@
     </row>
     <row r="27" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>24</v>
@@ -4182,7 +4153,7 @@
     </row>
     <row r="28" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>25</v>
@@ -4202,7 +4173,7 @@
     </row>
     <row r="29" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>26</v>
@@ -4222,7 +4193,7 @@
     </row>
     <row r="30" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>27</v>
@@ -4242,7 +4213,7 @@
     </row>
     <row r="31" spans="1:12" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>28</v>
@@ -4278,7 +4249,7 @@
     </row>
     <row r="32" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>29</v>
@@ -4304,7 +4275,7 @@
     </row>
     <row r="33" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>30</v>
@@ -4324,7 +4295,7 @@
     </row>
     <row r="34" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>31</v>
@@ -4342,7 +4313,7 @@
     </row>
     <row r="35" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>32</v>

--- a/other/input/regulatory_limits/master_reg_limits.xlsx
+++ b/other/input/regulatory_limits/master_reg_limits.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28324"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="22" documentId="11_F3222DCEA08A4C9A6976DB97F14DE766E6606446" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{33C3B079-7004-419E-8489-F8A9E5413390}"/>
+  <xr:revisionPtr revIDLastSave="24" documentId="11_F3222DCEA08A4C9A6976DB97F14DE766E6606446" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{10D8033A-B275-4C8E-9854-BD11F0DEEC58}"/>
   <bookViews>
-    <workbookView xWindow="30840" yWindow="-1335" windowWidth="21600" windowHeight="11295" tabRatio="795" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="29970" yWindow="-1815" windowWidth="21600" windowHeight="11295" tabRatio="795" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ReadMe" sheetId="8" r:id="rId1"/>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="724" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="726" uniqueCount="186">
   <si>
     <t>alkalinity (as CaCO3)</t>
   </si>
@@ -617,6 +617,9 @@
   </si>
   <si>
     <t>Benzene, toluene, ethyl benzene, xylenes mix</t>
+  </si>
+  <si>
+    <t>none</t>
   </si>
 </sst>
 </file>
@@ -2431,6 +2434,9 @@
       <c r="G51" s="15">
         <v>6.5</v>
       </c>
+      <c r="H51" s="15" t="s">
+        <v>185</v>
+      </c>
       <c r="I51" s="15" t="s">
         <v>167</v>
       </c>
@@ -2453,6 +2459,9 @@
       </c>
       <c r="G52" s="15">
         <v>8.5</v>
+      </c>
+      <c r="H52" s="15" t="s">
+        <v>185</v>
       </c>
       <c r="I52" s="15" t="s">
         <v>167</v>

--- a/other/input/regulatory_limits/master_reg_limits.xlsx
+++ b/other/input/regulatory_limits/master_reg_limits.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="24" documentId="11_F3222DCEA08A4C9A6976DB97F14DE766E6606446" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{10D8033A-B275-4C8E-9854-BD11F0DEEC58}"/>
+  <xr:revisionPtr revIDLastSave="27" documentId="11_F3222DCEA08A4C9A6976DB97F14DE766E6606446" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{009BD7B4-C43D-4DD9-AC85-F5B72744DDEF}"/>
   <bookViews>
-    <workbookView xWindow="29970" yWindow="-1815" windowWidth="21600" windowHeight="11295" tabRatio="795" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2055" yWindow="3570" windowWidth="21600" windowHeight="11295" tabRatio="795" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ReadMe" sheetId="8" r:id="rId1"/>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="726" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="726" uniqueCount="187">
   <si>
     <t>alkalinity (as CaCO3)</t>
   </si>
@@ -378,9 +378,6 @@
   </si>
   <si>
     <t>Toluene</t>
-  </si>
-  <si>
-    <t>Total Nitrate/Nitrite-N</t>
   </si>
   <si>
     <t>Total Phosphorus</t>
@@ -620,6 +617,12 @@
   </si>
   <si>
     <t>none</t>
+  </si>
+  <si>
+    <t>mg/l</t>
+  </si>
+  <si>
+    <t>Nitrate + Nitrite</t>
   </si>
 </sst>
 </file>
@@ -1153,12 +1156,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="3" spans="1:1" ht="18" x14ac:dyDescent="0.25">
       <c r="A3" s="29" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
   </sheetData>
@@ -1186,7 +1189,7 @@
   <sheetData>
     <row r="1" spans="1:16" s="14" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="14" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B1" s="14" t="s">
         <v>66</v>
@@ -1204,16 +1207,16 @@
         <v>72</v>
       </c>
       <c r="G1" s="14" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H1" s="14" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="I1" s="14" t="s">
         <v>79</v>
       </c>
       <c r="J1" s="14" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K1" s="14" t="s">
         <v>75</v>
@@ -1221,7 +1224,7 @@
     </row>
     <row r="2" spans="1:16" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A2" s="15" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B2" s="15" t="s">
         <v>73</v>
@@ -1239,7 +1242,7 @@
         <v>750</v>
       </c>
       <c r="H2" s="15" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I2" s="15" t="s">
         <v>80</v>
@@ -1250,7 +1253,7 @@
     </row>
     <row r="3" spans="1:16" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A3" s="15" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B3" s="15" t="s">
         <v>73</v>
@@ -1268,13 +1271,13 @@
         <v>87</v>
       </c>
       <c r="H3" s="15" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I3" s="15" t="s">
         <v>80</v>
       </c>
       <c r="J3" s="15" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K3" s="15" t="s">
         <v>76</v>
@@ -1282,7 +1285,7 @@
     </row>
     <row r="4" spans="1:16" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A4" s="15" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B4" s="15" t="s">
         <v>73</v>
@@ -1294,13 +1297,13 @@
         <v>81</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G4" s="15">
         <v>6</v>
       </c>
       <c r="H4" s="15" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I4" s="15" t="s">
         <v>80</v>
@@ -1311,7 +1314,7 @@
     </row>
     <row r="5" spans="1:16" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A5" s="15" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B5" s="15" t="s">
         <v>73</v>
@@ -1323,13 +1326,13 @@
         <v>81</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G5" s="15">
         <v>14</v>
       </c>
       <c r="H5" s="15" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I5" s="15" t="s">
         <v>80</v>
@@ -1340,7 +1343,7 @@
     </row>
     <row r="6" spans="1:16" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A6" s="15" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B6" s="15" t="s">
         <v>73</v>
@@ -1352,13 +1355,13 @@
         <v>81</v>
       </c>
       <c r="E6" s="15" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G6" s="15">
         <v>4300</v>
       </c>
       <c r="H6" s="15" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I6" s="15" t="s">
         <v>80</v>
@@ -1369,7 +1372,7 @@
     </row>
     <row r="7" spans="1:16" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A7" s="15" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B7" s="15" t="s">
         <v>73</v>
@@ -1381,24 +1384,24 @@
         <v>82</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G7" s="15">
         <v>10</v>
       </c>
       <c r="H7" s="15" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I7" s="15" t="s">
         <v>80</v>
       </c>
       <c r="K7" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="8" spans="1:16" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A8" s="15" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B8" s="15" t="s">
         <v>73</v>
@@ -1410,24 +1413,24 @@
         <v>82</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G8" s="15">
         <v>50</v>
       </c>
       <c r="H8" s="15" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I8" s="15" t="s">
         <v>80</v>
       </c>
       <c r="K8" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="9" spans="1:16" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A9" s="15" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B9" s="15" t="s">
         <v>73</v>
@@ -1439,24 +1442,24 @@
         <v>82</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G9" s="15">
         <v>100</v>
       </c>
       <c r="H9" s="15" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I9" s="15" t="s">
         <v>80</v>
       </c>
       <c r="K9" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="10" spans="1:16" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A10" s="15" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B10" s="15" t="s">
         <v>73</v>
@@ -1468,35 +1471,35 @@
         <v>83</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G10" s="15">
         <v>2000</v>
       </c>
       <c r="H10" s="15" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I10" s="15" t="s">
         <v>80</v>
       </c>
       <c r="K10" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="11" spans="1:16" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A11" s="15" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D11" s="16" t="s">
         <v>84</v>
       </c>
       <c r="K11" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="12" spans="1:16" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A12" s="15" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B12" s="15" t="s">
         <v>73</v>
@@ -1508,19 +1511,19 @@
         <v>85</v>
       </c>
       <c r="E12" s="15" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G12" s="15">
         <v>4</v>
       </c>
       <c r="H12" s="15" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I12" s="15" t="s">
         <v>80</v>
       </c>
       <c r="K12" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="P12" s="15" t="s">
         <v>33</v>
@@ -1528,7 +1531,7 @@
     </row>
     <row r="13" spans="1:16" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A13" s="15" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B13" s="15" t="s">
         <v>73</v>
@@ -1540,24 +1543,24 @@
         <v>85</v>
       </c>
       <c r="E13" s="15" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G13" s="15">
         <v>100</v>
       </c>
       <c r="H13" s="15" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I13" s="15" t="s">
         <v>80</v>
       </c>
       <c r="K13" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="14" spans="1:16" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A14" s="15" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B14" s="15" t="s">
         <v>73</v>
@@ -1566,59 +1569,59 @@
         <v>6</v>
       </c>
       <c r="D14" s="16" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G14" s="15">
         <v>750</v>
       </c>
       <c r="H14" s="15" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I14" s="15" t="s">
         <v>80</v>
       </c>
       <c r="K14" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A15" s="15" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B15" s="15" t="s">
         <v>73</v>
       </c>
       <c r="C15" s="30" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D15" s="30" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E15" s="15" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G15" s="15">
         <v>10</v>
       </c>
       <c r="H15" s="15" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I15" s="15" t="s">
+        <v>157</v>
+      </c>
+      <c r="J15" s="15" t="s">
+        <v>159</v>
+      </c>
+      <c r="K15" s="15" t="s">
         <v>158</v>
-      </c>
-      <c r="J15" s="15" t="s">
-        <v>160</v>
-      </c>
-      <c r="K15" s="15" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="16" spans="1:16" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A16" s="15" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B16" s="15" t="s">
         <v>73</v>
@@ -1630,24 +1633,24 @@
         <v>86</v>
       </c>
       <c r="E16" s="15" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G16" s="15">
         <v>5</v>
       </c>
       <c r="H16" s="15" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I16" s="15" t="s">
         <v>80</v>
       </c>
       <c r="K16" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A17" s="15" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B17" s="15" t="s">
         <v>73</v>
@@ -1659,24 +1662,24 @@
         <v>86</v>
       </c>
       <c r="E17" s="15" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G17" s="15">
         <v>10</v>
       </c>
       <c r="H17" s="15" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I17" s="15" t="s">
         <v>80</v>
       </c>
       <c r="K17" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A18" s="15" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B18" s="15" t="s">
         <v>73</v>
@@ -1688,24 +1691,24 @@
         <v>86</v>
       </c>
       <c r="E18" s="15" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G18" s="15">
         <v>10</v>
       </c>
       <c r="H18" s="15" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I18" s="15" t="s">
         <v>80</v>
       </c>
       <c r="K18" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19" s="15" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B19" s="15" t="s">
         <v>73</v>
@@ -1717,27 +1720,27 @@
         <v>70</v>
       </c>
       <c r="E19" s="15" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G19" s="15">
         <v>100</v>
       </c>
       <c r="H19" s="15" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I19" s="15" t="s">
         <v>80</v>
       </c>
       <c r="J19" s="15" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="K19" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20" s="15" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B20" s="15" t="s">
         <v>73</v>
@@ -1749,24 +1752,24 @@
         <v>70</v>
       </c>
       <c r="E20" s="15" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G20" s="15">
         <v>100</v>
       </c>
       <c r="H20" s="15" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I20" s="15" t="s">
         <v>80</v>
       </c>
       <c r="K20" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A21" s="15" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B21" s="15" t="s">
         <v>73</v>
@@ -1778,24 +1781,24 @@
         <v>87</v>
       </c>
       <c r="E21" s="15" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G21" s="15">
         <v>50</v>
       </c>
       <c r="H21" s="15" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I21" s="15" t="s">
         <v>80</v>
       </c>
       <c r="K21" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A22" s="15" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B22" s="15" t="s">
         <v>73</v>
@@ -1807,35 +1810,35 @@
         <v>88</v>
       </c>
       <c r="E22" s="15" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G22" s="15">
         <v>200</v>
       </c>
       <c r="H22" s="15" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I22" s="15" t="s">
         <v>80</v>
       </c>
       <c r="K22" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="23" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A23" s="15" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D23" s="16" t="s">
         <v>89</v>
       </c>
       <c r="K23" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="24" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A24" s="15" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B24" s="15" t="s">
         <v>73</v>
@@ -1844,50 +1847,50 @@
         <v>90</v>
       </c>
       <c r="E24" s="15" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G24" s="15">
         <v>400</v>
       </c>
       <c r="H24" s="15" t="s">
+        <v>180</v>
+      </c>
+      <c r="I24" s="15" t="s">
         <v>181</v>
       </c>
-      <c r="I24" s="15" t="s">
+      <c r="K24" s="15" t="s">
         <v>182</v>
-      </c>
-      <c r="K24" s="15" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="25" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A25" s="15" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B25" s="15" t="s">
         <v>73</v>
       </c>
       <c r="D25" s="16" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E25" s="15" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G25" s="15">
         <v>31</v>
       </c>
       <c r="H25" s="15" t="s">
+        <v>180</v>
+      </c>
+      <c r="I25" s="15" t="s">
         <v>181</v>
       </c>
-      <c r="I25" s="15" t="s">
+      <c r="K25" s="15" t="s">
         <v>182</v>
-      </c>
-      <c r="K25" s="15" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="26" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A26" s="15" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B26" s="15" t="s">
         <v>73</v>
@@ -1899,24 +1902,24 @@
         <v>91</v>
       </c>
       <c r="E26" s="15" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G26" s="15">
         <v>50</v>
       </c>
       <c r="H26" s="15" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I26" s="15" t="s">
         <v>80</v>
       </c>
       <c r="K26" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="27" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A27" s="15" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B27" s="15" t="s">
         <v>73</v>
@@ -1928,7 +1931,7 @@
         <v>91</v>
       </c>
       <c r="E27" s="15" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F27" s="15" t="s">
         <v>33</v>
@@ -1937,18 +1940,18 @@
         <v>5000</v>
       </c>
       <c r="H27" s="15" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I27" s="15" t="s">
         <v>80</v>
       </c>
       <c r="K27" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="28" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A28" s="15" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B28" s="15" t="s">
         <v>73</v>
@@ -1960,24 +1963,24 @@
         <v>92</v>
       </c>
       <c r="E28" s="15" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G28" s="15">
         <v>10</v>
       </c>
       <c r="H28" s="15" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I28" s="15" t="s">
         <v>80</v>
       </c>
       <c r="K28" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="29" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A29" s="15" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B29" s="15" t="s">
         <v>73</v>
@@ -1989,24 +1992,24 @@
         <v>93</v>
       </c>
       <c r="E29" s="15" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G29" s="15">
         <v>100</v>
       </c>
       <c r="H29" s="15" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I29" s="15" t="s">
         <v>80</v>
       </c>
       <c r="K29" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="30" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A30" s="15" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B30" s="15" t="s">
         <v>73</v>
@@ -2018,41 +2021,41 @@
         <v>93</v>
       </c>
       <c r="E30" s="15" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G30" s="15">
         <v>200</v>
       </c>
       <c r="H30" s="15" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I30" s="15" t="s">
         <v>80</v>
       </c>
       <c r="K30" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="31" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A31" s="15" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B31" s="15" t="s">
         <v>73</v>
       </c>
       <c r="C31" s="15" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D31" s="16" t="s">
         <v>94</v>
       </c>
       <c r="K31" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="32" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A32" s="15" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B32" s="15" t="s">
         <v>73</v>
@@ -2067,46 +2070,46 @@
         <v>33</v>
       </c>
       <c r="K32" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="33" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A33" s="15" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B33" s="15" t="s">
         <v>73</v>
       </c>
       <c r="C33" s="15" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D33" s="16" t="s">
         <v>96</v>
       </c>
       <c r="K33" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="34" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A34" s="15" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B34" s="15" t="s">
         <v>73</v>
       </c>
       <c r="C34" s="13" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D34" s="16" t="s">
         <v>97</v>
       </c>
       <c r="K34" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="35" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A35" s="15" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B35" s="15" t="s">
         <v>73</v>
@@ -2118,24 +2121,24 @@
         <v>98</v>
       </c>
       <c r="E35" s="15" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G35" s="15">
         <v>50</v>
       </c>
       <c r="H35" s="15" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I35" s="15" t="s">
         <v>80</v>
       </c>
       <c r="K35" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="36" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A36" s="15" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B36" s="15" t="s">
         <v>73</v>
@@ -2147,24 +2150,24 @@
         <v>98</v>
       </c>
       <c r="E36" s="15" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G36" s="15">
         <v>10</v>
       </c>
       <c r="H36" s="15" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I36" s="15" t="s">
         <v>80</v>
       </c>
       <c r="K36" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="37" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A37" s="15" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B37" s="15" t="s">
         <v>73</v>
@@ -2176,35 +2179,35 @@
         <v>98</v>
       </c>
       <c r="E37" s="15" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G37" s="15">
         <v>20</v>
       </c>
       <c r="H37" s="15" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I37" s="15" t="s">
         <v>80</v>
       </c>
       <c r="K37" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="38" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A38" s="15" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D38" s="16" t="s">
         <v>99</v>
       </c>
       <c r="K38" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="39" spans="1:11" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A39" s="15" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B39" s="15" t="s">
         <v>73</v>
@@ -2213,26 +2216,26 @@
         <v>100</v>
       </c>
       <c r="J39" s="31" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="K39" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="40" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A40" s="15" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D40" s="16" t="s">
         <v>101</v>
       </c>
       <c r="K40" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="41" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A41" s="15" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B41" s="15" t="s">
         <v>73</v>
@@ -2244,111 +2247,111 @@
         <v>102</v>
       </c>
       <c r="E41" s="15" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G41" s="15">
         <v>2</v>
       </c>
       <c r="H41" s="15" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I41" s="15" t="s">
         <v>80</v>
       </c>
       <c r="K41" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="42" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A42" s="15" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D42" s="16" t="s">
         <v>103</v>
       </c>
       <c r="K42" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="43" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A43" s="15" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D43" s="16" t="s">
         <v>104</v>
       </c>
       <c r="K43" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="44" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A44" s="15" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D44" s="16" t="s">
         <v>105</v>
       </c>
       <c r="J44" s="15" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="K44" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="45" spans="1:11" ht="15" x14ac:dyDescent="0.25">
       <c r="A45" s="15" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B45" s="15" t="s">
         <v>73</v>
       </c>
       <c r="C45" s="15" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D45" s="16" t="s">
-        <v>106</v>
+        <v>186</v>
       </c>
       <c r="E45" s="15" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G45" s="15">
-        <v>10000</v>
+        <v>10</v>
       </c>
       <c r="H45" s="15" t="s">
-        <v>123</v>
+        <v>185</v>
       </c>
       <c r="I45" s="32" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="K45" s="15" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="46" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A46" s="15" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D46" s="16" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="K46" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="47" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A47" s="15" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D47" s="16" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K47" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="48" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A48" s="15" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B48" s="15" t="s">
         <v>73</v>
@@ -2357,38 +2360,38 @@
         <v>31</v>
       </c>
       <c r="D48" s="16" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E48" s="15" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G48" s="15">
         <v>100</v>
       </c>
       <c r="H48" s="15" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I48" s="15" t="s">
         <v>80</v>
       </c>
       <c r="K48" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="49" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A49" s="15" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D49" s="16" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="K49" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="50" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A50" s="15" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B50" s="15" t="s">
         <v>73</v>
@@ -2397,74 +2400,74 @@
         <v>32</v>
       </c>
       <c r="D50" s="16" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E50" s="15" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G50" s="15">
         <v>2000</v>
       </c>
       <c r="H50" s="15" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I50" s="15" t="s">
         <v>80</v>
       </c>
       <c r="K50" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A51" s="15" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B51" s="15" t="s">
         <v>73</v>
       </c>
       <c r="C51" s="15" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D51" s="15" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E51" s="15" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G51" s="15">
         <v>6.5</v>
       </c>
       <c r="H51" s="15" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="I51" s="15" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A52" s="15" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B52" s="15" t="s">
         <v>73</v>
       </c>
       <c r="C52" s="15" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D52" s="15" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E52" s="15" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G52" s="15">
         <v>8.5</v>
       </c>
       <c r="H52" s="15" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="I52" s="15" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.2">
@@ -2497,7 +2500,7 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="25" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="2" spans="1:7" s="19" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
@@ -2514,13 +2517,13 @@
         <v>67</v>
       </c>
       <c r="E2" s="27" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F2" s="26" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G2" s="26" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -2537,7 +2540,7 @@
         <v>71</v>
       </c>
       <c r="E3" s="24" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F3" s="28" t="s">
         <v>36</v>
@@ -2557,10 +2560,10 @@
         <v>71</v>
       </c>
       <c r="E4" s="24" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F4" s="28" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G4" t="s">
         <v>50</v>
@@ -2580,7 +2583,7 @@
         <v>74</v>
       </c>
       <c r="E5" s="24" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F5" s="28" t="s">
         <v>51</v>
@@ -2600,7 +2603,7 @@
         <v>74</v>
       </c>
       <c r="E6" s="24" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F6" s="28" t="s">
         <v>51</v>
@@ -2617,13 +2620,13 @@
         <v>11</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D7" s="15" t="s">
         <v>71</v>
       </c>
       <c r="E7" s="24" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F7" t="s">
         <v>37</v>
@@ -2637,13 +2640,13 @@
         <v>11</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D8" s="15" t="s">
         <v>71</v>
       </c>
       <c r="E8" s="24" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F8" t="s">
         <v>37</v>
@@ -2660,13 +2663,13 @@
         <v>11</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D9" s="15" t="s">
         <v>74</v>
       </c>
       <c r="E9" s="24" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F9" t="s">
         <v>53</v>
@@ -2680,13 +2683,13 @@
         <v>11</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D10" s="15" t="s">
         <v>74</v>
       </c>
       <c r="E10" s="24" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F10" t="s">
         <v>53</v>
@@ -2709,7 +2712,7 @@
         <v>71</v>
       </c>
       <c r="E11" s="24" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F11" t="s">
         <v>38</v>
@@ -2729,7 +2732,7 @@
         <v>71</v>
       </c>
       <c r="E12" s="24" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F12" t="s">
         <v>38</v>
@@ -2752,7 +2755,7 @@
         <v>74</v>
       </c>
       <c r="E13" s="24" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F13" t="s">
         <v>54</v>
@@ -2772,7 +2775,7 @@
         <v>74</v>
       </c>
       <c r="E14" s="24" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F14" t="s">
         <v>54</v>
@@ -2795,7 +2798,7 @@
         <v>71</v>
       </c>
       <c r="E15" s="24" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F15" s="15" t="s">
         <v>40</v>
@@ -2815,7 +2818,7 @@
         <v>71</v>
       </c>
       <c r="E16" s="24" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F16" t="s">
         <v>40</v>
@@ -2838,7 +2841,7 @@
         <v>74</v>
       </c>
       <c r="E17" s="24" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F17" t="s">
         <v>57</v>
@@ -2858,7 +2861,7 @@
         <v>74</v>
       </c>
       <c r="E18" s="24" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F18" t="s">
         <v>57</v>
@@ -2879,7 +2882,7 @@
         <v>71</v>
       </c>
       <c r="E19" s="24" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F19" t="s">
         <v>41</v>
@@ -2897,7 +2900,7 @@
         <v>71</v>
       </c>
       <c r="E20" s="24" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F20" t="s">
         <v>41</v>
@@ -2918,7 +2921,7 @@
         <v>74</v>
       </c>
       <c r="E21" s="24" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F21" t="s">
         <v>58</v>
@@ -2936,7 +2939,7 @@
         <v>74</v>
       </c>
       <c r="E22" s="24" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F22" t="s">
         <v>58</v>
@@ -2957,7 +2960,7 @@
         <v>71</v>
       </c>
       <c r="E23" s="24" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F23" t="s">
         <v>42</v>
@@ -2975,7 +2978,7 @@
         <v>71</v>
       </c>
       <c r="E24" s="24" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F24" t="s">
         <v>42</v>
@@ -2996,7 +2999,7 @@
         <v>74</v>
       </c>
       <c r="E25" s="24" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F25">
         <v>5</v>
@@ -3014,7 +3017,7 @@
         <v>74</v>
       </c>
       <c r="E26" s="24" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F26">
         <v>5</v>
@@ -3035,7 +3038,7 @@
         <v>71</v>
       </c>
       <c r="E27" s="24" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F27" t="s">
         <v>43</v>
@@ -3053,7 +3056,7 @@
         <v>71</v>
       </c>
       <c r="E28" s="24" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F28" t="s">
         <v>43</v>
@@ -3070,13 +3073,13 @@
         <v>32</v>
       </c>
       <c r="C29" s="16" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D29" s="15" t="s">
         <v>71</v>
       </c>
       <c r="E29" s="24" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F29" t="s">
         <v>44</v>
@@ -3090,13 +3093,13 @@
         <v>32</v>
       </c>
       <c r="C30" s="16" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D30" s="15" t="s">
         <v>71</v>
       </c>
       <c r="E30" s="24" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F30" t="s">
         <v>44</v>
@@ -3113,13 +3116,13 @@
         <v>32</v>
       </c>
       <c r="C31" s="16" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D31" s="15" t="s">
         <v>74</v>
       </c>
       <c r="E31" s="24" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F31" t="s">
         <v>44</v>
@@ -3133,13 +3136,13 @@
         <v>32</v>
       </c>
       <c r="C32" s="16" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D32" s="15" t="s">
         <v>74</v>
       </c>
       <c r="E32" s="24" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F32" t="s">
         <v>44</v>
@@ -3181,7 +3184,7 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="2" spans="1:12" s="12" customFormat="1" ht="47.25" x14ac:dyDescent="0.25">
@@ -3189,25 +3192,25 @@
         <v>68</v>
       </c>
       <c r="B2" s="26" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C2" s="12" t="s">
+        <v>143</v>
+      </c>
+      <c r="D2" s="12" t="s">
         <v>144</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="E2" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="F2" s="12" t="s">
         <v>146</v>
       </c>
-      <c r="F2" s="12" t="s">
+      <c r="G2" s="26" t="s">
         <v>147</v>
       </c>
-      <c r="G2" s="26" t="s">
+      <c r="H2" s="26" t="s">
         <v>148</v>
-      </c>
-      <c r="H2" s="26" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
@@ -3244,7 +3247,7 @@
         <v>-4.7190000000000003</v>
       </c>
       <c r="G4" s="19" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H4" t="s">
         <v>52</v>
@@ -3255,7 +3258,7 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B5" t="s">
         <v>70</v>
@@ -3281,7 +3284,7 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G6">
         <v>0.98199999999999998</v>
@@ -3336,7 +3339,7 @@
         <v>-4.7050000000000001</v>
       </c>
       <c r="G8" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H8" t="s">
         <v>56</v>
@@ -3344,13 +3347,13 @@
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>150</v>
+      </c>
+      <c r="G9" t="s">
         <v>151</v>
       </c>
-      <c r="G9" t="s">
-        <v>152</v>
-      </c>
       <c r="H9" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
@@ -3398,10 +3401,10 @@
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B12" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C12">
         <v>0.84730000000000005</v>
@@ -3450,37 +3453,37 @@
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
   </sheetData>
@@ -3495,12 +3498,12 @@
   <sheetData>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="G6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
   </sheetData>
@@ -3526,7 +3529,7 @@
   <sheetData>
     <row r="1" spans="1:12" s="19" customFormat="1" ht="76.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B1" s="17" t="s">
         <v>34</v>
@@ -3570,7 +3573,7 @@
     </row>
     <row r="4" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>0</v>
@@ -3590,7 +3593,7 @@
     </row>
     <row r="5" spans="1:12" ht="19.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>1</v>
@@ -3612,7 +3615,7 @@
     </row>
     <row r="6" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>2</v>
@@ -3632,7 +3635,7 @@
     </row>
     <row r="7" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>3</v>
@@ -3668,7 +3671,7 @@
     </row>
     <row r="8" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>4</v>
@@ -3688,7 +3691,7 @@
     </row>
     <row r="9" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>5</v>
@@ -3710,7 +3713,7 @@
     </row>
     <row r="10" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>6</v>
@@ -3728,7 +3731,7 @@
     </row>
     <row r="11" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>7</v>
@@ -3764,7 +3767,7 @@
     </row>
     <row r="12" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>8</v>
@@ -3792,7 +3795,7 @@
     </row>
     <row r="13" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>9</v>
@@ -3814,7 +3817,7 @@
     </row>
     <row r="14" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>10</v>
@@ -3834,7 +3837,7 @@
     </row>
     <row r="15" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>11</v>
@@ -3868,7 +3871,7 @@
     </row>
     <row r="16" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>12</v>
@@ -3894,7 +3897,7 @@
     </row>
     <row r="17" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>13</v>
@@ -3912,7 +3915,7 @@
     </row>
     <row r="18" spans="1:12" s="23" customFormat="1" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B18" s="20" t="s">
         <v>14</v>
@@ -3946,7 +3949,7 @@
     </row>
     <row r="19" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>15</v>
@@ -3970,7 +3973,7 @@
     </row>
     <row r="20" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>17</v>
@@ -3990,7 +3993,7 @@
     </row>
     <row r="21" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>18</v>
@@ -4010,7 +4013,7 @@
     </row>
     <row r="22" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>19</v>
@@ -4044,7 +4047,7 @@
     </row>
     <row r="23" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>20</v>
@@ -4062,7 +4065,7 @@
     </row>
     <row r="24" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>21</v>
@@ -4080,7 +4083,7 @@
     </row>
     <row r="25" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>22</v>
@@ -4108,7 +4111,7 @@
     </row>
     <row r="26" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>23</v>
@@ -4126,7 +4129,7 @@
     </row>
     <row r="27" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>24</v>
@@ -4162,7 +4165,7 @@
     </row>
     <row r="28" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>25</v>
@@ -4182,7 +4185,7 @@
     </row>
     <row r="29" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>26</v>
@@ -4202,7 +4205,7 @@
     </row>
     <row r="30" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>27</v>
@@ -4222,7 +4225,7 @@
     </row>
     <row r="31" spans="1:12" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>28</v>
@@ -4258,7 +4261,7 @@
     </row>
     <row r="32" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>29</v>
@@ -4284,7 +4287,7 @@
     </row>
     <row r="33" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>30</v>
@@ -4304,7 +4307,7 @@
     </row>
     <row r="34" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>31</v>
@@ -4322,7 +4325,7 @@
     </row>
     <row r="35" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>32</v>
